--- a/docs/Clinical_Documentation_Audit_Simple.xlsx
+++ b/docs/Clinical_Documentation_Audit_Simple.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -84,8 +84,55 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000F172A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000B5555"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="20"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -132,8 +179,18 @@
         <fgColor rgb="00F8C9C9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F8F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000B5555"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -160,11 +217,88 @@
       <right/>
       <bottom/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -233,6 +367,54 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -630,580 +812,626 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Clinical Documentation Audit — Checklist</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>One chart · one page · tick each element ✓ Met · △ Partial · ✗ Not Met · N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Clinical Documentation Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>One chart per sheet · tick each item · scoring &amp; rating are automatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>Provider:</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="27" t="inlineStr">
         <is>
           <t>Date of Service:</t>
         </is>
       </c>
       <c r="D4" s="4" t="n"/>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
         <is>
           <t>How to use
-• Pick ✓ / △ / ✗ / N/A for each row
-• Score auto-totals at the bottom
-• Log the chart on the Audit Log tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+1. Fill in the yellow cells at top
+2. Rate each element (dropdown in column C)
+3. Overall % + Rating appear at the bottom
+4. Log the chart on the Audit Log tab when done</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>MRN (masked):</t>
         </is>
       </c>
       <c r="B5" s="4" t="n"/>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Auditor:</t>
         </is>
       </c>
       <c r="D5" s="4" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Category:</t>
         </is>
       </c>
       <c r="B6" s="4" t="n"/>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>Payer:</t>
         </is>
       </c>
       <c r="D6" s="4" t="n"/>
     </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="7" ht="12" customHeight="1"/>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
         <is>
           <t>§</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Documentation Element</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Documentation element</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="inlineStr">
         <is>
           <t>Rating</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Notes / Evidence</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Pts</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="inlineStr">
+        <is>
+          <t>Notes / evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A · Diagnosis Accuracy   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>All reported diagnoses are clinically supported in the note</t>
         </is>
       </c>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="9">
-        <f>IF(C9="✓ Met",1,IF(C9="△ Partial",0.5,IF(C9="✗ Not Met",0,IF(C9="N/A","",""))))</f>
-        <v/>
-      </c>
-      <c r="E9" s="10" t="n"/>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Chronic conditions actively addressed at this visit (not just carried forward)</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="9">
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="33">
         <f>IF(C10="✓ Met",1,IF(C10="△ Partial",0.5,IF(C10="✗ Not Met",0,IF(C10="N/A","",""))))</f>
         <v/>
       </c>
       <c r="E10" s="10" t="n"/>
     </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>A3</t>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>A2</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>No unsupported or resolved conditions billed as active</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="9">
+          <t>Chronic conditions actively addressed at this visit (not just carried forward)</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="33">
         <f>IF(C11="✓ Met",1,IF(C11="△ Partial",0.5,IF(C11="✗ Not Met",0,IF(C11="N/A","",""))))</f>
         <v/>
       </c>
       <c r="E11" s="10" t="n"/>
     </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>A4</t>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>A3</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Problem list matches today's assessment &amp; plan</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="9">
+          <t>No unsupported or resolved conditions billed as active</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="33">
         <f>IF(C12="✓ Met",1,IF(C12="△ Partial",0.5,IF(C12="✗ Not Met",0,IF(C12="N/A","",""))))</f>
         <v/>
       </c>
       <c r="E12" s="10" t="n"/>
     </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>ICD-10 codes at highest available specificity (avoid 'unspecified')</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="9">
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Problem list matches today's assessment &amp; plan</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="33">
         <f>IF(C13="✓ Met",1,IF(C13="△ Partial",0.5,IF(C13="✗ Not Met",0,IF(C13="N/A","",""))))</f>
         <v/>
       </c>
       <c r="E13" s="10" t="n"/>
     </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Diabetes: type + complications + control specified</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="9">
-        <f>IF(C14="✓ Met",1,IF(C14="△ Partial",0.5,IF(C14="✗ Not Met",0,IF(C14="N/A","",""))))</f>
-        <v/>
-      </c>
-      <c r="E14" s="10" t="n"/>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>S / O / A / P sections tell one consistent clinical story</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="9">
-        <f>IF(C15="✓ Met",1,IF(C15="△ Partial",0.5,IF(C15="✗ Not Met",0,IF(C15="N/A","",""))))</f>
-        <v/>
-      </c>
-      <c r="E15" s="10" t="n"/>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>B4</t>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B · Documentation Specificity   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>B1</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Note signed, dated, and closed by the rendering provider</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="9">
+          <t>ICD-10 codes at highest available specificity (avoid 'unspecified')</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="33">
         <f>IF(C16="✓ Met",1,IF(C16="△ Partial",0.5,IF(C16="✗ Not Met",0,IF(C16="N/A","",""))))</f>
         <v/>
       </c>
       <c r="E16" s="10" t="n"/>
     </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Monitor — signs, symptoms, or labs monitored</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="9">
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes: type + complications + control specified</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="33">
         <f>IF(C17="✓ Met",1,IF(C17="△ Partial",0.5,IF(C17="✗ Not Met",0,IF(C17="N/A","",""))))</f>
         <v/>
       </c>
       <c r="E17" s="10" t="n"/>
     </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>C2</t>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>B3</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Evaluate — response to treatment evaluated</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="9">
+          <t>S / O / A / P sections tell one consistent clinical story</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="33">
         <f>IF(C18="✓ Met",1,IF(C18="△ Partial",0.5,IF(C18="✗ Not Met",0,IF(C18="N/A","",""))))</f>
         <v/>
       </c>
       <c r="E18" s="10" t="n"/>
     </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>C3</t>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>B4</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Assess / Address — diagnosis explicitly assessed today</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="9">
+          <t>Note signed, dated, and closed by the rendering provider</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="33">
         <f>IF(C19="✓ Met",1,IF(C19="△ Partial",0.5,IF(C19="✗ Not Met",0,IF(C19="N/A","",""))))</f>
         <v/>
       </c>
       <c r="E19" s="10" t="n"/>
     </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>Treat — treatment plan documented (med / referral / testing / follow-up)</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="9">
-        <f>IF(C20="✓ Met",1,IF(C20="△ Partial",0.5,IF(C20="✗ Not Met",0,IF(C20="N/A","",""))))</f>
-        <v/>
-      </c>
-      <c r="E20" s="10" t="n"/>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Prior-year HCCs recaptured (or explicitly resolved with rationale)</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="9">
-        <f>IF(C21="✓ Met",1,IF(C21="△ Partial",0.5,IF(C21="✗ Not Met",0,IF(C21="N/A","",""))))</f>
-        <v/>
-      </c>
-      <c r="E21" s="10" t="n"/>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>D2</t>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C · MEAT Support   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>C1</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Suspected undocumented chronic conditions captured with support</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="9">
+          <t>Monitor — signs, symptoms, or labs monitored</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="33">
         <f>IF(C22="✓ Met",1,IF(C22="△ Partial",0.5,IF(C22="✗ Not Met",0,IF(C22="N/A","",""))))</f>
         <v/>
       </c>
       <c r="E22" s="10" t="n"/>
     </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>E1</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Applicable CPT II codes reported for open quality measures</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="9">
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Evaluate — response to treatment evaluated</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="33">
         <f>IF(C23="✓ Met",1,IF(C23="△ Partial",0.5,IF(C23="✗ Not Met",0,IF(C23="N/A","",""))))</f>
         <v/>
       </c>
       <c r="E23" s="10" t="n"/>
     </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>E2</t>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>C3</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Reason modifiers (1P / 2P / 3P / 8P) applied when measure not met</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="9">
+          <t>Assess / Address — diagnosis explicitly assessed today</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="33">
         <f>IF(C24="✓ Met",1,IF(C24="△ Partial",0.5,IF(C24="✗ Not Met",0,IF(C24="N/A","",""))))</f>
         <v/>
       </c>
       <c r="E24" s="10" t="n"/>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Treat — treatment plan documented (medication / referral / testing / follow-up)</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="33">
+        <f>IF(C25="✓ Met",1,IF(C25="△ Partial",0.5,IF(C25="✗ Not Met",0,IF(C25="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D · HCC Capture   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Prior-year HCCs recaptured (or explicitly resolved with rationale)</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="33">
+        <f>IF(C28="✓ Met",1,IF(C28="△ Partial",0.5,IF(C28="✗ Not Met",0,IF(C28="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Suspected undocumented chronic conditions captured with support</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="33">
+        <f>IF(C29="✓ Met",1,IF(C29="△ Partial",0.5,IF(C29="✗ Not Met",0,IF(C29="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E · CPT II Reporting   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Applicable CPT II codes reported for open quality measures</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="33">
+        <f>IF(C32="✓ Met",1,IF(C32="△ Partial",0.5,IF(C32="✗ Not Met",0,IF(C32="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Reason modifiers (1P / 2P / 3P / 8P) applied when a measure is not met</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33">
+        <f>IF(C33="✓ Met",1,IF(C33="△ Partial",0.5,IF(C33="✗ Not Met",0,IF(C33="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>§</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>Applicable</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>% Met</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>Diagnosis Accuracy</t>
         </is>
       </c>
-      <c r="C28" s="9">
-        <f>COUNTIF(C9:C12,"✓ Met")+COUNTIF(C9:C12,"△ Partial")+COUNTIF(C9:C12,"✗ Not Met")</f>
+      <c r="C38" s="36">
+        <f>COUNTIF(C10:C13,"✓ Met")+COUNTIF(C10:C13,"△ Partial")+COUNTIF(C10:C13,"✗ Not Met")</f>
         <v/>
       </c>
-      <c r="D28" s="12">
-        <f>IFERROR(SUM(D9:D12)/C28,"")</f>
+      <c r="D38" s="37">
+        <f>IFERROR(SUM(D10:D13)/C38,"")</f>
         <v/>
       </c>
-      <c r="E28" s="10" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="E38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>Documentation Specificity</t>
         </is>
       </c>
-      <c r="C29" s="9">
-        <f>COUNTIF(C13:C16,"✓ Met")+COUNTIF(C13:C16,"△ Partial")+COUNTIF(C13:C16,"✗ Not Met")</f>
+      <c r="C39" s="36">
+        <f>COUNTIF(C16:C19,"✓ Met")+COUNTIF(C16:C19,"△ Partial")+COUNTIF(C16:C19,"✗ Not Met")</f>
         <v/>
       </c>
-      <c r="D29" s="12">
-        <f>IFERROR(SUM(D13:D16)/C29,"")</f>
+      <c r="D39" s="37">
+        <f>IFERROR(SUM(D16:D19)/C39,"")</f>
         <v/>
       </c>
-      <c r="E29" s="10" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="E39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>MEAT Support</t>
         </is>
       </c>
-      <c r="C30" s="9">
-        <f>COUNTIF(C17:C20,"✓ Met")+COUNTIF(C17:C20,"△ Partial")+COUNTIF(C17:C20,"✗ Not Met")</f>
+      <c r="C40" s="36">
+        <f>COUNTIF(C22:C25,"✓ Met")+COUNTIF(C22:C25,"△ Partial")+COUNTIF(C22:C25,"✗ Not Met")</f>
         <v/>
       </c>
-      <c r="D30" s="12">
-        <f>IFERROR(SUM(D17:D20)/C30,"")</f>
+      <c r="D40" s="37">
+        <f>IFERROR(SUM(D22:D25)/C40,"")</f>
         <v/>
       </c>
-      <c r="E30" s="10" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="E40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>HCC Capture</t>
         </is>
       </c>
-      <c r="C31" s="9">
-        <f>COUNTIF(C21:C22,"✓ Met")+COUNTIF(C21:C22,"△ Partial")+COUNTIF(C21:C22,"✗ Not Met")</f>
+      <c r="C41" s="36">
+        <f>COUNTIF(C28:C29,"✓ Met")+COUNTIF(C28:C29,"△ Partial")+COUNTIF(C28:C29,"✗ Not Met")</f>
         <v/>
       </c>
-      <c r="D31" s="12">
-        <f>IFERROR(SUM(D21:D22)/C31,"")</f>
+      <c r="D41" s="37">
+        <f>IFERROR(SUM(D28:D29)/C41,"")</f>
         <v/>
       </c>
-      <c r="E31" s="10" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="E41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="35" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>CPT II Reporting</t>
         </is>
       </c>
-      <c r="C32" s="9">
-        <f>COUNTIF(C23:C24,"✓ Met")+COUNTIF(C23:C24,"△ Partial")+COUNTIF(C23:C24,"✗ Not Met")</f>
+      <c r="C42" s="36">
+        <f>COUNTIF(C32:C33,"✓ Met")+COUNTIF(C32:C33,"△ Partial")+COUNTIF(C32:C33,"✗ Not Met")</f>
         <v/>
       </c>
-      <c r="D32" s="12">
-        <f>IFERROR(SUM(D23:D24)/C32,"")</f>
+      <c r="D42" s="37">
+        <f>IFERROR(SUM(D32:D33)/C42,"")</f>
         <v/>
       </c>
-      <c r="E32" s="10" t="n"/>
-    </row>
-    <row r="34" ht="34" customHeight="1">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>OVERALL COMPLIANCE %</t>
-        </is>
-      </c>
-      <c r="B34" s="14" t="n"/>
-      <c r="C34" s="15">
-        <f>SUM(C28:C32)</f>
+      <c r="E42" s="14" t="inlineStr"/>
+    </row>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OVERALL COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="D44" s="39">
+        <f>IFERROR(SUMPRODUCT(D38:D42,C38:C42)/SUM(C38:C42),"")</f>
         <v/>
       </c>
-      <c r="D34" s="16">
-        <f>IFERROR(SUMPRODUCT(D28:D32,C28:C32)/SUM(C28:C32),"")</f>
+      <c r="E44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PERFORMANCE BAND</t>
+        </is>
+      </c>
+      <c r="D45" s="18">
+        <f>IF(D44="","",IF(D44&gt;=0.95,"Excellent",IF(D44&gt;=0.90,"Meets Expectations",IF(D44&gt;=0.80,"Needs Improvement","Corrective Education Required"))))</f>
         <v/>
       </c>
-      <c r="E34" s="17" t="n"/>
-    </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>RATING</t>
-        </is>
-      </c>
-      <c r="D35" s="18">
-        <f>IF(D34="","",IF(D34&gt;=0.95,"Excellent",IF(D34&gt;=0.90,"Meets Expectations",IF(D34&gt;=0.80,"Needs Improvement","Corrective Education Required"))))</f>
-        <v/>
-      </c>
-      <c r="E35" s="14" t="n"/>
+      <c r="E45" s="14" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="11">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A44:C44"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A15:E15"/>
     <mergeCell ref="E4:E6"/>
-    <mergeCell ref="E6"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A27:E27"/>
   </mergeCells>
-  <conditionalFormatting sqref="C9:C24">
+  <conditionalFormatting sqref="C10:C34">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>C9="✓ Met"</formula>
+      <formula>C10="✓ Met"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>C9="△ Partial"</formula>
+      <formula>C10="△ Partial"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="2">
-      <formula>C9="✗ Not Met"</formula>
+      <formula>C10="✗ Not Met"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>C9="N/A"</formula>
+      <formula>C10="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D28">
+  <conditionalFormatting sqref="D38">
     <cfRule type="cellIs" priority="5" operator="greaterThanOrEqual" dxfId="0">
       <formula>0.9</formula>
     </cfRule>
@@ -1215,7 +1443,7 @@
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D29">
+  <conditionalFormatting sqref="D39">
     <cfRule type="cellIs" priority="8" operator="greaterThanOrEqual" dxfId="0">
       <formula>0.9</formula>
     </cfRule>
@@ -1227,7 +1455,7 @@
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D30">
+  <conditionalFormatting sqref="D40">
     <cfRule type="cellIs" priority="11" operator="greaterThanOrEqual" dxfId="0">
       <formula>0.9</formula>
     </cfRule>
@@ -1239,7 +1467,7 @@
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D31">
+  <conditionalFormatting sqref="D41">
     <cfRule type="cellIs" priority="14" operator="greaterThanOrEqual" dxfId="0">
       <formula>0.9</formula>
     </cfRule>
@@ -1251,7 +1479,7 @@
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D32">
+  <conditionalFormatting sqref="D42">
     <cfRule type="cellIs" priority="17" operator="greaterThanOrEqual" dxfId="0">
       <formula>0.9</formula>
     </cfRule>
@@ -1263,7 +1491,7 @@
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D34">
+  <conditionalFormatting sqref="D44">
     <cfRule type="cellIs" priority="20" operator="greaterThanOrEqual" dxfId="3">
       <formula>0.95</formula>
     </cfRule>
@@ -1279,18 +1507,18 @@
       <formula>0.8</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D35">
+  <conditionalFormatting sqref="D45">
     <cfRule type="expression" priority="24" dxfId="3">
-      <formula>D35="Excellent"</formula>
+      <formula>D45="Excellent"</formula>
     </cfRule>
     <cfRule type="expression" priority="25" dxfId="0">
-      <formula>D35="Meets Expectations"</formula>
+      <formula>D45="Meets Expectations"</formula>
     </cfRule>
     <cfRule type="expression" priority="26" dxfId="1">
-      <formula>D35="Needs Improvement"</formula>
+      <formula>D45="Needs Improvement"</formula>
     </cfRule>
     <cfRule type="expression" priority="27" dxfId="2">
-      <formula>D35="Corrective Education Required"</formula>
+      <formula>D45="Corrective Education Required"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -1300,7 +1528,7 @@
     <dataValidation sqref="D6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Medicare Advantage,Commercial,Medicaid,Dual"</formula1>
     </dataValidation>
-    <dataValidation sqref="C9:C24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C10:C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓ Met,△ Partial,✗ Not Met,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/Clinical_Documentation_Audit_Simple.xlsx
+++ b/docs/Clinical_Documentation_Audit_Simple.xlsx
@@ -1079,7 +1079,7 @@
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  C · MEAT Support   (4 items)</t>
+          <t xml:space="preserve">  C · SOAP Note Structure   (4 items)</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Monitor — signs, symptoms, or labs monitored</t>
+          <t>Subjective — patient's history, symptoms, and concerns clearly documented</t>
         </is>
       </c>
       <c r="C22" s="32" t="n"/>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
-          <t>Evaluate — response to treatment evaluated</t>
+          <t>Objective — exam findings, vitals, and relevant test results documented</t>
         </is>
       </c>
       <c r="C23" s="32" t="n"/>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
-          <t>Assess / Address — diagnosis explicitly assessed today</t>
+          <t>Assessment — each diagnosis explicitly assessed with clinical reasoning</t>
         </is>
       </c>
       <c r="C24" s="32" t="n"/>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Treat — treatment plan documented (medication / referral / testing / follow-up)</t>
+          <t>Plan — treatment plan documented (medication / referral / testing / follow-up)</t>
         </is>
       </c>
       <c r="C25" s="32" t="n"/>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>MEAT Support</t>
+          <t>SOAP Note Structure</t>
         </is>
       </c>
       <c r="C40" s="36">
@@ -3842,14 +3842,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="19" t="inlineStr">
         <is>
-          <t>Quick Reference — MEAT · Bands · High-Risk Dx · CPT II</t>
+          <t>Quick Reference — SOAP · Bands · High-Risk Dx · CPT II</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="20" t="inlineStr">
         <is>
-          <t>MEAT Criteria</t>
+          <t>SOAP Note Structure</t>
         </is>
       </c>
     </row>
@@ -3874,17 +3874,17 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Monitor</t>
+          <t>Subjective</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>Signs / symptoms / labs monitored</t>
+          <t>Patient history, symptoms, concerns</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>HbA1c 7.8 stable, BP log reviewed</t>
+          <t>'Patient reports 2-week low mood, poor sleep, denies SI/HI'</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr"/>
@@ -3892,17 +3892,17 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Evaluate</t>
+          <t>Objective</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Response to treatment evaluated</t>
+          <t>Exam findings, vitals, labs, screening scores</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>BP controlled on lisinopril</t>
+          <t>'BP 128/82, PHQ-9 = 14, GAD-7 = 9, MSE alert &amp; oriented'</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr"/>
@@ -3910,17 +3910,17 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Assess / Address</t>
+          <t>Assessment</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Diagnosis reviewed and addressed</t>
+          <t>Diagnosis with clinical reasoning</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>DM Type 2 with neuropathy — ongoing</t>
+          <t>'MDD moderate (F32.1) — partial response; GAD (F41.1) stable'</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr"/>
@@ -3928,17 +3928,17 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Treat</t>
+          <t>Plan</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Treatment plan documented</t>
+          <t>Treatment plan documented in full</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Continue metformin 1000 mg BID; recheck A1c 3 mo</t>
+          <t>'Continue escitalopram 10 mg; CBT weekly; recheck PHQ-9 in 4 wk'</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr"/>

--- a/docs/Clinical_Documentation_Audit_Simple.xlsx
+++ b/docs/Clinical_Documentation_Audit_Simple.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Audit Checklist" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Audit Log" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Quick Reference" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Quarterly Report" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -131,8 +132,32 @@
       <color rgb="00FFFFFF"/>
       <sz val="20"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="22"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -187,6 +212,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="000B5555"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F7FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -298,7 +328,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -416,6 +446,28 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -520,6 +572,447 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="11"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Charts by Performance Band</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Quarterly Report'!C11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Quarterly Report'!$B$12:$B$15</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Quarterly Report'!$C$12:$C$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Count</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Charts by Category</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Quarterly Report'!F11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Quarterly Report'!$E$12:$E$16</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Quarterly Report'!$F$12:$F$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showPercent val="1"/>
+        </dLbls>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Monthly Compliance % Trend</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Quarterly Report'!J11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Quarterly Report'!$H$12:$H$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Quarterly Report'!$J$12:$J$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Avg Compliance %</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Charts Audited per Month</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Quarterly Report'!I11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Quarterly Report'!$H$12:$H$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Quarterly Report'!$I$12:$I$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -863,7 +1356,7 @@
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="27" t="inlineStr">
         <is>
-          <t>MRN (masked):</t>
+          <t>Claim Number:</t>
         </is>
       </c>
       <c r="B5" s="4" t="n"/>
@@ -1586,7 +2079,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>MRN (masked)</t>
+          <t>Claim Number</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -4570,4 +5063,340 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00B45309"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Quarterly Audit Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>Pick a quarter &amp; year — metrics and charts recalculate from the Audit Log automatically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="10" customHeight="1"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Quarter:</t>
+        </is>
+      </c>
+      <c r="C4" s="41" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Year:</t>
+        </is>
+      </c>
+      <c r="E4" s="41" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H4" s="42" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="I4" s="9">
+        <f>CHOOSE(MATCH($C$4,{"Q1","Q2","Q3","Q4"},0),"Jan – Mar","Apr – Jun","Jul – Sep","Oct – Dec")</f>
+        <v/>
+      </c>
+      <c r="J4" s="43">
+        <f>$E$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="44" t="inlineStr">
+        <is>
+          <t>Charts Audited</t>
+        </is>
+      </c>
+      <c r="C6" s="45" t="n"/>
+      <c r="D6" s="44" t="inlineStr">
+        <is>
+          <t>Avg Compliance %</t>
+        </is>
+      </c>
+      <c r="E6" s="45" t="n"/>
+      <c r="F6" s="44" t="inlineStr">
+        <is>
+          <t>Meeting Expectations (≥90%)</t>
+        </is>
+      </c>
+      <c r="G6" s="45" t="n"/>
+      <c r="H6" s="44" t="inlineStr">
+        <is>
+          <t>Corrective Required (&lt;80%)</t>
+        </is>
+      </c>
+      <c r="I6" s="45" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="B7" s="46">
+        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*1)</f>
+        <v/>
+      </c>
+      <c r="D7" s="47">
+        <f>IFERROR(SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="46">
+        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&gt;=0.9))</f>
+        <v/>
+      </c>
+      <c r="H7" s="46">
+        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;0.8)*('Audit Log'!$F$5:$F$200&lt;&gt;""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="14" t="n"/>
+      <c r="G8" s="14" t="n"/>
+      <c r="H8" s="14" t="n"/>
+      <c r="I8" s="14" t="n"/>
+    </row>
+    <row r="9" ht="8" customHeight="1"/>
+    <row r="10" ht="26" customHeight="1">
+      <c r="B10" s="48" t="inlineStr">
+        <is>
+          <t>Charts by Performance Band</t>
+        </is>
+      </c>
+      <c r="C10" s="45" t="n"/>
+      <c r="E10" s="48" t="inlineStr">
+        <is>
+          <t>Charts by Category</t>
+        </is>
+      </c>
+      <c r="F10" s="45" t="n"/>
+      <c r="H10" s="48" t="inlineStr">
+        <is>
+          <t>Monthly Trend — Avg Compliance %</t>
+        </is>
+      </c>
+      <c r="I10" s="45" t="n"/>
+      <c r="J10" s="45" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Charts</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Avg %</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+      <c r="C12" s="33">
+        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$G$5:$G$200="Excellent"))</f>
+        <v/>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes</t>
+        </is>
+      </c>
+      <c r="F12" s="33">
+        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$E$5:$E$200="Diabetes"))</f>
+        <v/>
+      </c>
+      <c r="H12" s="9">
+        <f>TEXT(DATE($E$4,(MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3+1,1),"mmm yyyy")</f>
+        <v/>
+      </c>
+      <c r="I12" s="33">
+        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3+1))*(YEAR('Audit Log'!$A$5:$A$200)=$E$4))</f>
+        <v/>
+      </c>
+      <c r="J12" s="37">
+        <f>IFERROR(SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3+1))*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3+1))*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Meets Expectations</t>
+        </is>
+      </c>
+      <c r="C13" s="33">
+        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$G$5:$G$200="Meets Expectations"))</f>
+        <v/>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>Chronic Kidney Disease</t>
+        </is>
+      </c>
+      <c r="F13" s="33">
+        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$E$5:$E$200="Chronic Kidney Disease"))</f>
+        <v/>
+      </c>
+      <c r="H13" s="9">
+        <f>TEXT(DATE($E$4,(MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3+2,1),"mmm yyyy")</f>
+        <v/>
+      </c>
+      <c r="I13" s="33">
+        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3+2))*(YEAR('Audit Log'!$A$5:$A$200)=$E$4))</f>
+        <v/>
+      </c>
+      <c r="J13" s="37">
+        <f>IFERROR(SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3+2))*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3+2))*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Needs Improvement</t>
+        </is>
+      </c>
+      <c r="C14" s="33">
+        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$G$5:$G$200="Needs Improvement"))</f>
+        <v/>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Annual Wellness Visit</t>
+        </is>
+      </c>
+      <c r="F14" s="33">
+        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$E$5:$E$200="Annual Wellness Visit"))</f>
+        <v/>
+      </c>
+      <c r="H14" s="9">
+        <f>TEXT(DATE($E$4,(MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3+3,1),"mmm yyyy")</f>
+        <v/>
+      </c>
+      <c r="I14" s="33">
+        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3+3))*(YEAR('Audit Log'!$A$5:$A$200)=$E$4))</f>
+        <v/>
+      </c>
+      <c r="J14" s="37">
+        <f>IFERROR(SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3+3))*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3+3))*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Corrective Education Required</t>
+        </is>
+      </c>
+      <c r="C15" s="33">
+        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$G$5:$G$200="Corrective Education Required"))</f>
+        <v/>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>High RAF Patient</t>
+        </is>
+      </c>
+      <c r="F15" s="33">
+        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$E$5:$E$200="High RAF Patient"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>Random Selection</t>
+        </is>
+      </c>
+      <c r="F16" s="33">
+        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$E$5:$E$200="Random Selection"))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="D7:E8"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="H7:I8"/>
+    <mergeCell ref="F7:G8"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="C4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Q1,Q2,Q3,Q4"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/docs/Clinical_Documentation_Audit_Simple.xlsx
+++ b/docs/Clinical_Documentation_Audit_Simple.xlsx
@@ -22,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -156,6 +156,12 @@
       <color rgb="000F172A"/>
       <sz val="22"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -220,7 +226,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -324,11 +330,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -466,6 +503,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -1696,7 +1739,7 @@
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  E · CPT II Reporting   (2 items)</t>
+          <t xml:space="preserve">  E · Documentation Supporting Quality Measures   (2 items)</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1751,7 @@
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>Applicable CPT II codes reported for open quality measures</t>
+          <t>Screening / measure results documented with specific values (PHQ-9, GAD-7, BMI, BP, HbA1c) — not just 'screened' or 'normal'</t>
         </is>
       </c>
       <c r="C32" s="32" t="n"/>
@@ -1726,7 +1769,7 @@
       </c>
       <c r="B33" s="10" t="inlineStr">
         <is>
-          <t>Reason modifiers (1P / 2P / 3P / 8P) applied when a measure is not met</t>
+          <t>Follow-up plan documented when a screening is positive or a result is abnormal (positive PHQ-9 → depression plan; elevated BMI → nutrition counseling)</t>
         </is>
       </c>
       <c r="C33" s="32" t="n"/>
@@ -1859,7 +1902,7 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>CPT II Reporting</t>
+          <t>Documentation Supporting Quality Measures</t>
         </is>
       </c>
       <c r="C42" s="36">
@@ -4323,7 +4366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4805,131 +4848,95 @@
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="20" t="inlineStr">
-        <is>
-          <t>CPT II Priority Measures</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="A31" s="49" t="inlineStr">
+        <is>
+          <t>Documentation Needed for CPT II Capture</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="50" t="inlineStr">
+        <is>
+          <t>The billing team assigns the codes below — your job is to document the specific value AND the follow-up action so they can capture the measure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="6" customHeight="1"/>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>Measure</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>CPT II Codes</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>HbA1c control (DM)</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>3044F / 3046F / 3051F / 3052F</t>
-        </is>
-      </c>
-      <c r="C33" s="10" t="inlineStr">
-        <is>
-          <t>Diabetes patients</t>
-        </is>
-      </c>
-      <c r="D33" s="10" t="inlineStr">
-        <is>
-          <t>Report per most recent A1c</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>BP control (HTN)</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>3074F / 3075F / 3077F / 3078F</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>Hypertension patients</t>
-        </is>
-      </c>
-      <c r="D34" s="10" t="inlineStr">
-        <is>
-          <t>Document sys &amp; dias</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>BMI screening + follow-up</t>
+          <t>HbA1c control (DM)</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>G8417 / G8418 / G8420</t>
+          <t>3044F / 3046F / 3051F / 3052F</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>All adult visits</t>
+          <t>Diabetes patients</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>Include intervention if abnormal</t>
+          <t>Report per most recent A1c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>Tobacco screening + cessation</t>
+          <t>BP control (HTN)</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>1036F / 4004F</t>
+          <t>3074F / 3075F / 3077F / 3078F</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>All adult visits</t>
+          <t>Hypertension patients</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>Screening + counseling combo</t>
+          <t>Document sys &amp; dias</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Depression screening + plan</t>
+          <t>BMI screening + follow-up</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>G8431 / G8510</t>
+          <t>G8417 / G8418 / G8420</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
@@ -4939,127 +4946,172 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>PHQ-2 / PHQ-9 documented</t>
+          <t>Include intervention if abnormal</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>Statin therapy for CVD</t>
+          <t>Tobacco screening + cessation</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>0521F / 4013F</t>
+          <t>1036F / 4004F</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>ASCVD / DM / LDL ≥190</t>
+          <t>All adult visits</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>On statin, refused, or contraindicated</t>
+          <t>Screening + counseling combo</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Diabetic eye exam</t>
+          <t>Depression screening + plan</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>2022F / 2024F / 2026F</t>
+          <t>G8431 / G8510</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Diabetes patients</t>
+          <t>All adult visits</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Negative or positive result</t>
+          <t>PHQ-2 / PHQ-9 documented</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>Nephropathy screening</t>
+          <t>Statin therapy for CVD</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>3060F / 3061F / 3062F</t>
+          <t>0521F / 4013F</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Diabetes patients</t>
+          <t>ASCVD / DM / LDL ≥190</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Urine albumin / on ACE-ARB</t>
+          <t>On statin, refused, or contraindicated</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Med rec post-discharge</t>
+          <t>Diabetic eye exam</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>1111F</t>
+          <t>2022F / 2024F / 2026F</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>Discharge in last 30 d</t>
+          <t>Diabetes patients</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Reconciliation documented</t>
+          <t>Negative or positive result</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
+          <t>Nephropathy screening</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>3060F / 3061F / 3062F</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes patients</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Urine albumin / on ACE-ARB</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Med rec post-discharge</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>1111F</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>Discharge in last 30 d</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Reconciliation documented</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
           <t>Fall risk assessment</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>1101F</t>
         </is>
       </c>
-      <c r="C42" s="10" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>Age 65+</t>
         </is>
       </c>
-      <c r="D42" s="10" t="inlineStr">
+      <c r="D44" s="10" t="inlineStr">
         <is>
           <t>Yearly for MA populations</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Clinical_Documentation_Audit_Simple.xlsx
+++ b/docs/Clinical_Documentation_Audit_Simple.xlsx
@@ -19,8 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -163,7 +164,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -223,6 +224,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F5F7FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -365,7 +371,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -511,6 +517,25 @@
     <xf numFmtId="0" fontId="23" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -704,9 +729,11 @@
             </rich>
           </tx>
         </title>
+        <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <majorUnit val="1"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -761,6 +788,7 @@
           </val>
         </ser>
         <dLbls>
+          <showCatName val="0"/>
           <showPercent val="1"/>
         </dLbls>
         <firstSliceAng val="0"/>
@@ -810,7 +838,8 @@
             </a:ln>
           </spPr>
           <marker>
-            <symbol val="none"/>
+            <symbol val="circle"/>
+            <size val="8"/>
             <spPr>
               <a:ln>
                 <a:prstDash val="solid"/>
@@ -849,6 +878,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="1"/>
+          <min val="0.6"/>
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
@@ -873,9 +904,6 @@
         <crossAx val="10"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -954,9 +982,11 @@
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
+        <numFmt formatCode="0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <majorUnit val="1"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -974,7 +1004,7 @@
       <row>17</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5760000" cy="3240000"/>
+    <ext cx="5400000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -991,12 +1021,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>7</col>
       <colOff>0</colOff>
       <row>17</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4320000" cy="3240000"/>
+    <ext cx="4320000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1015,10 +1045,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5760000" cy="3240000"/>
+    <ext cx="5400000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -1035,12 +1065,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>7</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4320000" cy="3240000"/>
+    <ext cx="4320000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -1409,6 +1439,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n"/>
+      <c r="E5" s="51" t="n"/>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="27" t="inlineStr">
@@ -1423,6 +1454,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n"/>
+      <c r="E6" s="52" t="n"/>
     </row>
     <row r="7" ht="12" customHeight="1"/>
     <row r="8" ht="32" customHeight="1">
@@ -1933,6 +1965,8 @@
           <t xml:space="preserve">  PERFORMANCE BAND</t>
         </is>
       </c>
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" s="54" t="n"/>
       <c r="D45" s="18">
         <f>IF(D44="","",IF(D44&gt;=0.95,"Excellent",IF(D44&gt;=0.90,"Meets Expectations",IF(D44&gt;=0.80,"Needs Improvement","Corrective Education Required"))))</f>
         <v/>
@@ -2157,114 +2191,414 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n"/>
-      <c r="B5" s="10" t="n"/>
-      <c r="C5" s="10" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="9" t="n"/>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="9" t="n"/>
-      <c r="H5" s="10" t="n"/>
-      <c r="I5" s="10" t="n"/>
+      <c r="A5" s="55" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B5" s="56" t="inlineStr">
+        <is>
+          <t>Dr. Rivera</t>
+        </is>
+      </c>
+      <c r="C5" s="56" t="inlineStr">
+        <is>
+          <t>CLM-2026-001</t>
+        </is>
+      </c>
+      <c r="D5" s="55" t="n">
+        <v>46201</v>
+      </c>
+      <c r="E5" s="57" t="inlineStr">
+        <is>
+          <t>Diabetes</t>
+        </is>
+      </c>
+      <c r="F5" s="58" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G5" s="57" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+      <c r="H5" s="56" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I5" s="56" t="inlineStr">
+        <is>
+          <t>Sample row · delete when starting real audits</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n"/>
-      <c r="B6" s="10" t="n"/>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="9" t="n"/>
-      <c r="E6" s="9" t="n"/>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="9" t="n"/>
-      <c r="H6" s="10" t="n"/>
-      <c r="I6" s="10" t="n"/>
+      <c r="A6" s="55" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B6" s="56" t="inlineStr">
+        <is>
+          <t>Dr. Rivera</t>
+        </is>
+      </c>
+      <c r="C6" s="56" t="inlineStr">
+        <is>
+          <t>CLM-2026-002</t>
+        </is>
+      </c>
+      <c r="D6" s="55" t="n">
+        <v>46203</v>
+      </c>
+      <c r="E6" s="57" t="inlineStr">
+        <is>
+          <t>Chronic Kidney Disease</t>
+        </is>
+      </c>
+      <c r="F6" s="58" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G6" s="57" t="inlineStr">
+        <is>
+          <t>Meets Expectations</t>
+        </is>
+      </c>
+      <c r="H6" s="56" t="inlineStr">
+        <is>
+          <t>N18 unspecified</t>
+        </is>
+      </c>
+      <c r="I6" s="56" t="inlineStr">
+        <is>
+          <t>Sample row · delete when starting real audits</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="n"/>
-      <c r="B7" s="10" t="n"/>
-      <c r="C7" s="10" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="9" t="n"/>
-      <c r="H7" s="10" t="n"/>
-      <c r="I7" s="10" t="n"/>
+      <c r="A7" s="55" t="n">
+        <v>46215</v>
+      </c>
+      <c r="B7" s="56" t="inlineStr">
+        <is>
+          <t>Dr. Colón</t>
+        </is>
+      </c>
+      <c r="C7" s="56" t="inlineStr">
+        <is>
+          <t>CLM-2026-003</t>
+        </is>
+      </c>
+      <c r="D7" s="55" t="n">
+        <v>46208</v>
+      </c>
+      <c r="E7" s="57" t="inlineStr">
+        <is>
+          <t>Diabetes</t>
+        </is>
+      </c>
+      <c r="F7" s="58" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G7" s="57" t="inlineStr">
+        <is>
+          <t>Needs Improvement</t>
+        </is>
+      </c>
+      <c r="H7" s="56" t="inlineStr">
+        <is>
+          <t>E11.9 use, missing MEAT</t>
+        </is>
+      </c>
+      <c r="I7" s="56" t="inlineStr">
+        <is>
+          <t>Sample row · delete when starting real audits</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="n"/>
-      <c r="B8" s="10" t="n"/>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="12" t="n"/>
-      <c r="G8" s="9" t="n"/>
-      <c r="H8" s="10" t="n"/>
-      <c r="I8" s="10" t="n"/>
+      <c r="A8" s="55" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B8" s="56" t="inlineStr">
+        <is>
+          <t>Dr. Colón</t>
+        </is>
+      </c>
+      <c r="C8" s="56" t="inlineStr">
+        <is>
+          <t>CLM-2026-004</t>
+        </is>
+      </c>
+      <c r="D8" s="55" t="n">
+        <v>46212</v>
+      </c>
+      <c r="E8" s="57" t="inlineStr">
+        <is>
+          <t>Annual Wellness Visit</t>
+        </is>
+      </c>
+      <c r="F8" s="58" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G8" s="57" t="inlineStr">
+        <is>
+          <t>Meets Expectations</t>
+        </is>
+      </c>
+      <c r="H8" s="56" t="inlineStr">
+        <is>
+          <t>PHQ-9 score not documented</t>
+        </is>
+      </c>
+      <c r="I8" s="56" t="inlineStr">
+        <is>
+          <t>Sample row · delete when starting real audits</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n"/>
-      <c r="B9" s="10" t="n"/>
-      <c r="C9" s="10" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="9" t="n"/>
-      <c r="H9" s="10" t="n"/>
-      <c r="I9" s="10" t="n"/>
+      <c r="A9" s="55" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B9" s="56" t="inlineStr">
+        <is>
+          <t>Dr. Rivera</t>
+        </is>
+      </c>
+      <c r="C9" s="56" t="inlineStr">
+        <is>
+          <t>CLM-2026-005</t>
+        </is>
+      </c>
+      <c r="D9" s="55" t="n">
+        <v>46233</v>
+      </c>
+      <c r="E9" s="57" t="inlineStr">
+        <is>
+          <t>High RAF Patient</t>
+        </is>
+      </c>
+      <c r="F9" s="58" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G9" s="57" t="inlineStr">
+        <is>
+          <t>Corrective Education Required</t>
+        </is>
+      </c>
+      <c r="H9" s="56" t="inlineStr">
+        <is>
+          <t>HCC recapture missed</t>
+        </is>
+      </c>
+      <c r="I9" s="56" t="inlineStr">
+        <is>
+          <t>Sample row · delete when starting real audits</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n"/>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="9" t="n"/>
-      <c r="H10" s="10" t="n"/>
-      <c r="I10" s="10" t="n"/>
+      <c r="A10" s="55" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B10" s="56" t="inlineStr">
+        <is>
+          <t>Dr. Colón</t>
+        </is>
+      </c>
+      <c r="C10" s="56" t="inlineStr">
+        <is>
+          <t>CLM-2026-006</t>
+        </is>
+      </c>
+      <c r="D10" s="55" t="n">
+        <v>46238</v>
+      </c>
+      <c r="E10" s="57" t="inlineStr">
+        <is>
+          <t>Diabetes</t>
+        </is>
+      </c>
+      <c r="F10" s="58" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G10" s="57" t="inlineStr">
+        <is>
+          <t>Meets Expectations</t>
+        </is>
+      </c>
+      <c r="H10" s="56" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I10" s="56" t="inlineStr">
+        <is>
+          <t>Sample row · delete when starting real audits</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n"/>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="9" t="n"/>
-      <c r="H11" s="10" t="n"/>
-      <c r="I11" s="10" t="n"/>
+      <c r="A11" s="55" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B11" s="56" t="inlineStr">
+        <is>
+          <t>Dr. Rivera</t>
+        </is>
+      </c>
+      <c r="C11" s="56" t="inlineStr">
+        <is>
+          <t>CLM-2026-007</t>
+        </is>
+      </c>
+      <c r="D11" s="55" t="n">
+        <v>46249</v>
+      </c>
+      <c r="E11" s="57" t="inlineStr">
+        <is>
+          <t>Chronic Kidney Disease</t>
+        </is>
+      </c>
+      <c r="F11" s="58" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G11" s="57" t="inlineStr">
+        <is>
+          <t>Needs Improvement</t>
+        </is>
+      </c>
+      <c r="H11" s="56" t="inlineStr">
+        <is>
+          <t>CKD stage unspecified</t>
+        </is>
+      </c>
+      <c r="I11" s="56" t="inlineStr">
+        <is>
+          <t>Sample row · delete when starting real audits</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n"/>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="9" t="n"/>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="10" t="n"/>
+      <c r="A12" s="55" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B12" s="56" t="inlineStr">
+        <is>
+          <t>Dr. Rivera</t>
+        </is>
+      </c>
+      <c r="C12" s="56" t="inlineStr">
+        <is>
+          <t>CLM-2026-008</t>
+        </is>
+      </c>
+      <c r="D12" s="55" t="n">
+        <v>46262</v>
+      </c>
+      <c r="E12" s="57" t="inlineStr">
+        <is>
+          <t>Annual Wellness Visit</t>
+        </is>
+      </c>
+      <c r="F12" s="58" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G12" s="57" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+      <c r="H12" s="56" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I12" s="56" t="inlineStr">
+        <is>
+          <t>Sample row · delete when starting real audits</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="n"/>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="9" t="n"/>
-      <c r="H13" s="10" t="n"/>
-      <c r="I13" s="10" t="n"/>
+      <c r="A13" s="55" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B13" s="56" t="inlineStr">
+        <is>
+          <t>Dr. Colón</t>
+        </is>
+      </c>
+      <c r="C13" s="56" t="inlineStr">
+        <is>
+          <t>CLM-2026-009</t>
+        </is>
+      </c>
+      <c r="D13" s="55" t="n">
+        <v>46269</v>
+      </c>
+      <c r="E13" s="57" t="inlineStr">
+        <is>
+          <t>Random Selection</t>
+        </is>
+      </c>
+      <c r="F13" s="58" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G13" s="57" t="inlineStr">
+        <is>
+          <t>Needs Improvement</t>
+        </is>
+      </c>
+      <c r="H13" s="56" t="inlineStr">
+        <is>
+          <t>Med rec not documented</t>
+        </is>
+      </c>
+      <c r="I13" s="56" t="inlineStr">
+        <is>
+          <t>Sample row · delete when starting real audits</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="n"/>
-      <c r="B14" s="10" t="n"/>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="9" t="n"/>
-      <c r="H14" s="10" t="n"/>
-      <c r="I14" s="10" t="n"/>
+      <c r="A14" s="55" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B14" s="56" t="inlineStr">
+        <is>
+          <t>Dr. Colón</t>
+        </is>
+      </c>
+      <c r="C14" s="56" t="inlineStr">
+        <is>
+          <t>CLM-2026-010</t>
+        </is>
+      </c>
+      <c r="D14" s="55" t="n">
+        <v>46276</v>
+      </c>
+      <c r="E14" s="57" t="inlineStr">
+        <is>
+          <t>High RAF Patient</t>
+        </is>
+      </c>
+      <c r="F14" s="58" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="G14" s="57" t="inlineStr">
+        <is>
+          <t>Meets Expectations</t>
+        </is>
+      </c>
+      <c r="H14" s="56" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I14" s="56" t="inlineStr">
+        <is>
+          <t>Sample row · delete when starting real audits</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n"/>
@@ -4860,6 +5194,9 @@
           <t>The billing team assigns the codes below — your job is to document the specific value AND the follow-up action so they can capture the measure.</t>
         </is>
       </c>
+      <c r="B32" s="53" t="n"/>
+      <c r="C32" s="53" t="n"/>
+      <c r="D32" s="54" t="n"/>
     </row>
     <row r="33" ht="6" customHeight="1"/>
     <row r="34">
@@ -5129,10 +5466,10 @@
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
@@ -5193,53 +5530,57 @@
           <t>Charts Audited</t>
         </is>
       </c>
-      <c r="C6" s="45" t="n"/>
+      <c r="C6" s="54" t="n"/>
       <c r="D6" s="44" t="inlineStr">
         <is>
           <t>Avg Compliance %</t>
         </is>
       </c>
-      <c r="E6" s="45" t="n"/>
+      <c r="E6" s="54" t="n"/>
       <c r="F6" s="44" t="inlineStr">
         <is>
           <t>Meeting Expectations (≥90%)</t>
         </is>
       </c>
-      <c r="G6" s="45" t="n"/>
+      <c r="G6" s="54" t="n"/>
       <c r="H6" s="44" t="inlineStr">
         <is>
           <t>Corrective Required (&lt;80%)</t>
         </is>
       </c>
-      <c r="I6" s="45" t="n"/>
+      <c r="I6" s="54" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="B7" s="46">
         <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*1)</f>
         <v/>
       </c>
+      <c r="C7" s="59" t="n"/>
       <c r="D7" s="47">
         <f>IFERROR(SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),"")</f>
         <v/>
       </c>
+      <c r="E7" s="59" t="n"/>
       <c r="F7" s="46">
         <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&gt;=0.9))</f>
         <v/>
       </c>
+      <c r="G7" s="59" t="n"/>
       <c r="H7" s="46">
         <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;0.8)*('Audit Log'!$F$5:$F$200&lt;&gt;""))</f>
         <v/>
       </c>
+      <c r="I7" s="59" t="n"/>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="14" t="n"/>
-      <c r="G8" s="14" t="n"/>
-      <c r="H8" s="14" t="n"/>
-      <c r="I8" s="14" t="n"/>
+      <c r="B8" s="60" t="n"/>
+      <c r="C8" s="61" t="n"/>
+      <c r="D8" s="60" t="n"/>
+      <c r="E8" s="61" t="n"/>
+      <c r="F8" s="60" t="n"/>
+      <c r="G8" s="61" t="n"/>
+      <c r="H8" s="60" t="n"/>
+      <c r="I8" s="61" t="n"/>
     </row>
     <row r="9" ht="8" customHeight="1"/>
     <row r="10" ht="26" customHeight="1">
@@ -5248,20 +5589,20 @@
           <t>Charts by Performance Band</t>
         </is>
       </c>
-      <c r="C10" s="45" t="n"/>
+      <c r="C10" s="54" t="n"/>
       <c r="E10" s="48" t="inlineStr">
         <is>
           <t>Charts by Category</t>
         </is>
       </c>
-      <c r="F10" s="45" t="n"/>
+      <c r="F10" s="54" t="n"/>
       <c r="H10" s="48" t="inlineStr">
         <is>
           <t>Monthly Trend — Avg Compliance %</t>
         </is>
       </c>
-      <c r="I10" s="45" t="n"/>
-      <c r="J10" s="45" t="n"/>
+      <c r="I10" s="53" t="n"/>
+      <c r="J10" s="54" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="7" t="inlineStr">
@@ -5427,6 +5768,43 @@
         <v/>
       </c>
     </row>
+    <row r="18" ht="18" customHeight="1"/>
+    <row r="19" ht="18" customHeight="1"/>
+    <row r="20" ht="18" customHeight="1"/>
+    <row r="21" ht="18" customHeight="1"/>
+    <row r="22" ht="18" customHeight="1"/>
+    <row r="23" ht="18" customHeight="1"/>
+    <row r="24" ht="18" customHeight="1"/>
+    <row r="25" ht="18" customHeight="1"/>
+    <row r="26" ht="18" customHeight="1"/>
+    <row r="27" ht="18" customHeight="1"/>
+    <row r="28" ht="18" customHeight="1"/>
+    <row r="29" ht="18" customHeight="1"/>
+    <row r="30" ht="18" customHeight="1"/>
+    <row r="31" ht="18" customHeight="1"/>
+    <row r="32" ht="18" customHeight="1"/>
+    <row r="33" ht="18" customHeight="1"/>
+    <row r="34" ht="18" customHeight="1"/>
+    <row r="35" ht="18" customHeight="1"/>
+    <row r="36" ht="18" customHeight="1"/>
+    <row r="37" ht="18" customHeight="1"/>
+    <row r="38" ht="18" customHeight="1"/>
+    <row r="39" ht="18" customHeight="1"/>
+    <row r="40" ht="18" customHeight="1"/>
+    <row r="41" ht="18" customHeight="1"/>
+    <row r="42" ht="18" customHeight="1"/>
+    <row r="43" ht="18" customHeight="1"/>
+    <row r="44" ht="18" customHeight="1"/>
+    <row r="45" ht="18" customHeight="1"/>
+    <row r="46" ht="18" customHeight="1"/>
+    <row r="47" ht="18" customHeight="1"/>
+    <row r="48" ht="18" customHeight="1"/>
+    <row r="49" ht="18" customHeight="1"/>
+    <row r="50" ht="18" customHeight="1"/>
+    <row r="51" ht="18" customHeight="1"/>
+    <row r="52" ht="18" customHeight="1"/>
+    <row r="53" ht="18" customHeight="1"/>
+    <row r="54" ht="18" customHeight="1"/>
   </sheetData>
   <mergeCells count="13">
     <mergeCell ref="D6:E6"/>

--- a/docs/Clinical_Documentation_Audit_Simple.xlsx
+++ b/docs/Clinical_Documentation_Audit_Simple.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -161,6 +161,13 @@
       <name val="Calibri"/>
       <i val="1"/>
       <color rgb="000F172A"/>
+      <sz val="10"/>
+    </font>
+    <font/>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000B5555"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -371,7 +378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -536,6 +543,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -644,7 +667,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="11"/>
   <chart>
     <title>
       <tx>
@@ -655,167 +677,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Charts by Performance Band</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Quarterly Report'!C11</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Quarterly Report'!$B$12:$B$15</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Quarterly Report'!$C$12:$C$15</f>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showVal val="1"/>
-        </dLbls>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Count</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-        <majorUnit val="1"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Charts by Category</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <pieChart>
-        <varyColors val="1"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Quarterly Report'!F11</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Quarterly Report'!$E$12:$E$16</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Quarterly Report'!$F$12:$F$16</f>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showCatName val="0"/>
-          <showPercent val="1"/>
-        </dLbls>
-        <firstSliceAng val="0"/>
-      </pieChart>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Monthly Compliance % Trend</a:t>
+              <a:t>Provider Compliance % Progression</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -829,7 +691,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Quarterly Report'!J11</f>
+              <f>'Quarterly Report'!B12</f>
             </strRef>
           </tx>
           <spPr>
@@ -839,7 +701,7 @@
           </spPr>
           <marker>
             <symbol val="circle"/>
-            <size val="8"/>
+            <size val="7"/>
             <spPr>
               <a:ln>
                 <a:prstDash val="solid"/>
@@ -848,17 +710,182 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Quarterly Report'!$H$12:$H$14</f>
+              <f>'Quarterly Report'!$C$12:$N$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Quarterly Report'!$J$12:$J$14</f>
+              <f>'Quarterly Report'!$C$12:$N$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Quarterly Report'!B13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Quarterly Report'!$C$12:$N$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Quarterly Report'!$C$13:$N$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Quarterly Report'!B14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Quarterly Report'!$C$12:$N$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Quarterly Report'!$C$14:$N$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Quarterly Report'!B15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Quarterly Report'!$C$12:$N$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Quarterly Report'!$C$15:$N$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>'Quarterly Report'!B16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Quarterly Report'!$C$12:$N$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Quarterly Report'!$C$16:$N$16</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="5"/>
+          <order val="5"/>
+          <tx>
+            <strRef>
+              <f>'Quarterly Report'!B17</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Quarterly Report'!$C$12:$N$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Quarterly Report'!$C$17:$N$17</f>
             </numRef>
           </val>
         </ser>
         <dLbls>
-          <showVal val="1"/>
+          <showVal val="0"/>
         </dLbls>
         <axId val="10"/>
         <axId val="100"/>
@@ -892,7 +919,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Avg Compliance %</a:t>
+                  <a:t>Compliance %</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -902,93 +929,12 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <majorUnit val="0.05"/>
       </valAx>
     </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Charts Audited per Month</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Quarterly Report'!I11</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Quarterly Report'!$H$12:$H$14</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Quarterly Report'!$I$12:$I$14</f>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showVal val="1"/>
-        </dLbls>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <numFmt formatCode="0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-        <majorUnit val="1"/>
-      </valAx>
-    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -1001,10 +947,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="3060000"/>
+    <ext cx="10080000" cy="4320000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1014,72 +960,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4320000" cy="3060000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>35</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="5400000" cy="3060000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="3" name="Chart 3"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>35</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4320000" cy="3060000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="4" name="Chart 4"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -5461,19 +5341,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="3" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -5582,189 +5467,375 @@
       <c r="H8" s="60" t="n"/>
       <c r="I8" s="61" t="n"/>
     </row>
-    <row r="9" ht="8" customHeight="1"/>
-    <row r="10" ht="26" customHeight="1">
-      <c r="B10" s="48" t="inlineStr">
-        <is>
-          <t>Charts by Performance Band</t>
-        </is>
-      </c>
-      <c r="C10" s="54" t="n"/>
-      <c r="E10" s="48" t="inlineStr">
-        <is>
-          <t>Charts by Category</t>
-        </is>
-      </c>
-      <c r="F10" s="54" t="n"/>
-      <c r="H10" s="48" t="inlineStr">
-        <is>
-          <t>Monthly Trend — Avg Compliance %</t>
-        </is>
-      </c>
-      <c r="I10" s="53" t="n"/>
-      <c r="J10" s="54" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Band</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>Charts</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>Avg %</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Excellent</t>
-        </is>
-      </c>
-      <c r="C12" s="33">
-        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$G$5:$G$200="Excellent"))</f>
-        <v/>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>Diabetes</t>
-        </is>
-      </c>
-      <c r="F12" s="33">
-        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$E$5:$E$200="Diabetes"))</f>
-        <v/>
-      </c>
-      <c r="H12" s="9">
-        <f>TEXT(DATE($E$4,(MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3+1,1),"mmm yyyy")</f>
-        <v/>
-      </c>
-      <c r="I12" s="33">
-        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3+1))*(YEAR('Audit Log'!$A$5:$A$200)=$E$4))</f>
-        <v/>
-      </c>
-      <c r="J12" s="37">
-        <f>IFERROR(SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3+1))*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3+1))*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Meets Expectations</t>
-        </is>
-      </c>
-      <c r="C13" s="33">
-        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$G$5:$G$200="Meets Expectations"))</f>
-        <v/>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>Chronic Kidney Disease</t>
-        </is>
-      </c>
-      <c r="F13" s="33">
-        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$E$5:$E$200="Chronic Kidney Disease"))</f>
-        <v/>
-      </c>
-      <c r="H13" s="9">
-        <f>TEXT(DATE($E$4,(MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3+2,1),"mmm yyyy")</f>
-        <v/>
-      </c>
-      <c r="I13" s="33">
-        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3+2))*(YEAR('Audit Log'!$A$5:$A$200)=$E$4))</f>
-        <v/>
-      </c>
-      <c r="J13" s="37">
-        <f>IFERROR(SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3+2))*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3+2))*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Needs Improvement</t>
-        </is>
-      </c>
-      <c r="C14" s="33">
-        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$G$5:$G$200="Needs Improvement"))</f>
-        <v/>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>Annual Wellness Visit</t>
-        </is>
-      </c>
-      <c r="F14" s="33">
-        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$E$5:$E$200="Annual Wellness Visit"))</f>
-        <v/>
-      </c>
-      <c r="H14" s="9">
-        <f>TEXT(DATE($E$4,(MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3+3,1),"mmm yyyy")</f>
-        <v/>
-      </c>
-      <c r="I14" s="33">
-        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3+3))*(YEAR('Audit Log'!$A$5:$A$200)=$E$4))</f>
-        <v/>
-      </c>
-      <c r="J14" s="37">
-        <f>IFERROR(SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3+3))*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3+3))*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>Corrective Education Required</t>
-        </is>
-      </c>
-      <c r="C15" s="33">
-        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$G$5:$G$200="Corrective Education Required"))</f>
-        <v/>
-      </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>High RAF Patient</t>
-        </is>
-      </c>
-      <c r="F15" s="33">
-        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$E$5:$E$200="High RAF Patient"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>Random Selection</t>
-        </is>
-      </c>
-      <c r="F16" s="33">
-        <f>SUMPRODUCT(('Audit Log'!$A$5:$A$200&lt;&gt;"")*(MONTH('Audit Log'!$A$5:$A$200)&gt;=((MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)-1)*3)+1)*(MONTH('Audit Log'!$A$5:$A$200)&lt;=MATCH($C$4,{"Q1","Q2","Q3","Q4"},0)*3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$E$5:$E$200="Random Selection"))</f>
+    <row r="9" ht="10" customHeight="1">
+      <c r="A9" s="62" t="n"/>
+      <c r="B9" s="62" t="n"/>
+      <c r="C9" s="62" t="n"/>
+      <c r="D9" s="62" t="n"/>
+      <c r="E9" s="62" t="n"/>
+      <c r="F9" s="62" t="n"/>
+      <c r="G9" s="62" t="n"/>
+      <c r="H9" s="62" t="n"/>
+      <c r="I9" s="62" t="n"/>
+      <c r="J9" s="62" t="n"/>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Provider Progression — Monthly Compliance % by Provider</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="64" t="inlineStr">
+        <is>
+          <t>Type each provider's name in column B — the row fills in automatically from the Audit Log for the year picked above. Rising lines = improvement · falling lines = decline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="6" t="inlineStr"/>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Provider</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Jan</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Feb</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Apr</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>May</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Jun</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Jul</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Aug</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>Oct</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>Nov</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="65" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="66" t="inlineStr">
+        <is>
+          <t>Dr. Rivera</t>
+        </is>
+      </c>
+      <c r="C13" s="67">
+        <f>IF($B13="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B13)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=1)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B13)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=1)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="D13" s="67">
+        <f>IF($B13="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B13)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=2)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B13)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=2)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="E13" s="67">
+        <f>IF($B13="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B13)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B13)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="F13" s="67">
+        <f>IF($B13="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B13)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=4)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B13)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=4)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="G13" s="67">
+        <f>IF($B13="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B13)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=5)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B13)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=5)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="H13" s="67">
+        <f>IF($B13="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B13)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=6)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B13)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=6)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="I13" s="67">
+        <f>IF($B13="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B13)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=7)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B13)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=7)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="J13" s="67">
+        <f>IF($B13="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B13)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=8)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B13)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=8)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="K13" s="67">
+        <f>IF($B13="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B13)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=9)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B13)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=9)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="L13" s="67">
+        <f>IF($B13="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B13)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=10)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B13)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=10)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="M13" s="67">
+        <f>IF($B13="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B13)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=11)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B13)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=11)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="N13" s="67">
+        <f>IF($B13="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B13)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=12)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B13)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=12)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="65" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="66" t="inlineStr">
+        <is>
+          <t>Dr. Colón</t>
+        </is>
+      </c>
+      <c r="C14" s="67">
+        <f>IF($B14="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B14)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=1)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B14)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=1)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="D14" s="67">
+        <f>IF($B14="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B14)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=2)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B14)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=2)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="E14" s="67">
+        <f>IF($B14="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B14)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B14)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="F14" s="67">
+        <f>IF($B14="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B14)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=4)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B14)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=4)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="G14" s="67">
+        <f>IF($B14="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B14)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=5)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B14)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=5)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="H14" s="67">
+        <f>IF($B14="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B14)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=6)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B14)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=6)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="I14" s="67">
+        <f>IF($B14="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B14)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=7)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B14)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=7)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="J14" s="67">
+        <f>IF($B14="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B14)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=8)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B14)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=8)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="K14" s="67">
+        <f>IF($B14="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B14)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=9)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B14)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=9)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="L14" s="67">
+        <f>IF($B14="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B14)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=10)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B14)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=10)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="M14" s="67">
+        <f>IF($B14="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B14)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=11)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B14)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=11)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="N14" s="67">
+        <f>IF($B14="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B14)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=12)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B14)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=12)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="65" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="66" t="n"/>
+      <c r="C15" s="67">
+        <f>IF($B15="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B15)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=1)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B15)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=1)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="D15" s="67">
+        <f>IF($B15="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B15)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=2)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B15)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=2)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="E15" s="67">
+        <f>IF($B15="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B15)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B15)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="F15" s="67">
+        <f>IF($B15="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B15)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=4)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B15)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=4)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="G15" s="67">
+        <f>IF($B15="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B15)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=5)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B15)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=5)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="H15" s="67">
+        <f>IF($B15="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B15)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=6)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B15)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=6)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="I15" s="67">
+        <f>IF($B15="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B15)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=7)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B15)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=7)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="J15" s="67">
+        <f>IF($B15="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B15)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=8)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B15)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=8)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="K15" s="67">
+        <f>IF($B15="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B15)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=9)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B15)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=9)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="L15" s="67">
+        <f>IF($B15="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B15)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=10)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B15)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=10)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="M15" s="67">
+        <f>IF($B15="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B15)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=11)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B15)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=11)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="N15" s="67">
+        <f>IF($B15="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B15)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=12)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B15)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=12)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="65" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="66" t="n"/>
+      <c r="C16" s="67">
+        <f>IF($B16="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B16)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=1)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B16)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=1)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="D16" s="67">
+        <f>IF($B16="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B16)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=2)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B16)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=2)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="E16" s="67">
+        <f>IF($B16="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B16)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B16)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="F16" s="67">
+        <f>IF($B16="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B16)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=4)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B16)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=4)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="G16" s="67">
+        <f>IF($B16="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B16)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=5)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B16)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=5)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="H16" s="67">
+        <f>IF($B16="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B16)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=6)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B16)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=6)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="I16" s="67">
+        <f>IF($B16="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B16)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=7)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B16)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=7)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="J16" s="67">
+        <f>IF($B16="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B16)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=8)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B16)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=8)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="K16" s="67">
+        <f>IF($B16="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B16)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=9)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B16)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=9)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="L16" s="67">
+        <f>IF($B16="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B16)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=10)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B16)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=10)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="M16" s="67">
+        <f>IF($B16="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B16)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=11)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B16)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=11)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="N16" s="67">
+        <f>IF($B16="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B16)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=12)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B16)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=12)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="65" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="66" t="n"/>
+      <c r="C17" s="67">
+        <f>IF($B17="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B17)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=1)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B17)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=1)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="D17" s="67">
+        <f>IF($B17="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B17)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=2)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B17)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=2)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="E17" s="67">
+        <f>IF($B17="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B17)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B17)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=3)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="F17" s="67">
+        <f>IF($B17="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B17)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=4)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B17)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=4)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="G17" s="67">
+        <f>IF($B17="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B17)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=5)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B17)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=5)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="H17" s="67">
+        <f>IF($B17="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B17)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=6)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B17)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=6)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="I17" s="67">
+        <f>IF($B17="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B17)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=7)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B17)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=7)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="J17" s="67">
+        <f>IF($B17="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B17)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=8)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B17)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=8)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="K17" s="67">
+        <f>IF($B17="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B17)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=9)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B17)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=9)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="L17" s="67">
+        <f>IF($B17="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B17)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=10)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B17)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=10)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="M17" s="67">
+        <f>IF($B17="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B17)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=11)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B17)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=11)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
+        <v/>
+      </c>
+      <c r="N17" s="67">
+        <f>IF($B17="","",IFERROR(SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B17)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=12)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*'Audit Log'!$F$5:$F$200)/SUMPRODUCT(('Audit Log'!$B$5:$B$200=$B17)*ISNUMBER('Audit Log'!$A$5:$A$200)*(MONTH('Audit Log'!$A$5:$A$200)=12)*(YEAR('Audit Log'!$A$5:$A$200)=$E$4)*('Audit Log'!$F$5:$F$200&lt;&gt;"")),""))</f>
         <v/>
       </c>
     </row>
@@ -5806,21 +5877,33 @@
     <row r="53" ht="18" customHeight="1"/>
     <row r="54" ht="18" customHeight="1"/>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="12">
     <mergeCell ref="D6:E6"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="H10:J10"/>
     <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A10:N10"/>
     <mergeCell ref="D7:E8"/>
     <mergeCell ref="B7:C8"/>
-    <mergeCell ref="E10:F10"/>
     <mergeCell ref="H7:I8"/>
     <mergeCell ref="F7:G8"/>
-    <mergeCell ref="B10:C10"/>
     <mergeCell ref="F6:G6"/>
+    <mergeCell ref="A11:N11"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
+  <conditionalFormatting sqref="C13:N17">
+    <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="between" dxfId="1">
+      <formula>0.8</formula>
+      <formula>0.8999</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="between" dxfId="2">
+      <formula>0.0001</formula>
+      <formula>0.7999</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="C4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Q1,Q2,Q3,Q4"</formula1>

--- a/docs/Clinical_Documentation_Audit_Simple.xlsx
+++ b/docs/Clinical_Documentation_Audit_Simple.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Audit Checklist" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Audit Log" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Quick Reference" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Quarterly Report" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Checklist" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Batch (10)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Reference" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly Report" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -378,7 +379,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -559,6 +560,45 @@
     <xf numFmtId="164" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -666,13 +706,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -695,7 +735,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -703,7 +743,7 @@
             <symbol val="circle"/>
             <size val="7"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -728,7 +768,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -736,7 +776,7 @@
             <symbol val="circle"/>
             <size val="7"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -761,7 +801,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -769,7 +809,7 @@
             <symbol val="circle"/>
             <size val="7"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -794,7 +834,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -802,7 +842,7 @@
             <symbol val="circle"/>
             <size val="7"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -827,7 +867,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -835,7 +875,7 @@
             <symbol val="circle"/>
             <size val="7"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -860,7 +900,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -868,7 +908,7 @@
             <symbol val="circle"/>
             <size val="7"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -913,8 +953,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -942,7 +982,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
@@ -957,9 +997,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1991,6 +2031,1166 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00B45309"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="68" t="inlineStr">
+        <is>
+          <t>Monthly Batch — Audit up to 10 Claims Side by Side</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="69" t="inlineStr">
+        <is>
+          <t>One column per claim · fill in the yellow header + ratings · each column's Compliance % and Rating compute automatically. Nothing gets erased between charts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>Provider</t>
+        </is>
+      </c>
+      <c r="B4" s="70" t="n"/>
+      <c r="C4" s="70" t="n"/>
+      <c r="D4" s="70" t="n"/>
+      <c r="E4" s="70" t="n"/>
+      <c r="F4" s="70" t="n"/>
+      <c r="G4" s="70" t="n"/>
+      <c r="H4" s="70" t="n"/>
+      <c r="I4" s="70" t="n"/>
+      <c r="J4" s="70" t="n"/>
+      <c r="K4" s="70" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Claim Number</t>
+        </is>
+      </c>
+      <c r="B5" s="70" t="n"/>
+      <c r="C5" s="70" t="n"/>
+      <c r="D5" s="70" t="n"/>
+      <c r="E5" s="70" t="n"/>
+      <c r="F5" s="70" t="n"/>
+      <c r="G5" s="70" t="n"/>
+      <c r="H5" s="70" t="n"/>
+      <c r="I5" s="70" t="n"/>
+      <c r="J5" s="70" t="n"/>
+      <c r="K5" s="70" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Date of Service</t>
+        </is>
+      </c>
+      <c r="B6" s="70" t="n"/>
+      <c r="C6" s="70" t="n"/>
+      <c r="D6" s="70" t="n"/>
+      <c r="E6" s="70" t="n"/>
+      <c r="F6" s="70" t="n"/>
+      <c r="G6" s="70" t="n"/>
+      <c r="H6" s="70" t="n"/>
+      <c r="I6" s="70" t="n"/>
+      <c r="J6" s="70" t="n"/>
+      <c r="K6" s="70" t="n"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B7" s="70" t="n"/>
+      <c r="C7" s="70" t="n"/>
+      <c r="D7" s="70" t="n"/>
+      <c r="E7" s="70" t="n"/>
+      <c r="F7" s="70" t="n"/>
+      <c r="G7" s="70" t="n"/>
+      <c r="H7" s="70" t="n"/>
+      <c r="I7" s="70" t="n"/>
+      <c r="J7" s="70" t="n"/>
+      <c r="K7" s="70" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>Payer</t>
+        </is>
+      </c>
+      <c r="B8" s="70" t="n"/>
+      <c r="C8" s="70" t="n"/>
+      <c r="D8" s="70" t="n"/>
+      <c r="E8" s="70" t="n"/>
+      <c r="F8" s="70" t="n"/>
+      <c r="G8" s="70" t="n"/>
+      <c r="H8" s="70" t="n"/>
+      <c r="I8" s="70" t="n"/>
+      <c r="J8" s="70" t="n"/>
+      <c r="K8" s="70" t="n"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="71" t="inlineStr">
+        <is>
+          <t>Element ↓  ·  Chart →</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>#1</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>#2</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>#3</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>#4</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>#5</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>#7</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>#8</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>#9</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>#10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A · Diagnosis Accuracy   (30%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="73" t="inlineStr">
+        <is>
+          <t>A1 — Diagnoses clinically supported</t>
+        </is>
+      </c>
+      <c r="B11" s="74" t="n"/>
+      <c r="C11" s="74" t="n"/>
+      <c r="D11" s="74" t="n"/>
+      <c r="E11" s="74" t="n"/>
+      <c r="F11" s="74" t="n"/>
+      <c r="G11" s="74" t="n"/>
+      <c r="H11" s="74" t="n"/>
+      <c r="I11" s="74" t="n"/>
+      <c r="J11" s="74" t="n"/>
+      <c r="K11" s="74" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="73" t="inlineStr">
+        <is>
+          <t>A2 — Chronic conditions actively addressed</t>
+        </is>
+      </c>
+      <c r="B12" s="74" t="n"/>
+      <c r="C12" s="74" t="n"/>
+      <c r="D12" s="74" t="n"/>
+      <c r="E12" s="74" t="n"/>
+      <c r="F12" s="74" t="n"/>
+      <c r="G12" s="74" t="n"/>
+      <c r="H12" s="74" t="n"/>
+      <c r="I12" s="74" t="n"/>
+      <c r="J12" s="74" t="n"/>
+      <c r="K12" s="74" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="73" t="inlineStr">
+        <is>
+          <t>A3 — No unsupported / resolved dx billed</t>
+        </is>
+      </c>
+      <c r="B13" s="74" t="n"/>
+      <c r="C13" s="74" t="n"/>
+      <c r="D13" s="74" t="n"/>
+      <c r="E13" s="74" t="n"/>
+      <c r="F13" s="74" t="n"/>
+      <c r="G13" s="74" t="n"/>
+      <c r="H13" s="74" t="n"/>
+      <c r="I13" s="74" t="n"/>
+      <c r="J13" s="74" t="n"/>
+      <c r="K13" s="74" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="73" t="inlineStr">
+        <is>
+          <t>A4 — Problem list matches A&amp;P</t>
+        </is>
+      </c>
+      <c r="B14" s="74" t="n"/>
+      <c r="C14" s="74" t="n"/>
+      <c r="D14" s="74" t="n"/>
+      <c r="E14" s="74" t="n"/>
+      <c r="F14" s="74" t="n"/>
+      <c r="G14" s="74" t="n"/>
+      <c r="H14" s="74" t="n"/>
+      <c r="I14" s="74" t="n"/>
+      <c r="J14" s="74" t="n"/>
+      <c r="K14" s="74" t="n"/>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B · Documentation Specificity   (25%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="73" t="inlineStr">
+        <is>
+          <t>B1 — ICD-10 at highest specificity</t>
+        </is>
+      </c>
+      <c r="B16" s="74" t="n"/>
+      <c r="C16" s="74" t="n"/>
+      <c r="D16" s="74" t="n"/>
+      <c r="E16" s="74" t="n"/>
+      <c r="F16" s="74" t="n"/>
+      <c r="G16" s="74" t="n"/>
+      <c r="H16" s="74" t="n"/>
+      <c r="I16" s="74" t="n"/>
+      <c r="J16" s="74" t="n"/>
+      <c r="K16" s="74" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="73" t="inlineStr">
+        <is>
+          <t>B2 — Diabetes: type + complications + control</t>
+        </is>
+      </c>
+      <c r="B17" s="74" t="n"/>
+      <c r="C17" s="74" t="n"/>
+      <c r="D17" s="74" t="n"/>
+      <c r="E17" s="74" t="n"/>
+      <c r="F17" s="74" t="n"/>
+      <c r="G17" s="74" t="n"/>
+      <c r="H17" s="74" t="n"/>
+      <c r="I17" s="74" t="n"/>
+      <c r="J17" s="74" t="n"/>
+      <c r="K17" s="74" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="73" t="inlineStr">
+        <is>
+          <t>B3 — S/O/A/P tell one consistent story</t>
+        </is>
+      </c>
+      <c r="B18" s="74" t="n"/>
+      <c r="C18" s="74" t="n"/>
+      <c r="D18" s="74" t="n"/>
+      <c r="E18" s="74" t="n"/>
+      <c r="F18" s="74" t="n"/>
+      <c r="G18" s="74" t="n"/>
+      <c r="H18" s="74" t="n"/>
+      <c r="I18" s="74" t="n"/>
+      <c r="J18" s="74" t="n"/>
+      <c r="K18" s="74" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="73" t="inlineStr">
+        <is>
+          <t>B4 — Note signed / dated / closed</t>
+        </is>
+      </c>
+      <c r="B19" s="74" t="n"/>
+      <c r="C19" s="74" t="n"/>
+      <c r="D19" s="74" t="n"/>
+      <c r="E19" s="74" t="n"/>
+      <c r="F19" s="74" t="n"/>
+      <c r="G19" s="74" t="n"/>
+      <c r="H19" s="74" t="n"/>
+      <c r="I19" s="74" t="n"/>
+      <c r="J19" s="74" t="n"/>
+      <c r="K19" s="74" t="n"/>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C · SOAP Note Structure   (25%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="73" t="inlineStr">
+        <is>
+          <t>C1 — Subjective documented</t>
+        </is>
+      </c>
+      <c r="B21" s="74" t="n"/>
+      <c r="C21" s="74" t="n"/>
+      <c r="D21" s="74" t="n"/>
+      <c r="E21" s="74" t="n"/>
+      <c r="F21" s="74" t="n"/>
+      <c r="G21" s="74" t="n"/>
+      <c r="H21" s="74" t="n"/>
+      <c r="I21" s="74" t="n"/>
+      <c r="J21" s="74" t="n"/>
+      <c r="K21" s="74" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="73" t="inlineStr">
+        <is>
+          <t>C2 — Objective documented</t>
+        </is>
+      </c>
+      <c r="B22" s="74" t="n"/>
+      <c r="C22" s="74" t="n"/>
+      <c r="D22" s="74" t="n"/>
+      <c r="E22" s="74" t="n"/>
+      <c r="F22" s="74" t="n"/>
+      <c r="G22" s="74" t="n"/>
+      <c r="H22" s="74" t="n"/>
+      <c r="I22" s="74" t="n"/>
+      <c r="J22" s="74" t="n"/>
+      <c r="K22" s="74" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="73" t="inlineStr">
+        <is>
+          <t>C3 — Assessment (dx with reasoning)</t>
+        </is>
+      </c>
+      <c r="B23" s="74" t="n"/>
+      <c r="C23" s="74" t="n"/>
+      <c r="D23" s="74" t="n"/>
+      <c r="E23" s="74" t="n"/>
+      <c r="F23" s="74" t="n"/>
+      <c r="G23" s="74" t="n"/>
+      <c r="H23" s="74" t="n"/>
+      <c r="I23" s="74" t="n"/>
+      <c r="J23" s="74" t="n"/>
+      <c r="K23" s="74" t="n"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="73" t="inlineStr">
+        <is>
+          <t>C4 — Plan documented</t>
+        </is>
+      </c>
+      <c r="B24" s="74" t="n"/>
+      <c r="C24" s="74" t="n"/>
+      <c r="D24" s="74" t="n"/>
+      <c r="E24" s="74" t="n"/>
+      <c r="F24" s="74" t="n"/>
+      <c r="G24" s="74" t="n"/>
+      <c r="H24" s="74" t="n"/>
+      <c r="I24" s="74" t="n"/>
+      <c r="J24" s="74" t="n"/>
+      <c r="K24" s="74" t="n"/>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D · HCC Capture   (10%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="73" t="inlineStr">
+        <is>
+          <t>D1 — Prior-year HCCs recaptured</t>
+        </is>
+      </c>
+      <c r="B26" s="74" t="n"/>
+      <c r="C26" s="74" t="n"/>
+      <c r="D26" s="74" t="n"/>
+      <c r="E26" s="74" t="n"/>
+      <c r="F26" s="74" t="n"/>
+      <c r="G26" s="74" t="n"/>
+      <c r="H26" s="74" t="n"/>
+      <c r="I26" s="74" t="n"/>
+      <c r="J26" s="74" t="n"/>
+      <c r="K26" s="74" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="73" t="inlineStr">
+        <is>
+          <t>D2 — Suspected chronic conditions captured</t>
+        </is>
+      </c>
+      <c r="B27" s="74" t="n"/>
+      <c r="C27" s="74" t="n"/>
+      <c r="D27" s="74" t="n"/>
+      <c r="E27" s="74" t="n"/>
+      <c r="F27" s="74" t="n"/>
+      <c r="G27" s="74" t="n"/>
+      <c r="H27" s="74" t="n"/>
+      <c r="I27" s="74" t="n"/>
+      <c r="J27" s="74" t="n"/>
+      <c r="K27" s="74" t="n"/>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E · Documentation Supporting Quality Measures   (10%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="73" t="inlineStr">
+        <is>
+          <t>E1 — Screening values documented (score/number)</t>
+        </is>
+      </c>
+      <c r="B29" s="74" t="n"/>
+      <c r="C29" s="74" t="n"/>
+      <c r="D29" s="74" t="n"/>
+      <c r="E29" s="74" t="n"/>
+      <c r="F29" s="74" t="n"/>
+      <c r="G29" s="74" t="n"/>
+      <c r="H29" s="74" t="n"/>
+      <c r="I29" s="74" t="n"/>
+      <c r="J29" s="74" t="n"/>
+      <c r="K29" s="74" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="73" t="inlineStr">
+        <is>
+          <t>E2 — Follow-up plan when positive/abnormal</t>
+        </is>
+      </c>
+      <c r="B30" s="74" t="n"/>
+      <c r="C30" s="74" t="n"/>
+      <c r="D30" s="74" t="n"/>
+      <c r="E30" s="74" t="n"/>
+      <c r="F30" s="74" t="n"/>
+      <c r="G30" s="74" t="n"/>
+      <c r="H30" s="74" t="n"/>
+      <c r="I30" s="74" t="n"/>
+      <c r="J30" s="74" t="n"/>
+      <c r="K30" s="74" t="n"/>
+    </row>
+    <row r="32" ht="6" customHeight="1"/>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="75" t="inlineStr">
+        <is>
+          <t>SECTION SUBTOTALS</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="17" t="n"/>
+      <c r="G33" s="17" t="n"/>
+      <c r="H33" s="17" t="n"/>
+      <c r="I33" s="17" t="n"/>
+      <c r="J33" s="17" t="n"/>
+      <c r="K33" s="17" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A · % Met  (weight 30%)</t>
+        </is>
+      </c>
+      <c r="B34" s="76">
+        <f>IFERROR((COUNTIF(B11:B14,"✓")+COUNTIF(B11:B14,"△")*0.5)/(COUNTIF(B11:B14,"✓")+COUNTIF(B11:B14,"△")+COUNTIF(B11:B14,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="76">
+        <f>IFERROR((COUNTIF(C11:C14,"✓")+COUNTIF(C11:C14,"△")*0.5)/(COUNTIF(C11:C14,"✓")+COUNTIF(C11:C14,"△")+COUNTIF(C11:C14,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="76">
+        <f>IFERROR((COUNTIF(D11:D14,"✓")+COUNTIF(D11:D14,"△")*0.5)/(COUNTIF(D11:D14,"✓")+COUNTIF(D11:D14,"△")+COUNTIF(D11:D14,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="76">
+        <f>IFERROR((COUNTIF(E11:E14,"✓")+COUNTIF(E11:E14,"△")*0.5)/(COUNTIF(E11:E14,"✓")+COUNTIF(E11:E14,"△")+COUNTIF(E11:E14,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="76">
+        <f>IFERROR((COUNTIF(F11:F14,"✓")+COUNTIF(F11:F14,"△")*0.5)/(COUNTIF(F11:F14,"✓")+COUNTIF(F11:F14,"△")+COUNTIF(F11:F14,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="76">
+        <f>IFERROR((COUNTIF(G11:G14,"✓")+COUNTIF(G11:G14,"△")*0.5)/(COUNTIF(G11:G14,"✓")+COUNTIF(G11:G14,"△")+COUNTIF(G11:G14,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="76">
+        <f>IFERROR((COUNTIF(H11:H14,"✓")+COUNTIF(H11:H14,"△")*0.5)/(COUNTIF(H11:H14,"✓")+COUNTIF(H11:H14,"△")+COUNTIF(H11:H14,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="76">
+        <f>IFERROR((COUNTIF(I11:I14,"✓")+COUNTIF(I11:I14,"△")*0.5)/(COUNTIF(I11:I14,"✓")+COUNTIF(I11:I14,"△")+COUNTIF(I11:I14,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="J34" s="76">
+        <f>IFERROR((COUNTIF(J11:J14,"✓")+COUNTIF(J11:J14,"△")*0.5)/(COUNTIF(J11:J14,"✓")+COUNTIF(J11:J14,"△")+COUNTIF(J11:J14,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="K34" s="76">
+        <f>IFERROR((COUNTIF(K11:K14,"✓")+COUNTIF(K11:K14,"△")*0.5)/(COUNTIF(K11:K14,"✓")+COUNTIF(K11:K14,"△")+COUNTIF(K11:K14,"✗")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B · % Met  (weight 25%)</t>
+        </is>
+      </c>
+      <c r="B35" s="76">
+        <f>IFERROR((COUNTIF(B16:B19,"✓")+COUNTIF(B16:B19,"△")*0.5)/(COUNTIF(B16:B19,"✓")+COUNTIF(B16:B19,"△")+COUNTIF(B16:B19,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="C35" s="76">
+        <f>IFERROR((COUNTIF(C16:C19,"✓")+COUNTIF(C16:C19,"△")*0.5)/(COUNTIF(C16:C19,"✓")+COUNTIF(C16:C19,"△")+COUNTIF(C16:C19,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="76">
+        <f>IFERROR((COUNTIF(D16:D19,"✓")+COUNTIF(D16:D19,"△")*0.5)/(COUNTIF(D16:D19,"✓")+COUNTIF(D16:D19,"△")+COUNTIF(D16:D19,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="76">
+        <f>IFERROR((COUNTIF(E16:E19,"✓")+COUNTIF(E16:E19,"△")*0.5)/(COUNTIF(E16:E19,"✓")+COUNTIF(E16:E19,"△")+COUNTIF(E16:E19,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="76">
+        <f>IFERROR((COUNTIF(F16:F19,"✓")+COUNTIF(F16:F19,"△")*0.5)/(COUNTIF(F16:F19,"✓")+COUNTIF(F16:F19,"△")+COUNTIF(F16:F19,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="76">
+        <f>IFERROR((COUNTIF(G16:G19,"✓")+COUNTIF(G16:G19,"△")*0.5)/(COUNTIF(G16:G19,"✓")+COUNTIF(G16:G19,"△")+COUNTIF(G16:G19,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="76">
+        <f>IFERROR((COUNTIF(H16:H19,"✓")+COUNTIF(H16:H19,"△")*0.5)/(COUNTIF(H16:H19,"✓")+COUNTIF(H16:H19,"△")+COUNTIF(H16:H19,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="76">
+        <f>IFERROR((COUNTIF(I16:I19,"✓")+COUNTIF(I16:I19,"△")*0.5)/(COUNTIF(I16:I19,"✓")+COUNTIF(I16:I19,"△")+COUNTIF(I16:I19,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="76">
+        <f>IFERROR((COUNTIF(J16:J19,"✓")+COUNTIF(J16:J19,"△")*0.5)/(COUNTIF(J16:J19,"✓")+COUNTIF(J16:J19,"△")+COUNTIF(J16:J19,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="K35" s="76">
+        <f>IFERROR((COUNTIF(K16:K19,"✓")+COUNTIF(K16:K19,"△")*0.5)/(COUNTIF(K16:K19,"✓")+COUNTIF(K16:K19,"△")+COUNTIF(K16:K19,"✗")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C · % Met  (weight 25%)</t>
+        </is>
+      </c>
+      <c r="B36" s="76">
+        <f>IFERROR((COUNTIF(B21:B24,"✓")+COUNTIF(B21:B24,"△")*0.5)/(COUNTIF(B21:B24,"✓")+COUNTIF(B21:B24,"△")+COUNTIF(B21:B24,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="76">
+        <f>IFERROR((COUNTIF(C21:C24,"✓")+COUNTIF(C21:C24,"△")*0.5)/(COUNTIF(C21:C24,"✓")+COUNTIF(C21:C24,"△")+COUNTIF(C21:C24,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="76">
+        <f>IFERROR((COUNTIF(D21:D24,"✓")+COUNTIF(D21:D24,"△")*0.5)/(COUNTIF(D21:D24,"✓")+COUNTIF(D21:D24,"△")+COUNTIF(D21:D24,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="76">
+        <f>IFERROR((COUNTIF(E21:E24,"✓")+COUNTIF(E21:E24,"△")*0.5)/(COUNTIF(E21:E24,"✓")+COUNTIF(E21:E24,"△")+COUNTIF(E21:E24,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="76">
+        <f>IFERROR((COUNTIF(F21:F24,"✓")+COUNTIF(F21:F24,"△")*0.5)/(COUNTIF(F21:F24,"✓")+COUNTIF(F21:F24,"△")+COUNTIF(F21:F24,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="76">
+        <f>IFERROR((COUNTIF(G21:G24,"✓")+COUNTIF(G21:G24,"△")*0.5)/(COUNTIF(G21:G24,"✓")+COUNTIF(G21:G24,"△")+COUNTIF(G21:G24,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="76">
+        <f>IFERROR((COUNTIF(H21:H24,"✓")+COUNTIF(H21:H24,"△")*0.5)/(COUNTIF(H21:H24,"✓")+COUNTIF(H21:H24,"△")+COUNTIF(H21:H24,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="76">
+        <f>IFERROR((COUNTIF(I21:I24,"✓")+COUNTIF(I21:I24,"△")*0.5)/(COUNTIF(I21:I24,"✓")+COUNTIF(I21:I24,"△")+COUNTIF(I21:I24,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="J36" s="76">
+        <f>IFERROR((COUNTIF(J21:J24,"✓")+COUNTIF(J21:J24,"△")*0.5)/(COUNTIF(J21:J24,"✓")+COUNTIF(J21:J24,"△")+COUNTIF(J21:J24,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="K36" s="76">
+        <f>IFERROR((COUNTIF(K21:K24,"✓")+COUNTIF(K21:K24,"△")*0.5)/(COUNTIF(K21:K24,"✓")+COUNTIF(K21:K24,"△")+COUNTIF(K21:K24,"✗")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D · % Met  (weight 10%)</t>
+        </is>
+      </c>
+      <c r="B37" s="76">
+        <f>IFERROR((COUNTIF(B26:B27,"✓")+COUNTIF(B26:B27,"△")*0.5)/(COUNTIF(B26:B27,"✓")+COUNTIF(B26:B27,"△")+COUNTIF(B26:B27,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="C37" s="76">
+        <f>IFERROR((COUNTIF(C26:C27,"✓")+COUNTIF(C26:C27,"△")*0.5)/(COUNTIF(C26:C27,"✓")+COUNTIF(C26:C27,"△")+COUNTIF(C26:C27,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="76">
+        <f>IFERROR((COUNTIF(D26:D27,"✓")+COUNTIF(D26:D27,"△")*0.5)/(COUNTIF(D26:D27,"✓")+COUNTIF(D26:D27,"△")+COUNTIF(D26:D27,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="76">
+        <f>IFERROR((COUNTIF(E26:E27,"✓")+COUNTIF(E26:E27,"△")*0.5)/(COUNTIF(E26:E27,"✓")+COUNTIF(E26:E27,"△")+COUNTIF(E26:E27,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="76">
+        <f>IFERROR((COUNTIF(F26:F27,"✓")+COUNTIF(F26:F27,"△")*0.5)/(COUNTIF(F26:F27,"✓")+COUNTIF(F26:F27,"△")+COUNTIF(F26:F27,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="76">
+        <f>IFERROR((COUNTIF(G26:G27,"✓")+COUNTIF(G26:G27,"△")*0.5)/(COUNTIF(G26:G27,"✓")+COUNTIF(G26:G27,"△")+COUNTIF(G26:G27,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="76">
+        <f>IFERROR((COUNTIF(H26:H27,"✓")+COUNTIF(H26:H27,"△")*0.5)/(COUNTIF(H26:H27,"✓")+COUNTIF(H26:H27,"△")+COUNTIF(H26:H27,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="I37" s="76">
+        <f>IFERROR((COUNTIF(I26:I27,"✓")+COUNTIF(I26:I27,"△")*0.5)/(COUNTIF(I26:I27,"✓")+COUNTIF(I26:I27,"△")+COUNTIF(I26:I27,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="J37" s="76">
+        <f>IFERROR((COUNTIF(J26:J27,"✓")+COUNTIF(J26:J27,"△")*0.5)/(COUNTIF(J26:J27,"✓")+COUNTIF(J26:J27,"△")+COUNTIF(J26:J27,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="K37" s="76">
+        <f>IFERROR((COUNTIF(K26:K27,"✓")+COUNTIF(K26:K27,"△")*0.5)/(COUNTIF(K26:K27,"✓")+COUNTIF(K26:K27,"△")+COUNTIF(K26:K27,"✗")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E · % Met  (weight 10%)</t>
+        </is>
+      </c>
+      <c r="B38" s="76">
+        <f>IFERROR((COUNTIF(B29:B30,"✓")+COUNTIF(B29:B30,"△")*0.5)/(COUNTIF(B29:B30,"✓")+COUNTIF(B29:B30,"△")+COUNTIF(B29:B30,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="C38" s="76">
+        <f>IFERROR((COUNTIF(C29:C30,"✓")+COUNTIF(C29:C30,"△")*0.5)/(COUNTIF(C29:C30,"✓")+COUNTIF(C29:C30,"△")+COUNTIF(C29:C30,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="76">
+        <f>IFERROR((COUNTIF(D29:D30,"✓")+COUNTIF(D29:D30,"△")*0.5)/(COUNTIF(D29:D30,"✓")+COUNTIF(D29:D30,"△")+COUNTIF(D29:D30,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="76">
+        <f>IFERROR((COUNTIF(E29:E30,"✓")+COUNTIF(E29:E30,"△")*0.5)/(COUNTIF(E29:E30,"✓")+COUNTIF(E29:E30,"△")+COUNTIF(E29:E30,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="76">
+        <f>IFERROR((COUNTIF(F29:F30,"✓")+COUNTIF(F29:F30,"△")*0.5)/(COUNTIF(F29:F30,"✓")+COUNTIF(F29:F30,"△")+COUNTIF(F29:F30,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="76">
+        <f>IFERROR((COUNTIF(G29:G30,"✓")+COUNTIF(G29:G30,"△")*0.5)/(COUNTIF(G29:G30,"✓")+COUNTIF(G29:G30,"△")+COUNTIF(G29:G30,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="76">
+        <f>IFERROR((COUNTIF(H29:H30,"✓")+COUNTIF(H29:H30,"△")*0.5)/(COUNTIF(H29:H30,"✓")+COUNTIF(H29:H30,"△")+COUNTIF(H29:H30,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="76">
+        <f>IFERROR((COUNTIF(I29:I30,"✓")+COUNTIF(I29:I30,"△")*0.5)/(COUNTIF(I29:I30,"✓")+COUNTIF(I29:I30,"△")+COUNTIF(I29:I30,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="76">
+        <f>IFERROR((COUNTIF(J29:J30,"✓")+COUNTIF(J29:J30,"△")*0.5)/(COUNTIF(J29:J30,"✓")+COUNTIF(J29:J30,"△")+COUNTIF(J29:J30,"✗")),"")</f>
+        <v/>
+      </c>
+      <c r="K38" s="76">
+        <f>IFERROR((COUNTIF(K29:K30,"✓")+COUNTIF(K29:K30,"△")*0.5)/(COUNTIF(K29:K30,"✓")+COUNTIF(K29:K30,"△")+COUNTIF(K29:K30,"✗")),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>OVERALL COMPLIANCE %</t>
+        </is>
+      </c>
+      <c r="B40" s="77">
+        <f>IFERROR((IFERROR(B34,0)*IF(B34="",0,0.3)+IFERROR(B35,0)*IF(B35="",0,0.25)+IFERROR(B36,0)*IF(B36="",0,0.25)+IFERROR(B37,0)*IF(B37="",0,0.1)+IFERROR(B38,0)*IF(B38="",0,0.1))/(IF(B34="",0,0.3)+IF(B35="",0,0.25)+IF(B36="",0,0.25)+IF(B37="",0,0.1)+IF(B38="",0,0.1)),"")</f>
+        <v/>
+      </c>
+      <c r="C40" s="77">
+        <f>IFERROR((IFERROR(C34,0)*IF(C34="",0,0.3)+IFERROR(C35,0)*IF(C35="",0,0.25)+IFERROR(C36,0)*IF(C36="",0,0.25)+IFERROR(C37,0)*IF(C37="",0,0.1)+IFERROR(C38,0)*IF(C38="",0,0.1))/(IF(C34="",0,0.3)+IF(C35="",0,0.25)+IF(C36="",0,0.25)+IF(C37="",0,0.1)+IF(C38="",0,0.1)),"")</f>
+        <v/>
+      </c>
+      <c r="D40" s="77">
+        <f>IFERROR((IFERROR(D34,0)*IF(D34="",0,0.3)+IFERROR(D35,0)*IF(D35="",0,0.25)+IFERROR(D36,0)*IF(D36="",0,0.25)+IFERROR(D37,0)*IF(D37="",0,0.1)+IFERROR(D38,0)*IF(D38="",0,0.1))/(IF(D34="",0,0.3)+IF(D35="",0,0.25)+IF(D36="",0,0.25)+IF(D37="",0,0.1)+IF(D38="",0,0.1)),"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="77">
+        <f>IFERROR((IFERROR(E34,0)*IF(E34="",0,0.3)+IFERROR(E35,0)*IF(E35="",0,0.25)+IFERROR(E36,0)*IF(E36="",0,0.25)+IFERROR(E37,0)*IF(E37="",0,0.1)+IFERROR(E38,0)*IF(E38="",0,0.1))/(IF(E34="",0,0.3)+IF(E35="",0,0.25)+IF(E36="",0,0.25)+IF(E37="",0,0.1)+IF(E38="",0,0.1)),"")</f>
+        <v/>
+      </c>
+      <c r="F40" s="77">
+        <f>IFERROR((IFERROR(F34,0)*IF(F34="",0,0.3)+IFERROR(F35,0)*IF(F35="",0,0.25)+IFERROR(F36,0)*IF(F36="",0,0.25)+IFERROR(F37,0)*IF(F37="",0,0.1)+IFERROR(F38,0)*IF(F38="",0,0.1))/(IF(F34="",0,0.3)+IF(F35="",0,0.25)+IF(F36="",0,0.25)+IF(F37="",0,0.1)+IF(F38="",0,0.1)),"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="77">
+        <f>IFERROR((IFERROR(G34,0)*IF(G34="",0,0.3)+IFERROR(G35,0)*IF(G35="",0,0.25)+IFERROR(G36,0)*IF(G36="",0,0.25)+IFERROR(G37,0)*IF(G37="",0,0.1)+IFERROR(G38,0)*IF(G38="",0,0.1))/(IF(G34="",0,0.3)+IF(G35="",0,0.25)+IF(G36="",0,0.25)+IF(G37="",0,0.1)+IF(G38="",0,0.1)),"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="77">
+        <f>IFERROR((IFERROR(H34,0)*IF(H34="",0,0.3)+IFERROR(H35,0)*IF(H35="",0,0.25)+IFERROR(H36,0)*IF(H36="",0,0.25)+IFERROR(H37,0)*IF(H37="",0,0.1)+IFERROR(H38,0)*IF(H38="",0,0.1))/(IF(H34="",0,0.3)+IF(H35="",0,0.25)+IF(H36="",0,0.25)+IF(H37="",0,0.1)+IF(H38="",0,0.1)),"")</f>
+        <v/>
+      </c>
+      <c r="I40" s="77">
+        <f>IFERROR((IFERROR(I34,0)*IF(I34="",0,0.3)+IFERROR(I35,0)*IF(I35="",0,0.25)+IFERROR(I36,0)*IF(I36="",0,0.25)+IFERROR(I37,0)*IF(I37="",0,0.1)+IFERROR(I38,0)*IF(I38="",0,0.1))/(IF(I34="",0,0.3)+IF(I35="",0,0.25)+IF(I36="",0,0.25)+IF(I37="",0,0.1)+IF(I38="",0,0.1)),"")</f>
+        <v/>
+      </c>
+      <c r="J40" s="77">
+        <f>IFERROR((IFERROR(J34,0)*IF(J34="",0,0.3)+IFERROR(J35,0)*IF(J35="",0,0.25)+IFERROR(J36,0)*IF(J36="",0,0.25)+IFERROR(J37,0)*IF(J37="",0,0.1)+IFERROR(J38,0)*IF(J38="",0,0.1))/(IF(J34="",0,0.3)+IF(J35="",0,0.25)+IF(J36="",0,0.25)+IF(J37="",0,0.1)+IF(J38="",0,0.1)),"")</f>
+        <v/>
+      </c>
+      <c r="K40" s="77">
+        <f>IFERROR((IFERROR(K34,0)*IF(K34="",0,0.3)+IFERROR(K35,0)*IF(K35="",0,0.25)+IFERROR(K36,0)*IF(K36="",0,0.25)+IFERROR(K37,0)*IF(K37="",0,0.1)+IFERROR(K38,0)*IF(K38="",0,0.1))/(IF(K34="",0,0.3)+IF(K35="",0,0.25)+IF(K36="",0,0.25)+IF(K37="",0,0.1)+IF(K38="",0,0.1)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="40" t="inlineStr">
+        <is>
+          <t>RATING</t>
+        </is>
+      </c>
+      <c r="B41" s="78">
+        <f>IF(B40="","",IF(B40&gt;=0.95,"Excellent",IF(B40&gt;=0.9,"Meets",IF(B40&gt;=0.8,"Needs Impr","Corrective"))))</f>
+        <v/>
+      </c>
+      <c r="C41" s="78">
+        <f>IF(C40="","",IF(C40&gt;=0.95,"Excellent",IF(C40&gt;=0.9,"Meets",IF(C40&gt;=0.8,"Needs Impr","Corrective"))))</f>
+        <v/>
+      </c>
+      <c r="D41" s="78">
+        <f>IF(D40="","",IF(D40&gt;=0.95,"Excellent",IF(D40&gt;=0.9,"Meets",IF(D40&gt;=0.8,"Needs Impr","Corrective"))))</f>
+        <v/>
+      </c>
+      <c r="E41" s="78">
+        <f>IF(E40="","",IF(E40&gt;=0.95,"Excellent",IF(E40&gt;=0.9,"Meets",IF(E40&gt;=0.8,"Needs Impr","Corrective"))))</f>
+        <v/>
+      </c>
+      <c r="F41" s="78">
+        <f>IF(F40="","",IF(F40&gt;=0.95,"Excellent",IF(F40&gt;=0.9,"Meets",IF(F40&gt;=0.8,"Needs Impr","Corrective"))))</f>
+        <v/>
+      </c>
+      <c r="G41" s="78">
+        <f>IF(G40="","",IF(G40&gt;=0.95,"Excellent",IF(G40&gt;=0.9,"Meets",IF(G40&gt;=0.8,"Needs Impr","Corrective"))))</f>
+        <v/>
+      </c>
+      <c r="H41" s="78">
+        <f>IF(H40="","",IF(H40&gt;=0.95,"Excellent",IF(H40&gt;=0.9,"Meets",IF(H40&gt;=0.8,"Needs Impr","Corrective"))))</f>
+        <v/>
+      </c>
+      <c r="I41" s="78">
+        <f>IF(I40="","",IF(I40&gt;=0.95,"Excellent",IF(I40&gt;=0.9,"Meets",IF(I40&gt;=0.8,"Needs Impr","Corrective"))))</f>
+        <v/>
+      </c>
+      <c r="J41" s="78">
+        <f>IF(J40="","",IF(J40&gt;=0.95,"Excellent",IF(J40&gt;=0.9,"Meets",IF(J40&gt;=0.8,"Needs Impr","Corrective"))))</f>
+        <v/>
+      </c>
+      <c r="K41" s="78">
+        <f>IF(K40="","",IF(K40&gt;=0.95,"Excellent",IF(K40&gt;=0.9,"Meets",IF(K40&gt;=0.8,"Needs Impr","Corrective"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="6" customHeight="1"/>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  BATCH SUMMARY (this month)</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Claims audited</t>
+        </is>
+      </c>
+      <c r="D45" s="79">
+        <f>COUNT(B40:K40)</f>
+        <v/>
+      </c>
+      <c r="E45" s="14" t="n"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Average compliance %</t>
+        </is>
+      </c>
+      <c r="D46" s="80">
+        <f>IFERROR(AVERAGE(B40:K40),"")</f>
+        <v/>
+      </c>
+      <c r="E46" s="14" t="n"/>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Charts scoring Meets+ (≥90%)</t>
+        </is>
+      </c>
+      <c r="D47" s="79">
+        <f>COUNTIF(B40:K40,"&gt;=0.9")</f>
+        <v/>
+      </c>
+      <c r="E47" s="14" t="n"/>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Charts needing Corrective (&lt;80%)</t>
+        </is>
+      </c>
+      <c r="D48" s="79">
+        <f>COUNTIFS(B40:K40,"&lt;0.8",B40:K40,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="E48" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A20:K20"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A28:K28"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B11:B30">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>B11="✓"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>B11="△"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>B11="✗"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="3">
+      <formula>B11="N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C11:C30">
+    <cfRule type="expression" priority="5" dxfId="0">
+      <formula>C11="✓"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="1">
+      <formula>C11="△"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" dxfId="2">
+      <formula>C11="✗"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="3">
+      <formula>C11="N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D11:D30">
+    <cfRule type="expression" priority="9" dxfId="0">
+      <formula>D11="✓"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="10" dxfId="1">
+      <formula>D11="△"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="11" dxfId="2">
+      <formula>D11="✗"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="12" dxfId="3">
+      <formula>D11="N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E11:E30">
+    <cfRule type="expression" priority="13" dxfId="0">
+      <formula>E11="✓"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="14" dxfId="1">
+      <formula>E11="△"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="15" dxfId="2">
+      <formula>E11="✗"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="16" dxfId="3">
+      <formula>E11="N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F11:F30">
+    <cfRule type="expression" priority="17" dxfId="0">
+      <formula>F11="✓"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="18" dxfId="1">
+      <formula>F11="△"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="19" dxfId="2">
+      <formula>F11="✗"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="20" dxfId="3">
+      <formula>F11="N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11:G30">
+    <cfRule type="expression" priority="21" dxfId="0">
+      <formula>G11="✓"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="22" dxfId="1">
+      <formula>G11="△"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="23" dxfId="2">
+      <formula>G11="✗"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="24" dxfId="3">
+      <formula>G11="N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H11:H30">
+    <cfRule type="expression" priority="25" dxfId="0">
+      <formula>H11="✓"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="26" dxfId="1">
+      <formula>H11="△"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="27" dxfId="2">
+      <formula>H11="✗"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="28" dxfId="3">
+      <formula>H11="N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I11:I30">
+    <cfRule type="expression" priority="29" dxfId="0">
+      <formula>I11="✓"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="30" dxfId="1">
+      <formula>I11="△"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="31" dxfId="2">
+      <formula>I11="✗"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="32" dxfId="3">
+      <formula>I11="N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J11:J30">
+    <cfRule type="expression" priority="33" dxfId="0">
+      <formula>J11="✓"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="34" dxfId="1">
+      <formula>J11="△"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="35" dxfId="2">
+      <formula>J11="✗"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="36" dxfId="3">
+      <formula>J11="N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K11:K30">
+    <cfRule type="expression" priority="37" dxfId="0">
+      <formula>K11="✓"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="38" dxfId="1">
+      <formula>K11="△"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="39" dxfId="2">
+      <formula>K11="✗"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="40" dxfId="3">
+      <formula>K11="N/A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34:K34">
+    <cfRule type="cellIs" priority="41" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="42" operator="between" dxfId="1">
+      <formula>0.8</formula>
+      <formula>0.8999</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="43" operator="between" dxfId="2">
+      <formula>0.0001</formula>
+      <formula>0.7999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:K35">
+    <cfRule type="cellIs" priority="44" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="45" operator="between" dxfId="1">
+      <formula>0.8</formula>
+      <formula>0.8999</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="46" operator="between" dxfId="2">
+      <formula>0.0001</formula>
+      <formula>0.7999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B36:K36">
+    <cfRule type="cellIs" priority="47" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="48" operator="between" dxfId="1">
+      <formula>0.8</formula>
+      <formula>0.8999</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="49" operator="between" dxfId="2">
+      <formula>0.0001</formula>
+      <formula>0.7999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B37:K37">
+    <cfRule type="cellIs" priority="50" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="51" operator="between" dxfId="1">
+      <formula>0.8</formula>
+      <formula>0.8999</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="52" operator="between" dxfId="2">
+      <formula>0.0001</formula>
+      <formula>0.7999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38:K38">
+    <cfRule type="cellIs" priority="53" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0.9</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="54" operator="between" dxfId="1">
+      <formula>0.8</formula>
+      <formula>0.8999</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="55" operator="between" dxfId="2">
+      <formula>0.0001</formula>
+      <formula>0.7999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B40:K40">
+    <cfRule type="cellIs" priority="56" operator="greaterThanOrEqual" dxfId="3">
+      <formula>0.95</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="57" operator="between" dxfId="0">
+      <formula>0.9</formula>
+      <formula>0.9499</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="58" operator="between" dxfId="1">
+      <formula>0.8</formula>
+      <formula>0.8999</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="59" operator="between" dxfId="2">
+      <formula>0.0001</formula>
+      <formula>0.7999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B41:K41">
+    <cfRule type="expression" priority="60" dxfId="3">
+      <formula>B41="Excellent"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="61" dxfId="0">
+      <formula>B41="Meets"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="62" dxfId="1">
+      <formula>B41="Needs Impr"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="63" dxfId="2">
+      <formula>B41="Corrective"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation sqref="B7:K7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Diabetes,Chronic Kidney Disease,Annual Wellness Visit,High RAF Patient,Random Selection"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8:K8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Medicare Advantage,Commercial,Medicaid,Dual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B11:K30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,△,✗,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="001E40AF"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -4573,7 +5773,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00334155"/>
@@ -5334,7 +6534,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00B45309"/>

--- a/docs/Clinical_Documentation_Audit_Simple.xlsx
+++ b/docs/Clinical_Documentation_Audit_Simple.xlsx
@@ -8,10 +8,19 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Checklist" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Batch (10)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Reference" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly Report" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claim 01" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claim 02" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claim 03" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claim 04" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claim 05" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claim 06" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claim 07" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claim 08" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claim 09" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claim 10" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Log" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Reference" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly Report" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1338,11 +1347,11 @@
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="28" t="inlineStr">
         <is>
-          <t>How to use
-1. Fill in the yellow cells at top
-2. Rate each element (dropdown in column C)
-3. Overall % + Rating appear at the bottom
-4. Log the chart on the Audit Log tab when done</t>
+          <t>How to audit a claim
+1. Click a Claim 01–10 tab (bottom of the workbook)
+2. Fill the yellow header + ratings — auto-scores
+3. Log the finished claim on the Audit Log tab
+4. Move to the next Claim tab · this Audit Checklist tab stays as the master template</t>
         </is>
       </c>
     </row>
@@ -2028,1167 +2037,1231 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00B45309"/>
+    <tabColor rgb="001E7A6E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="68" t="inlineStr">
-        <is>
-          <t>Monthly Batch — Audit up to 10 Claims Side by Side</t>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Clinical Documentation Audit</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="69" t="inlineStr">
-        <is>
-          <t>One column per claim · fill in the yellow header + ratings · each column's Compliance % and Rating compute automatically. Nothing gets erased between charts.</t>
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>One chart per sheet · tick each item · scoring &amp; rating are automatic</t>
         </is>
       </c>
     </row>
     <row r="3" ht="8" customHeight="1"/>
-    <row r="4" ht="22" customHeight="1">
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="27" t="inlineStr">
         <is>
-          <t>Provider</t>
-        </is>
-      </c>
-      <c r="B4" s="70" t="n"/>
-      <c r="C4" s="70" t="n"/>
-      <c r="D4" s="70" t="n"/>
-      <c r="E4" s="70" t="n"/>
-      <c r="F4" s="70" t="n"/>
-      <c r="G4" s="70" t="n"/>
-      <c r="H4" s="70" t="n"/>
-      <c r="I4" s="70" t="n"/>
-      <c r="J4" s="70" t="n"/>
-      <c r="K4" s="70" t="n"/>
-    </row>
-    <row r="5" ht="22" customHeight="1">
+          <t>Provider:</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Date of Service:</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>How to use
+1. Fill in the yellow cells at top
+2. Rate each element (dropdown in column C)
+3. Overall % + Rating appear at the bottom
+4. Log the chart on the Audit Log tab when done</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
       <c r="A5" s="27" t="inlineStr">
         <is>
-          <t>Claim Number</t>
-        </is>
-      </c>
-      <c r="B5" s="70" t="n"/>
-      <c r="C5" s="70" t="n"/>
-      <c r="D5" s="70" t="n"/>
-      <c r="E5" s="70" t="n"/>
-      <c r="F5" s="70" t="n"/>
-      <c r="G5" s="70" t="n"/>
-      <c r="H5" s="70" t="n"/>
-      <c r="I5" s="70" t="n"/>
-      <c r="J5" s="70" t="n"/>
-      <c r="K5" s="70" t="n"/>
-    </row>
-    <row r="6" ht="22" customHeight="1">
+          <t>Claim Number:</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Auditor:</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="51" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
       <c r="A6" s="27" t="inlineStr">
         <is>
-          <t>Date of Service</t>
-        </is>
-      </c>
-      <c r="B6" s="70" t="n"/>
-      <c r="C6" s="70" t="n"/>
-      <c r="D6" s="70" t="n"/>
-      <c r="E6" s="70" t="n"/>
-      <c r="F6" s="70" t="n"/>
-      <c r="G6" s="70" t="n"/>
-      <c r="H6" s="70" t="n"/>
-      <c r="I6" s="70" t="n"/>
-      <c r="J6" s="70" t="n"/>
-      <c r="K6" s="70" t="n"/>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
+          <t>Category:</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Payer:</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="52" t="n"/>
+    </row>
+    <row r="7" ht="12" customHeight="1"/>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Documentation element</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Pts</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A · Diagnosis Accuracy   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>All reported diagnoses are clinically supported in the note</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="33">
+        <f>IF(C10="✓ Met",1,IF(C10="△ Partial",0.5,IF(C10="✗ Not Met",0,IF(C10="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Chronic conditions actively addressed at this visit (not just carried forward)</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="33">
+        <f>IF(C11="✓ Met",1,IF(C11="△ Partial",0.5,IF(C11="✗ Not Met",0,IF(C11="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>No unsupported or resolved conditions billed as active</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="33">
+        <f>IF(C12="✓ Met",1,IF(C12="△ Partial",0.5,IF(C12="✗ Not Met",0,IF(C12="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Problem list matches today's assessment &amp; plan</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="33">
+        <f>IF(C13="✓ Met",1,IF(C13="△ Partial",0.5,IF(C13="✗ Not Met",0,IF(C13="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B · Documentation Specificity   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>ICD-10 codes at highest available specificity (avoid 'unspecified')</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="33">
+        <f>IF(C16="✓ Met",1,IF(C16="△ Partial",0.5,IF(C16="✗ Not Met",0,IF(C16="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes: type + complications + control specified</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="33">
+        <f>IF(C17="✓ Met",1,IF(C17="△ Partial",0.5,IF(C17="✗ Not Met",0,IF(C17="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>S / O / A / P sections tell one consistent clinical story</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="33">
+        <f>IF(C18="✓ Met",1,IF(C18="△ Partial",0.5,IF(C18="✗ Not Met",0,IF(C18="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Note signed, dated, and closed by the rendering provider</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="33">
+        <f>IF(C19="✓ Met",1,IF(C19="△ Partial",0.5,IF(C19="✗ Not Met",0,IF(C19="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C · SOAP Note Structure   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Subjective — patient's history, symptoms, and concerns clearly documented</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="33">
+        <f>IF(C22="✓ Met",1,IF(C22="△ Partial",0.5,IF(C22="✗ Not Met",0,IF(C22="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Objective — exam findings, vitals, and relevant test results documented</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="33">
+        <f>IF(C23="✓ Met",1,IF(C23="△ Partial",0.5,IF(C23="✗ Not Met",0,IF(C23="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Assessment — each diagnosis explicitly assessed with clinical reasoning</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="33">
+        <f>IF(C24="✓ Met",1,IF(C24="△ Partial",0.5,IF(C24="✗ Not Met",0,IF(C24="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Plan — treatment plan documented (medication / referral / testing / follow-up)</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="33">
+        <f>IF(C25="✓ Met",1,IF(C25="△ Partial",0.5,IF(C25="✗ Not Met",0,IF(C25="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D · HCC Capture   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Prior-year HCCs recaptured (or explicitly resolved with rationale)</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="33">
+        <f>IF(C28="✓ Met",1,IF(C28="△ Partial",0.5,IF(C28="✗ Not Met",0,IF(C28="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Suspected undocumented chronic conditions captured with support</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="33">
+        <f>IF(C29="✓ Met",1,IF(C29="△ Partial",0.5,IF(C29="✗ Not Met",0,IF(C29="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E · Documentation Supporting Quality Measures   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Screening / measure results documented with specific values (PHQ-9, GAD-7, BMI, BP, HbA1c) — not just 'screened' or 'normal'</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="33">
+        <f>IF(C32="✓ Met",1,IF(C32="△ Partial",0.5,IF(C32="✗ Not Met",0,IF(C32="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Follow-up plan documented when a screening is positive or a result is abnormal (positive PHQ-9 → depression plan; elevated BMI → nutrition counseling)</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33">
+        <f>IF(C33="✓ Met",1,IF(C33="△ Partial",0.5,IF(C33="✗ Not Met",0,IF(C33="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B7" s="70" t="n"/>
-      <c r="C7" s="70" t="n"/>
-      <c r="D7" s="70" t="n"/>
-      <c r="E7" s="70" t="n"/>
-      <c r="F7" s="70" t="n"/>
-      <c r="G7" s="70" t="n"/>
-      <c r="H7" s="70" t="n"/>
-      <c r="I7" s="70" t="n"/>
-      <c r="J7" s="70" t="n"/>
-      <c r="K7" s="70" t="n"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="27" t="inlineStr">
-        <is>
-          <t>Payer</t>
-        </is>
-      </c>
-      <c r="B8" s="70" t="n"/>
-      <c r="C8" s="70" t="n"/>
-      <c r="D8" s="70" t="n"/>
-      <c r="E8" s="70" t="n"/>
-      <c r="F8" s="70" t="n"/>
-      <c r="G8" s="70" t="n"/>
-      <c r="H8" s="70" t="n"/>
-      <c r="I8" s="70" t="n"/>
-      <c r="J8" s="70" t="n"/>
-      <c r="K8" s="70" t="n"/>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="71" t="inlineStr">
-        <is>
-          <t>Element ↓  ·  Chart →</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>#1</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>#2</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>#3</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>#4</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>#5</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>#6</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>#7</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>#8</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>#9</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>#10</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  A · Diagnosis Accuracy   (30%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="73" t="inlineStr">
-        <is>
-          <t>A1 — Diagnoses clinically supported</t>
-        </is>
-      </c>
-      <c r="B11" s="74" t="n"/>
-      <c r="C11" s="74" t="n"/>
-      <c r="D11" s="74" t="n"/>
-      <c r="E11" s="74" t="n"/>
-      <c r="F11" s="74" t="n"/>
-      <c r="G11" s="74" t="n"/>
-      <c r="H11" s="74" t="n"/>
-      <c r="I11" s="74" t="n"/>
-      <c r="J11" s="74" t="n"/>
-      <c r="K11" s="74" t="n"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="73" t="inlineStr">
-        <is>
-          <t>A2 — Chronic conditions actively addressed</t>
-        </is>
-      </c>
-      <c r="B12" s="74" t="n"/>
-      <c r="C12" s="74" t="n"/>
-      <c r="D12" s="74" t="n"/>
-      <c r="E12" s="74" t="n"/>
-      <c r="F12" s="74" t="n"/>
-      <c r="G12" s="74" t="n"/>
-      <c r="H12" s="74" t="n"/>
-      <c r="I12" s="74" t="n"/>
-      <c r="J12" s="74" t="n"/>
-      <c r="K12" s="74" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="73" t="inlineStr">
-        <is>
-          <t>A3 — No unsupported / resolved dx billed</t>
-        </is>
-      </c>
-      <c r="B13" s="74" t="n"/>
-      <c r="C13" s="74" t="n"/>
-      <c r="D13" s="74" t="n"/>
-      <c r="E13" s="74" t="n"/>
-      <c r="F13" s="74" t="n"/>
-      <c r="G13" s="74" t="n"/>
-      <c r="H13" s="74" t="n"/>
-      <c r="I13" s="74" t="n"/>
-      <c r="J13" s="74" t="n"/>
-      <c r="K13" s="74" t="n"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="73" t="inlineStr">
-        <is>
-          <t>A4 — Problem list matches A&amp;P</t>
-        </is>
-      </c>
-      <c r="B14" s="74" t="n"/>
-      <c r="C14" s="74" t="n"/>
-      <c r="D14" s="74" t="n"/>
-      <c r="E14" s="74" t="n"/>
-      <c r="F14" s="74" t="n"/>
-      <c r="G14" s="74" t="n"/>
-      <c r="H14" s="74" t="n"/>
-      <c r="I14" s="74" t="n"/>
-      <c r="J14" s="74" t="n"/>
-      <c r="K14" s="74" t="n"/>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  B · Documentation Specificity   (25%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="73" t="inlineStr">
-        <is>
-          <t>B1 — ICD-10 at highest specificity</t>
-        </is>
-      </c>
-      <c r="B16" s="74" t="n"/>
-      <c r="C16" s="74" t="n"/>
-      <c r="D16" s="74" t="n"/>
-      <c r="E16" s="74" t="n"/>
-      <c r="F16" s="74" t="n"/>
-      <c r="G16" s="74" t="n"/>
-      <c r="H16" s="74" t="n"/>
-      <c r="I16" s="74" t="n"/>
-      <c r="J16" s="74" t="n"/>
-      <c r="K16" s="74" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="73" t="inlineStr">
-        <is>
-          <t>B2 — Diabetes: type + complications + control</t>
-        </is>
-      </c>
-      <c r="B17" s="74" t="n"/>
-      <c r="C17" s="74" t="n"/>
-      <c r="D17" s="74" t="n"/>
-      <c r="E17" s="74" t="n"/>
-      <c r="F17" s="74" t="n"/>
-      <c r="G17" s="74" t="n"/>
-      <c r="H17" s="74" t="n"/>
-      <c r="I17" s="74" t="n"/>
-      <c r="J17" s="74" t="n"/>
-      <c r="K17" s="74" t="n"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="73" t="inlineStr">
-        <is>
-          <t>B3 — S/O/A/P tell one consistent story</t>
-        </is>
-      </c>
-      <c r="B18" s="74" t="n"/>
-      <c r="C18" s="74" t="n"/>
-      <c r="D18" s="74" t="n"/>
-      <c r="E18" s="74" t="n"/>
-      <c r="F18" s="74" t="n"/>
-      <c r="G18" s="74" t="n"/>
-      <c r="H18" s="74" t="n"/>
-      <c r="I18" s="74" t="n"/>
-      <c r="J18" s="74" t="n"/>
-      <c r="K18" s="74" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="73" t="inlineStr">
-        <is>
-          <t>B4 — Note signed / dated / closed</t>
-        </is>
-      </c>
-      <c r="B19" s="74" t="n"/>
-      <c r="C19" s="74" t="n"/>
-      <c r="D19" s="74" t="n"/>
-      <c r="E19" s="74" t="n"/>
-      <c r="F19" s="74" t="n"/>
-      <c r="G19" s="74" t="n"/>
-      <c r="H19" s="74" t="n"/>
-      <c r="I19" s="74" t="n"/>
-      <c r="J19" s="74" t="n"/>
-      <c r="K19" s="74" t="n"/>
-    </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  C · SOAP Note Structure   (25%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="73" t="inlineStr">
-        <is>
-          <t>C1 — Subjective documented</t>
-        </is>
-      </c>
-      <c r="B21" s="74" t="n"/>
-      <c r="C21" s="74" t="n"/>
-      <c r="D21" s="74" t="n"/>
-      <c r="E21" s="74" t="n"/>
-      <c r="F21" s="74" t="n"/>
-      <c r="G21" s="74" t="n"/>
-      <c r="H21" s="74" t="n"/>
-      <c r="I21" s="74" t="n"/>
-      <c r="J21" s="74" t="n"/>
-      <c r="K21" s="74" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="73" t="inlineStr">
-        <is>
-          <t>C2 — Objective documented</t>
-        </is>
-      </c>
-      <c r="B22" s="74" t="n"/>
-      <c r="C22" s="74" t="n"/>
-      <c r="D22" s="74" t="n"/>
-      <c r="E22" s="74" t="n"/>
-      <c r="F22" s="74" t="n"/>
-      <c r="G22" s="74" t="n"/>
-      <c r="H22" s="74" t="n"/>
-      <c r="I22" s="74" t="n"/>
-      <c r="J22" s="74" t="n"/>
-      <c r="K22" s="74" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="73" t="inlineStr">
-        <is>
-          <t>C3 — Assessment (dx with reasoning)</t>
-        </is>
-      </c>
-      <c r="B23" s="74" t="n"/>
-      <c r="C23" s="74" t="n"/>
-      <c r="D23" s="74" t="n"/>
-      <c r="E23" s="74" t="n"/>
-      <c r="F23" s="74" t="n"/>
-      <c r="G23" s="74" t="n"/>
-      <c r="H23" s="74" t="n"/>
-      <c r="I23" s="74" t="n"/>
-      <c r="J23" s="74" t="n"/>
-      <c r="K23" s="74" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="73" t="inlineStr">
-        <is>
-          <t>C4 — Plan documented</t>
-        </is>
-      </c>
-      <c r="B24" s="74" t="n"/>
-      <c r="C24" s="74" t="n"/>
-      <c r="D24" s="74" t="n"/>
-      <c r="E24" s="74" t="n"/>
-      <c r="F24" s="74" t="n"/>
-      <c r="G24" s="74" t="n"/>
-      <c r="H24" s="74" t="n"/>
-      <c r="I24" s="74" t="n"/>
-      <c r="J24" s="74" t="n"/>
-      <c r="K24" s="74" t="n"/>
-    </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  D · HCC Capture   (10%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="73" t="inlineStr">
-        <is>
-          <t>D1 — Prior-year HCCs recaptured</t>
-        </is>
-      </c>
-      <c r="B26" s="74" t="n"/>
-      <c r="C26" s="74" t="n"/>
-      <c r="D26" s="74" t="n"/>
-      <c r="E26" s="74" t="n"/>
-      <c r="F26" s="74" t="n"/>
-      <c r="G26" s="74" t="n"/>
-      <c r="H26" s="74" t="n"/>
-      <c r="I26" s="74" t="n"/>
-      <c r="J26" s="74" t="n"/>
-      <c r="K26" s="74" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="73" t="inlineStr">
-        <is>
-          <t>D2 — Suspected chronic conditions captured</t>
-        </is>
-      </c>
-      <c r="B27" s="74" t="n"/>
-      <c r="C27" s="74" t="n"/>
-      <c r="D27" s="74" t="n"/>
-      <c r="E27" s="74" t="n"/>
-      <c r="F27" s="74" t="n"/>
-      <c r="G27" s="74" t="n"/>
-      <c r="H27" s="74" t="n"/>
-      <c r="I27" s="74" t="n"/>
-      <c r="J27" s="74" t="n"/>
-      <c r="K27" s="74" t="n"/>
-    </row>
-    <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  E · Documentation Supporting Quality Measures   (10%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="73" t="inlineStr">
-        <is>
-          <t>E1 — Screening values documented (score/number)</t>
-        </is>
-      </c>
-      <c r="B29" s="74" t="n"/>
-      <c r="C29" s="74" t="n"/>
-      <c r="D29" s="74" t="n"/>
-      <c r="E29" s="74" t="n"/>
-      <c r="F29" s="74" t="n"/>
-      <c r="G29" s="74" t="n"/>
-      <c r="H29" s="74" t="n"/>
-      <c r="I29" s="74" t="n"/>
-      <c r="J29" s="74" t="n"/>
-      <c r="K29" s="74" t="n"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="73" t="inlineStr">
-        <is>
-          <t>E2 — Follow-up plan when positive/abnormal</t>
-        </is>
-      </c>
-      <c r="B30" s="74" t="n"/>
-      <c r="C30" s="74" t="n"/>
-      <c r="D30" s="74" t="n"/>
-      <c r="E30" s="74" t="n"/>
-      <c r="F30" s="74" t="n"/>
-      <c r="G30" s="74" t="n"/>
-      <c r="H30" s="74" t="n"/>
-      <c r="I30" s="74" t="n"/>
-      <c r="J30" s="74" t="n"/>
-      <c r="K30" s="74" t="n"/>
-    </row>
-    <row r="32" ht="6" customHeight="1"/>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="75" t="inlineStr">
-        <is>
-          <t>SECTION SUBTOTALS</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="n"/>
-      <c r="C33" s="17" t="n"/>
-      <c r="D33" s="17" t="n"/>
-      <c r="E33" s="17" t="n"/>
-      <c r="F33" s="17" t="n"/>
-      <c r="G33" s="17" t="n"/>
-      <c r="H33" s="17" t="n"/>
-      <c r="I33" s="17" t="n"/>
-      <c r="J33" s="17" t="n"/>
-      <c r="K33" s="17" t="n"/>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  A · % Met  (weight 30%)</t>
-        </is>
-      </c>
-      <c r="B34" s="76">
-        <f>IFERROR((COUNTIF(B11:B14,"✓")+COUNTIF(B11:B14,"△")*0.5)/(COUNTIF(B11:B14,"✓")+COUNTIF(B11:B14,"△")+COUNTIF(B11:B14,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="C34" s="76">
-        <f>IFERROR((COUNTIF(C11:C14,"✓")+COUNTIF(C11:C14,"△")*0.5)/(COUNTIF(C11:C14,"✓")+COUNTIF(C11:C14,"△")+COUNTIF(C11:C14,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="D34" s="76">
-        <f>IFERROR((COUNTIF(D11:D14,"✓")+COUNTIF(D11:D14,"△")*0.5)/(COUNTIF(D11:D14,"✓")+COUNTIF(D11:D14,"△")+COUNTIF(D11:D14,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="E34" s="76">
-        <f>IFERROR((COUNTIF(E11:E14,"✓")+COUNTIF(E11:E14,"△")*0.5)/(COUNTIF(E11:E14,"✓")+COUNTIF(E11:E14,"△")+COUNTIF(E11:E14,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="F34" s="76">
-        <f>IFERROR((COUNTIF(F11:F14,"✓")+COUNTIF(F11:F14,"△")*0.5)/(COUNTIF(F11:F14,"✓")+COUNTIF(F11:F14,"△")+COUNTIF(F11:F14,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="G34" s="76">
-        <f>IFERROR((COUNTIF(G11:G14,"✓")+COUNTIF(G11:G14,"△")*0.5)/(COUNTIF(G11:G14,"✓")+COUNTIF(G11:G14,"△")+COUNTIF(G11:G14,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="76">
-        <f>IFERROR((COUNTIF(H11:H14,"✓")+COUNTIF(H11:H14,"△")*0.5)/(COUNTIF(H11:H14,"✓")+COUNTIF(H11:H14,"△")+COUNTIF(H11:H14,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="I34" s="76">
-        <f>IFERROR((COUNTIF(I11:I14,"✓")+COUNTIF(I11:I14,"△")*0.5)/(COUNTIF(I11:I14,"✓")+COUNTIF(I11:I14,"△")+COUNTIF(I11:I14,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="J34" s="76">
-        <f>IFERROR((COUNTIF(J11:J14,"✓")+COUNTIF(J11:J14,"△")*0.5)/(COUNTIF(J11:J14,"✓")+COUNTIF(J11:J14,"△")+COUNTIF(J11:J14,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="K34" s="76">
-        <f>IFERROR((COUNTIF(K11:K14,"✓")+COUNTIF(K11:K14,"△")*0.5)/(COUNTIF(K11:K14,"✓")+COUNTIF(K11:K14,"△")+COUNTIF(K11:K14,"✗")),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  B · % Met  (weight 25%)</t>
-        </is>
-      </c>
-      <c r="B35" s="76">
-        <f>IFERROR((COUNTIF(B16:B19,"✓")+COUNTIF(B16:B19,"△")*0.5)/(COUNTIF(B16:B19,"✓")+COUNTIF(B16:B19,"△")+COUNTIF(B16:B19,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="C35" s="76">
-        <f>IFERROR((COUNTIF(C16:C19,"✓")+COUNTIF(C16:C19,"△")*0.5)/(COUNTIF(C16:C19,"✓")+COUNTIF(C16:C19,"△")+COUNTIF(C16:C19,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="D35" s="76">
-        <f>IFERROR((COUNTIF(D16:D19,"✓")+COUNTIF(D16:D19,"△")*0.5)/(COUNTIF(D16:D19,"✓")+COUNTIF(D16:D19,"△")+COUNTIF(D16:D19,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="E35" s="76">
-        <f>IFERROR((COUNTIF(E16:E19,"✓")+COUNTIF(E16:E19,"△")*0.5)/(COUNTIF(E16:E19,"✓")+COUNTIF(E16:E19,"△")+COUNTIF(E16:E19,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="76">
-        <f>IFERROR((COUNTIF(F16:F19,"✓")+COUNTIF(F16:F19,"△")*0.5)/(COUNTIF(F16:F19,"✓")+COUNTIF(F16:F19,"△")+COUNTIF(F16:F19,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="G35" s="76">
-        <f>IFERROR((COUNTIF(G16:G19,"✓")+COUNTIF(G16:G19,"△")*0.5)/(COUNTIF(G16:G19,"✓")+COUNTIF(G16:G19,"△")+COUNTIF(G16:G19,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="76">
-        <f>IFERROR((COUNTIF(H16:H19,"✓")+COUNTIF(H16:H19,"△")*0.5)/(COUNTIF(H16:H19,"✓")+COUNTIF(H16:H19,"△")+COUNTIF(H16:H19,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="I35" s="76">
-        <f>IFERROR((COUNTIF(I16:I19,"✓")+COUNTIF(I16:I19,"△")*0.5)/(COUNTIF(I16:I19,"✓")+COUNTIF(I16:I19,"△")+COUNTIF(I16:I19,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="J35" s="76">
-        <f>IFERROR((COUNTIF(J16:J19,"✓")+COUNTIF(J16:J19,"△")*0.5)/(COUNTIF(J16:J19,"✓")+COUNTIF(J16:J19,"△")+COUNTIF(J16:J19,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="K35" s="76">
-        <f>IFERROR((COUNTIF(K16:K19,"✓")+COUNTIF(K16:K19,"△")*0.5)/(COUNTIF(K16:K19,"✓")+COUNTIF(K16:K19,"△")+COUNTIF(K16:K19,"✗")),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  C · % Met  (weight 25%)</t>
-        </is>
-      </c>
-      <c r="B36" s="76">
-        <f>IFERROR((COUNTIF(B21:B24,"✓")+COUNTIF(B21:B24,"△")*0.5)/(COUNTIF(B21:B24,"✓")+COUNTIF(B21:B24,"△")+COUNTIF(B21:B24,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="C36" s="76">
-        <f>IFERROR((COUNTIF(C21:C24,"✓")+COUNTIF(C21:C24,"△")*0.5)/(COUNTIF(C21:C24,"✓")+COUNTIF(C21:C24,"△")+COUNTIF(C21:C24,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="D36" s="76">
-        <f>IFERROR((COUNTIF(D21:D24,"✓")+COUNTIF(D21:D24,"△")*0.5)/(COUNTIF(D21:D24,"✓")+COUNTIF(D21:D24,"△")+COUNTIF(D21:D24,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="E36" s="76">
-        <f>IFERROR((COUNTIF(E21:E24,"✓")+COUNTIF(E21:E24,"△")*0.5)/(COUNTIF(E21:E24,"✓")+COUNTIF(E21:E24,"△")+COUNTIF(E21:E24,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="F36" s="76">
-        <f>IFERROR((COUNTIF(F21:F24,"✓")+COUNTIF(F21:F24,"△")*0.5)/(COUNTIF(F21:F24,"✓")+COUNTIF(F21:F24,"△")+COUNTIF(F21:F24,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="G36" s="76">
-        <f>IFERROR((COUNTIF(G21:G24,"✓")+COUNTIF(G21:G24,"△")*0.5)/(COUNTIF(G21:G24,"✓")+COUNTIF(G21:G24,"△")+COUNTIF(G21:G24,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="76">
-        <f>IFERROR((COUNTIF(H21:H24,"✓")+COUNTIF(H21:H24,"△")*0.5)/(COUNTIF(H21:H24,"✓")+COUNTIF(H21:H24,"△")+COUNTIF(H21:H24,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="I36" s="76">
-        <f>IFERROR((COUNTIF(I21:I24,"✓")+COUNTIF(I21:I24,"△")*0.5)/(COUNTIF(I21:I24,"✓")+COUNTIF(I21:I24,"△")+COUNTIF(I21:I24,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="J36" s="76">
-        <f>IFERROR((COUNTIF(J21:J24,"✓")+COUNTIF(J21:J24,"△")*0.5)/(COUNTIF(J21:J24,"✓")+COUNTIF(J21:J24,"△")+COUNTIF(J21:J24,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="K36" s="76">
-        <f>IFERROR((COUNTIF(K21:K24,"✓")+COUNTIF(K21:K24,"△")*0.5)/(COUNTIF(K21:K24,"✓")+COUNTIF(K21:K24,"△")+COUNTIF(K21:K24,"✗")),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  D · % Met  (weight 10%)</t>
-        </is>
-      </c>
-      <c r="B37" s="76">
-        <f>IFERROR((COUNTIF(B26:B27,"✓")+COUNTIF(B26:B27,"△")*0.5)/(COUNTIF(B26:B27,"✓")+COUNTIF(B26:B27,"△")+COUNTIF(B26:B27,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="C37" s="76">
-        <f>IFERROR((COUNTIF(C26:C27,"✓")+COUNTIF(C26:C27,"△")*0.5)/(COUNTIF(C26:C27,"✓")+COUNTIF(C26:C27,"△")+COUNTIF(C26:C27,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="D37" s="76">
-        <f>IFERROR((COUNTIF(D26:D27,"✓")+COUNTIF(D26:D27,"△")*0.5)/(COUNTIF(D26:D27,"✓")+COUNTIF(D26:D27,"△")+COUNTIF(D26:D27,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="E37" s="76">
-        <f>IFERROR((COUNTIF(E26:E27,"✓")+COUNTIF(E26:E27,"△")*0.5)/(COUNTIF(E26:E27,"✓")+COUNTIF(E26:E27,"△")+COUNTIF(E26:E27,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="F37" s="76">
-        <f>IFERROR((COUNTIF(F26:F27,"✓")+COUNTIF(F26:F27,"△")*0.5)/(COUNTIF(F26:F27,"✓")+COUNTIF(F26:F27,"△")+COUNTIF(F26:F27,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="G37" s="76">
-        <f>IFERROR((COUNTIF(G26:G27,"✓")+COUNTIF(G26:G27,"△")*0.5)/(COUNTIF(G26:G27,"✓")+COUNTIF(G26:G27,"△")+COUNTIF(G26:G27,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="76">
-        <f>IFERROR((COUNTIF(H26:H27,"✓")+COUNTIF(H26:H27,"△")*0.5)/(COUNTIF(H26:H27,"✓")+COUNTIF(H26:H27,"△")+COUNTIF(H26:H27,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="I37" s="76">
-        <f>IFERROR((COUNTIF(I26:I27,"✓")+COUNTIF(I26:I27,"△")*0.5)/(COUNTIF(I26:I27,"✓")+COUNTIF(I26:I27,"△")+COUNTIF(I26:I27,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="J37" s="76">
-        <f>IFERROR((COUNTIF(J26:J27,"✓")+COUNTIF(J26:J27,"△")*0.5)/(COUNTIF(J26:J27,"✓")+COUNTIF(J26:J27,"△")+COUNTIF(J26:J27,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="K37" s="76">
-        <f>IFERROR((COUNTIF(K26:K27,"✓")+COUNTIF(K26:K27,"△")*0.5)/(COUNTIF(K26:K27,"✓")+COUNTIF(K26:K27,"△")+COUNTIF(K26:K27,"✗")),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  E · % Met  (weight 10%)</t>
-        </is>
-      </c>
-      <c r="B38" s="76">
-        <f>IFERROR((COUNTIF(B29:B30,"✓")+COUNTIF(B29:B30,"△")*0.5)/(COUNTIF(B29:B30,"✓")+COUNTIF(B29:B30,"△")+COUNTIF(B29:B30,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="C38" s="76">
-        <f>IFERROR((COUNTIF(C29:C30,"✓")+COUNTIF(C29:C30,"△")*0.5)/(COUNTIF(C29:C30,"✓")+COUNTIF(C29:C30,"△")+COUNTIF(C29:C30,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="D38" s="76">
-        <f>IFERROR((COUNTIF(D29:D30,"✓")+COUNTIF(D29:D30,"△")*0.5)/(COUNTIF(D29:D30,"✓")+COUNTIF(D29:D30,"△")+COUNTIF(D29:D30,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="E38" s="76">
-        <f>IFERROR((COUNTIF(E29:E30,"✓")+COUNTIF(E29:E30,"△")*0.5)/(COUNTIF(E29:E30,"✓")+COUNTIF(E29:E30,"△")+COUNTIF(E29:E30,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="F38" s="76">
-        <f>IFERROR((COUNTIF(F29:F30,"✓")+COUNTIF(F29:F30,"△")*0.5)/(COUNTIF(F29:F30,"✓")+COUNTIF(F29:F30,"△")+COUNTIF(F29:F30,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="G38" s="76">
-        <f>IFERROR((COUNTIF(G29:G30,"✓")+COUNTIF(G29:G30,"△")*0.5)/(COUNTIF(G29:G30,"✓")+COUNTIF(G29:G30,"△")+COUNTIF(G29:G30,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="76">
-        <f>IFERROR((COUNTIF(H29:H30,"✓")+COUNTIF(H29:H30,"△")*0.5)/(COUNTIF(H29:H30,"✓")+COUNTIF(H29:H30,"△")+COUNTIF(H29:H30,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="I38" s="76">
-        <f>IFERROR((COUNTIF(I29:I30,"✓")+COUNTIF(I29:I30,"△")*0.5)/(COUNTIF(I29:I30,"✓")+COUNTIF(I29:I30,"△")+COUNTIF(I29:I30,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="J38" s="76">
-        <f>IFERROR((COUNTIF(J29:J30,"✓")+COUNTIF(J29:J30,"△")*0.5)/(COUNTIF(J29:J30,"✓")+COUNTIF(J29:J30,"△")+COUNTIF(J29:J30,"✗")),"")</f>
-        <v/>
-      </c>
-      <c r="K38" s="76">
-        <f>IFERROR((COUNTIF(K29:K30,"✓")+COUNTIF(K29:K30,"△")*0.5)/(COUNTIF(K29:K30,"✓")+COUNTIF(K29:K30,"△")+COUNTIF(K29:K30,"✗")),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="13" t="inlineStr">
-        <is>
-          <t>OVERALL COMPLIANCE %</t>
-        </is>
-      </c>
-      <c r="B40" s="77">
-        <f>IFERROR((IFERROR(B34,0)*IF(B34="",0,0.3)+IFERROR(B35,0)*IF(B35="",0,0.25)+IFERROR(B36,0)*IF(B36="",0,0.25)+IFERROR(B37,0)*IF(B37="",0,0.1)+IFERROR(B38,0)*IF(B38="",0,0.1))/(IF(B34="",0,0.3)+IF(B35="",0,0.25)+IF(B36="",0,0.25)+IF(B37="",0,0.1)+IF(B38="",0,0.1)),"")</f>
-        <v/>
-      </c>
-      <c r="C40" s="77">
-        <f>IFERROR((IFERROR(C34,0)*IF(C34="",0,0.3)+IFERROR(C35,0)*IF(C35="",0,0.25)+IFERROR(C36,0)*IF(C36="",0,0.25)+IFERROR(C37,0)*IF(C37="",0,0.1)+IFERROR(C38,0)*IF(C38="",0,0.1))/(IF(C34="",0,0.3)+IF(C35="",0,0.25)+IF(C36="",0,0.25)+IF(C37="",0,0.1)+IF(C38="",0,0.1)),"")</f>
-        <v/>
-      </c>
-      <c r="D40" s="77">
-        <f>IFERROR((IFERROR(D34,0)*IF(D34="",0,0.3)+IFERROR(D35,0)*IF(D35="",0,0.25)+IFERROR(D36,0)*IF(D36="",0,0.25)+IFERROR(D37,0)*IF(D37="",0,0.1)+IFERROR(D38,0)*IF(D38="",0,0.1))/(IF(D34="",0,0.3)+IF(D35="",0,0.25)+IF(D36="",0,0.25)+IF(D37="",0,0.1)+IF(D38="",0,0.1)),"")</f>
-        <v/>
-      </c>
-      <c r="E40" s="77">
-        <f>IFERROR((IFERROR(E34,0)*IF(E34="",0,0.3)+IFERROR(E35,0)*IF(E35="",0,0.25)+IFERROR(E36,0)*IF(E36="",0,0.25)+IFERROR(E37,0)*IF(E37="",0,0.1)+IFERROR(E38,0)*IF(E38="",0,0.1))/(IF(E34="",0,0.3)+IF(E35="",0,0.25)+IF(E36="",0,0.25)+IF(E37="",0,0.1)+IF(E38="",0,0.1)),"")</f>
-        <v/>
-      </c>
-      <c r="F40" s="77">
-        <f>IFERROR((IFERROR(F34,0)*IF(F34="",0,0.3)+IFERROR(F35,0)*IF(F35="",0,0.25)+IFERROR(F36,0)*IF(F36="",0,0.25)+IFERROR(F37,0)*IF(F37="",0,0.1)+IFERROR(F38,0)*IF(F38="",0,0.1))/(IF(F34="",0,0.3)+IF(F35="",0,0.25)+IF(F36="",0,0.25)+IF(F37="",0,0.1)+IF(F38="",0,0.1)),"")</f>
-        <v/>
-      </c>
-      <c r="G40" s="77">
-        <f>IFERROR((IFERROR(G34,0)*IF(G34="",0,0.3)+IFERROR(G35,0)*IF(G35="",0,0.25)+IFERROR(G36,0)*IF(G36="",0,0.25)+IFERROR(G37,0)*IF(G37="",0,0.1)+IFERROR(G38,0)*IF(G38="",0,0.1))/(IF(G34="",0,0.3)+IF(G35="",0,0.25)+IF(G36="",0,0.25)+IF(G37="",0,0.1)+IF(G38="",0,0.1)),"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="77">
-        <f>IFERROR((IFERROR(H34,0)*IF(H34="",0,0.3)+IFERROR(H35,0)*IF(H35="",0,0.25)+IFERROR(H36,0)*IF(H36="",0,0.25)+IFERROR(H37,0)*IF(H37="",0,0.1)+IFERROR(H38,0)*IF(H38="",0,0.1))/(IF(H34="",0,0.3)+IF(H35="",0,0.25)+IF(H36="",0,0.25)+IF(H37="",0,0.1)+IF(H38="",0,0.1)),"")</f>
-        <v/>
-      </c>
-      <c r="I40" s="77">
-        <f>IFERROR((IFERROR(I34,0)*IF(I34="",0,0.3)+IFERROR(I35,0)*IF(I35="",0,0.25)+IFERROR(I36,0)*IF(I36="",0,0.25)+IFERROR(I37,0)*IF(I37="",0,0.1)+IFERROR(I38,0)*IF(I38="",0,0.1))/(IF(I34="",0,0.3)+IF(I35="",0,0.25)+IF(I36="",0,0.25)+IF(I37="",0,0.1)+IF(I38="",0,0.1)),"")</f>
-        <v/>
-      </c>
-      <c r="J40" s="77">
-        <f>IFERROR((IFERROR(J34,0)*IF(J34="",0,0.3)+IFERROR(J35,0)*IF(J35="",0,0.25)+IFERROR(J36,0)*IF(J36="",0,0.25)+IFERROR(J37,0)*IF(J37="",0,0.1)+IFERROR(J38,0)*IF(J38="",0,0.1))/(IF(J34="",0,0.3)+IF(J35="",0,0.25)+IF(J36="",0,0.25)+IF(J37="",0,0.1)+IF(J38="",0,0.1)),"")</f>
-        <v/>
-      </c>
-      <c r="K40" s="77">
-        <f>IFERROR((IFERROR(K34,0)*IF(K34="",0,0.3)+IFERROR(K35,0)*IF(K35="",0,0.25)+IFERROR(K36,0)*IF(K36="",0,0.25)+IFERROR(K37,0)*IF(K37="",0,0.1)+IFERROR(K38,0)*IF(K38="",0,0.1))/(IF(K34="",0,0.3)+IF(K35="",0,0.25)+IF(K36="",0,0.25)+IF(K37="",0,0.1)+IF(K38="",0,0.1)),"")</f>
-        <v/>
-      </c>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>% Met</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Diagnosis Accuracy</t>
+        </is>
+      </c>
+      <c r="C38" s="36">
+        <f>COUNTIF(C10:C13,"✓ Met")+COUNTIF(C10:C13,"△ Partial")+COUNTIF(C10:C13,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D38" s="37">
+        <f>IFERROR(SUM(D10:D13)/C38,"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Specificity</t>
+        </is>
+      </c>
+      <c r="C39" s="36">
+        <f>COUNTIF(C16:C19,"✓ Met")+COUNTIF(C16:C19,"△ Partial")+COUNTIF(C16:C19,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D39" s="37">
+        <f>IFERROR(SUM(D16:D19)/C39,"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>SOAP Note Structure</t>
+        </is>
+      </c>
+      <c r="C40" s="36">
+        <f>COUNTIF(C22:C25,"✓ Met")+COUNTIF(C22:C25,"△ Partial")+COUNTIF(C22:C25,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D40" s="37">
+        <f>IFERROR(SUM(D22:D25)/C40,"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="14" t="inlineStr"/>
     </row>
     <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="40" t="inlineStr">
-        <is>
-          <t>RATING</t>
-        </is>
-      </c>
-      <c r="B41" s="78">
-        <f>IF(B40="","",IF(B40&gt;=0.95,"Excellent",IF(B40&gt;=0.9,"Meets",IF(B40&gt;=0.8,"Needs Impr","Corrective"))))</f>
-        <v/>
-      </c>
-      <c r="C41" s="78">
-        <f>IF(C40="","",IF(C40&gt;=0.95,"Excellent",IF(C40&gt;=0.9,"Meets",IF(C40&gt;=0.8,"Needs Impr","Corrective"))))</f>
-        <v/>
-      </c>
-      <c r="D41" s="78">
-        <f>IF(D40="","",IF(D40&gt;=0.95,"Excellent",IF(D40&gt;=0.9,"Meets",IF(D40&gt;=0.8,"Needs Impr","Corrective"))))</f>
-        <v/>
-      </c>
-      <c r="E41" s="78">
-        <f>IF(E40="","",IF(E40&gt;=0.95,"Excellent",IF(E40&gt;=0.9,"Meets",IF(E40&gt;=0.8,"Needs Impr","Corrective"))))</f>
-        <v/>
-      </c>
-      <c r="F41" s="78">
-        <f>IF(F40="","",IF(F40&gt;=0.95,"Excellent",IF(F40&gt;=0.9,"Meets",IF(F40&gt;=0.8,"Needs Impr","Corrective"))))</f>
-        <v/>
-      </c>
-      <c r="G41" s="78">
-        <f>IF(G40="","",IF(G40&gt;=0.95,"Excellent",IF(G40&gt;=0.9,"Meets",IF(G40&gt;=0.8,"Needs Impr","Corrective"))))</f>
-        <v/>
-      </c>
-      <c r="H41" s="78">
-        <f>IF(H40="","",IF(H40&gt;=0.95,"Excellent",IF(H40&gt;=0.9,"Meets",IF(H40&gt;=0.8,"Needs Impr","Corrective"))))</f>
-        <v/>
-      </c>
-      <c r="I41" s="78">
-        <f>IF(I40="","",IF(I40&gt;=0.95,"Excellent",IF(I40&gt;=0.9,"Meets",IF(I40&gt;=0.8,"Needs Impr","Corrective"))))</f>
-        <v/>
-      </c>
-      <c r="J41" s="78">
-        <f>IF(J40="","",IF(J40&gt;=0.95,"Excellent",IF(J40&gt;=0.9,"Meets",IF(J40&gt;=0.8,"Needs Impr","Corrective"))))</f>
-        <v/>
-      </c>
-      <c r="K41" s="78">
-        <f>IF(K40="","",IF(K40&gt;=0.95,"Excellent",IF(K40&gt;=0.9,"Meets",IF(K40&gt;=0.8,"Needs Impr","Corrective"))))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43" ht="6" customHeight="1"/>
-    <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  BATCH SUMMARY (this month)</t>
-        </is>
-      </c>
-      <c r="B44" s="17" t="n"/>
-      <c r="C44" s="17" t="n"/>
-      <c r="D44" s="17" t="n"/>
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>HCC Capture</t>
+        </is>
+      </c>
+      <c r="C41" s="36">
+        <f>COUNTIF(C28:C29,"✓ Met")+COUNTIF(C28:C29,"△ Partial")+COUNTIF(C28:C29,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D41" s="37">
+        <f>IFERROR(SUM(D28:D29)/C41,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Supporting Quality Measures</t>
+        </is>
+      </c>
+      <c r="C42" s="36">
+        <f>COUNTIF(C32:C33,"✓ Met")+COUNTIF(C32:C33,"△ Partial")+COUNTIF(C32:C33,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D42" s="37">
+        <f>IFERROR(SUM(D32:D33)/C42,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OVERALL COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="D44" s="39">
+        <f>IFERROR(SUMPRODUCT(D38:D42,C38:C42)/SUM(C38:C42),"")</f>
+        <v/>
+      </c>
       <c r="E44" s="17" t="n"/>
     </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Claims audited</t>
-        </is>
-      </c>
-      <c r="D45" s="79">
-        <f>COUNT(B40:K40)</f>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PERFORMANCE BAND</t>
+        </is>
+      </c>
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="18">
+        <f>IF(D44="","",IF(D44&gt;=0.95,"Excellent",IF(D44&gt;=0.90,"Meets Expectations",IF(D44&gt;=0.80,"Needs Improvement","Corrective Education Required"))))</f>
         <v/>
       </c>
       <c r="E45" s="14" t="n"/>
     </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Average compliance %</t>
-        </is>
-      </c>
-      <c r="D46" s="80">
-        <f>IFERROR(AVERAGE(B40:K40),"")</f>
-        <v/>
-      </c>
-      <c r="E46" s="14" t="n"/>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Charts scoring Meets+ (≥90%)</t>
-        </is>
-      </c>
-      <c r="D47" s="79">
-        <f>COUNTIF(B40:K40,"&gt;=0.9")</f>
-        <v/>
-      </c>
-      <c r="E47" s="14" t="n"/>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Charts needing Corrective (&lt;80%)</t>
-        </is>
-      </c>
-      <c r="D48" s="79">
-        <f>COUNTIFS(B40:K40,"&lt;0.8",B40:K40,"&gt;0")</f>
-        <v/>
-      </c>
-      <c r="E48" s="14" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A20:K20"/>
+  <mergeCells count="11">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A2:E2"/>
     <mergeCell ref="A45:C45"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A15:K15"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A27:E27"/>
   </mergeCells>
-  <conditionalFormatting sqref="B11:B30">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>B11="✓"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
-      <formula>B11="△"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
-      <formula>B11="✗"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
-      <formula>B11="N/A"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C11:C30">
-    <cfRule type="expression" priority="5" dxfId="0">
-      <formula>C11="✓"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="6" dxfId="1">
-      <formula>C11="△"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="7" dxfId="2">
-      <formula>C11="✗"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="8" dxfId="3">
-      <formula>C11="N/A"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D11:D30">
-    <cfRule type="expression" priority="9" dxfId="0">
-      <formula>D11="✓"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="10" dxfId="1">
-      <formula>D11="△"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="11" dxfId="2">
-      <formula>D11="✗"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="12" dxfId="3">
-      <formula>D11="N/A"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E11:E30">
-    <cfRule type="expression" priority="13" dxfId="0">
-      <formula>E11="✓"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="14" dxfId="1">
-      <formula>E11="△"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="15" dxfId="2">
-      <formula>E11="✗"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="16" dxfId="3">
-      <formula>E11="N/A"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F11:F30">
-    <cfRule type="expression" priority="17" dxfId="0">
-      <formula>F11="✓"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="18" dxfId="1">
-      <formula>F11="△"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="19" dxfId="2">
-      <formula>F11="✗"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="20" dxfId="3">
-      <formula>F11="N/A"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11:G30">
-    <cfRule type="expression" priority="21" dxfId="0">
-      <formula>G11="✓"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="22" dxfId="1">
-      <formula>G11="△"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="23" dxfId="2">
-      <formula>G11="✗"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="24" dxfId="3">
-      <formula>G11="N/A"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11:H30">
-    <cfRule type="expression" priority="25" dxfId="0">
-      <formula>H11="✓"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="26" dxfId="1">
-      <formula>H11="△"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="27" dxfId="2">
-      <formula>H11="✗"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="28" dxfId="3">
-      <formula>H11="N/A"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I30">
-    <cfRule type="expression" priority="29" dxfId="0">
-      <formula>I11="✓"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="30" dxfId="1">
-      <formula>I11="△"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="31" dxfId="2">
-      <formula>I11="✗"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="32" dxfId="3">
-      <formula>I11="N/A"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J11:J30">
-    <cfRule type="expression" priority="33" dxfId="0">
-      <formula>J11="✓"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="34" dxfId="1">
-      <formula>J11="△"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="35" dxfId="2">
-      <formula>J11="✗"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="36" dxfId="3">
-      <formula>J11="N/A"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K11:K30">
-    <cfRule type="expression" priority="37" dxfId="0">
-      <formula>K11="✓"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="38" dxfId="1">
-      <formula>K11="△"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="39" dxfId="2">
-      <formula>K11="✗"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="40" dxfId="3">
-      <formula>K11="N/A"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B34:K34">
-    <cfRule type="cellIs" priority="41" operator="greaterThanOrEqual" dxfId="0">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="42" operator="between" dxfId="1">
-      <formula>0.8</formula>
-      <formula>0.8999</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="43" operator="between" dxfId="2">
-      <formula>0.0001</formula>
-      <formula>0.7999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B35:K35">
-    <cfRule type="cellIs" priority="44" operator="greaterThanOrEqual" dxfId="0">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="45" operator="between" dxfId="1">
-      <formula>0.8</formula>
-      <formula>0.8999</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="46" operator="between" dxfId="2">
-      <formula>0.0001</formula>
-      <formula>0.7999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B36:K36">
-    <cfRule type="cellIs" priority="47" operator="greaterThanOrEqual" dxfId="0">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="48" operator="between" dxfId="1">
-      <formula>0.8</formula>
-      <formula>0.8999</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="49" operator="between" dxfId="2">
-      <formula>0.0001</formula>
-      <formula>0.7999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B37:K37">
-    <cfRule type="cellIs" priority="50" operator="greaterThanOrEqual" dxfId="0">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="51" operator="between" dxfId="1">
-      <formula>0.8</formula>
-      <formula>0.8999</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="52" operator="between" dxfId="2">
-      <formula>0.0001</formula>
-      <formula>0.7999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38:K38">
-    <cfRule type="cellIs" priority="53" operator="greaterThanOrEqual" dxfId="0">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="54" operator="between" dxfId="1">
-      <formula>0.8</formula>
-      <formula>0.8999</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="55" operator="between" dxfId="2">
-      <formula>0.0001</formula>
-      <formula>0.7999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B40:K40">
-    <cfRule type="cellIs" priority="56" operator="greaterThanOrEqual" dxfId="3">
-      <formula>0.95</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="57" operator="between" dxfId="0">
-      <formula>0.9</formula>
-      <formula>0.9499</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="58" operator="between" dxfId="1">
-      <formula>0.8</formula>
-      <formula>0.8999</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="59" operator="between" dxfId="2">
-      <formula>0.0001</formula>
-      <formula>0.7999</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B41:K41">
-    <cfRule type="expression" priority="60" dxfId="3">
-      <formula>B41="Excellent"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="61" dxfId="0">
-      <formula>B41="Meets"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="62" dxfId="1">
-      <formula>B41="Needs Impr"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="63" dxfId="2">
-      <formula>B41="Corrective"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation sqref="B7:K7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Diabetes,Chronic Kidney Disease,Annual Wellness Visit,High RAF Patient,Random Selection"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B8:K8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Medicare Advantage,Commercial,Medicaid,Dual"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B11:K30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,△,✗,N/A"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001E7A6E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Clinical Documentation Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>One chart per sheet · tick each item · scoring &amp; rating are automatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>Provider:</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Date of Service:</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>How to use
+1. Fill in the yellow cells at top
+2. Rate each element (dropdown in column C)
+3. Overall % + Rating appear at the bottom
+4. Log the chart on the Audit Log tab when done</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Claim Number:</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Auditor:</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="51" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Category:</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Payer:</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="52" t="n"/>
+    </row>
+    <row r="7" ht="12" customHeight="1"/>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Documentation element</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Pts</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A · Diagnosis Accuracy   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>All reported diagnoses are clinically supported in the note</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="33">
+        <f>IF(C10="✓ Met",1,IF(C10="△ Partial",0.5,IF(C10="✗ Not Met",0,IF(C10="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Chronic conditions actively addressed at this visit (not just carried forward)</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="33">
+        <f>IF(C11="✓ Met",1,IF(C11="△ Partial",0.5,IF(C11="✗ Not Met",0,IF(C11="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>No unsupported or resolved conditions billed as active</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="33">
+        <f>IF(C12="✓ Met",1,IF(C12="△ Partial",0.5,IF(C12="✗ Not Met",0,IF(C12="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Problem list matches today's assessment &amp; plan</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="33">
+        <f>IF(C13="✓ Met",1,IF(C13="△ Partial",0.5,IF(C13="✗ Not Met",0,IF(C13="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B · Documentation Specificity   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>ICD-10 codes at highest available specificity (avoid 'unspecified')</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="33">
+        <f>IF(C16="✓ Met",1,IF(C16="△ Partial",0.5,IF(C16="✗ Not Met",0,IF(C16="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes: type + complications + control specified</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="33">
+        <f>IF(C17="✓ Met",1,IF(C17="△ Partial",0.5,IF(C17="✗ Not Met",0,IF(C17="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>S / O / A / P sections tell one consistent clinical story</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="33">
+        <f>IF(C18="✓ Met",1,IF(C18="△ Partial",0.5,IF(C18="✗ Not Met",0,IF(C18="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Note signed, dated, and closed by the rendering provider</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="33">
+        <f>IF(C19="✓ Met",1,IF(C19="△ Partial",0.5,IF(C19="✗ Not Met",0,IF(C19="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C · SOAP Note Structure   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Subjective — patient's history, symptoms, and concerns clearly documented</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="33">
+        <f>IF(C22="✓ Met",1,IF(C22="△ Partial",0.5,IF(C22="✗ Not Met",0,IF(C22="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Objective — exam findings, vitals, and relevant test results documented</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="33">
+        <f>IF(C23="✓ Met",1,IF(C23="△ Partial",0.5,IF(C23="✗ Not Met",0,IF(C23="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Assessment — each diagnosis explicitly assessed with clinical reasoning</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="33">
+        <f>IF(C24="✓ Met",1,IF(C24="△ Partial",0.5,IF(C24="✗ Not Met",0,IF(C24="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Plan — treatment plan documented (medication / referral / testing / follow-up)</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="33">
+        <f>IF(C25="✓ Met",1,IF(C25="△ Partial",0.5,IF(C25="✗ Not Met",0,IF(C25="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D · HCC Capture   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Prior-year HCCs recaptured (or explicitly resolved with rationale)</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="33">
+        <f>IF(C28="✓ Met",1,IF(C28="△ Partial",0.5,IF(C28="✗ Not Met",0,IF(C28="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Suspected undocumented chronic conditions captured with support</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="33">
+        <f>IF(C29="✓ Met",1,IF(C29="△ Partial",0.5,IF(C29="✗ Not Met",0,IF(C29="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E · Documentation Supporting Quality Measures   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Screening / measure results documented with specific values (PHQ-9, GAD-7, BMI, BP, HbA1c) — not just 'screened' or 'normal'</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="33">
+        <f>IF(C32="✓ Met",1,IF(C32="△ Partial",0.5,IF(C32="✗ Not Met",0,IF(C32="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Follow-up plan documented when a screening is positive or a result is abnormal (positive PHQ-9 → depression plan; elevated BMI → nutrition counseling)</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33">
+        <f>IF(C33="✓ Met",1,IF(C33="△ Partial",0.5,IF(C33="✗ Not Met",0,IF(C33="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>% Met</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Diagnosis Accuracy</t>
+        </is>
+      </c>
+      <c r="C38" s="36">
+        <f>COUNTIF(C10:C13,"✓ Met")+COUNTIF(C10:C13,"△ Partial")+COUNTIF(C10:C13,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D38" s="37">
+        <f>IFERROR(SUM(D10:D13)/C38,"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Specificity</t>
+        </is>
+      </c>
+      <c r="C39" s="36">
+        <f>COUNTIF(C16:C19,"✓ Met")+COUNTIF(C16:C19,"△ Partial")+COUNTIF(C16:C19,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D39" s="37">
+        <f>IFERROR(SUM(D16:D19)/C39,"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>SOAP Note Structure</t>
+        </is>
+      </c>
+      <c r="C40" s="36">
+        <f>COUNTIF(C22:C25,"✓ Met")+COUNTIF(C22:C25,"△ Partial")+COUNTIF(C22:C25,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D40" s="37">
+        <f>IFERROR(SUM(D22:D25)/C40,"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>HCC Capture</t>
+        </is>
+      </c>
+      <c r="C41" s="36">
+        <f>COUNTIF(C28:C29,"✓ Met")+COUNTIF(C28:C29,"△ Partial")+COUNTIF(C28:C29,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D41" s="37">
+        <f>IFERROR(SUM(D28:D29)/C41,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Supporting Quality Measures</t>
+        </is>
+      </c>
+      <c r="C42" s="36">
+        <f>COUNTIF(C32:C33,"✓ Met")+COUNTIF(C32:C33,"△ Partial")+COUNTIF(C32:C33,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D42" s="37">
+        <f>IFERROR(SUM(D32:D33)/C42,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OVERALL COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="D44" s="39">
+        <f>IFERROR(SUMPRODUCT(D38:D42,C38:C42)/SUM(C38:C42),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PERFORMANCE BAND</t>
+        </is>
+      </c>
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="18">
+        <f>IF(D44="","",IF(D44&gt;=0.95,"Excellent",IF(D44&gt;=0.90,"Meets Expectations",IF(D44&gt;=0.80,"Needs Improvement","Corrective Education Required"))))</f>
+        <v/>
+      </c>
+      <c r="E45" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001E40AF"/>
@@ -5773,7 +5846,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00334155"/>
@@ -6534,7 +6607,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00B45309"/>
@@ -7112,4 +7185,4900 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001E7A6E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Clinical Documentation Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>One chart per sheet · tick each item · scoring &amp; rating are automatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>Provider:</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Date of Service:</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>How to use
+1. Fill in the yellow cells at top
+2. Rate each element (dropdown in column C)
+3. Overall % + Rating appear at the bottom
+4. Log the chart on the Audit Log tab when done</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Claim Number:</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Auditor:</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="51" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Category:</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Payer:</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="52" t="n"/>
+    </row>
+    <row r="7" ht="12" customHeight="1"/>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Documentation element</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Pts</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A · Diagnosis Accuracy   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>All reported diagnoses are clinically supported in the note</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="33">
+        <f>IF(C10="✓ Met",1,IF(C10="△ Partial",0.5,IF(C10="✗ Not Met",0,IF(C10="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Chronic conditions actively addressed at this visit (not just carried forward)</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="33">
+        <f>IF(C11="✓ Met",1,IF(C11="△ Partial",0.5,IF(C11="✗ Not Met",0,IF(C11="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>No unsupported or resolved conditions billed as active</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="33">
+        <f>IF(C12="✓ Met",1,IF(C12="△ Partial",0.5,IF(C12="✗ Not Met",0,IF(C12="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Problem list matches today's assessment &amp; plan</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="33">
+        <f>IF(C13="✓ Met",1,IF(C13="△ Partial",0.5,IF(C13="✗ Not Met",0,IF(C13="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B · Documentation Specificity   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>ICD-10 codes at highest available specificity (avoid 'unspecified')</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="33">
+        <f>IF(C16="✓ Met",1,IF(C16="△ Partial",0.5,IF(C16="✗ Not Met",0,IF(C16="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes: type + complications + control specified</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="33">
+        <f>IF(C17="✓ Met",1,IF(C17="△ Partial",0.5,IF(C17="✗ Not Met",0,IF(C17="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>S / O / A / P sections tell one consistent clinical story</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="33">
+        <f>IF(C18="✓ Met",1,IF(C18="△ Partial",0.5,IF(C18="✗ Not Met",0,IF(C18="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Note signed, dated, and closed by the rendering provider</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="33">
+        <f>IF(C19="✓ Met",1,IF(C19="△ Partial",0.5,IF(C19="✗ Not Met",0,IF(C19="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C · SOAP Note Structure   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Subjective — patient's history, symptoms, and concerns clearly documented</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="33">
+        <f>IF(C22="✓ Met",1,IF(C22="△ Partial",0.5,IF(C22="✗ Not Met",0,IF(C22="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Objective — exam findings, vitals, and relevant test results documented</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="33">
+        <f>IF(C23="✓ Met",1,IF(C23="△ Partial",0.5,IF(C23="✗ Not Met",0,IF(C23="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Assessment — each diagnosis explicitly assessed with clinical reasoning</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="33">
+        <f>IF(C24="✓ Met",1,IF(C24="△ Partial",0.5,IF(C24="✗ Not Met",0,IF(C24="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Plan — treatment plan documented (medication / referral / testing / follow-up)</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="33">
+        <f>IF(C25="✓ Met",1,IF(C25="△ Partial",0.5,IF(C25="✗ Not Met",0,IF(C25="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D · HCC Capture   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Prior-year HCCs recaptured (or explicitly resolved with rationale)</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="33">
+        <f>IF(C28="✓ Met",1,IF(C28="△ Partial",0.5,IF(C28="✗ Not Met",0,IF(C28="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Suspected undocumented chronic conditions captured with support</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="33">
+        <f>IF(C29="✓ Met",1,IF(C29="△ Partial",0.5,IF(C29="✗ Not Met",0,IF(C29="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E · Documentation Supporting Quality Measures   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Screening / measure results documented with specific values (PHQ-9, GAD-7, BMI, BP, HbA1c) — not just 'screened' or 'normal'</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="33">
+        <f>IF(C32="✓ Met",1,IF(C32="△ Partial",0.5,IF(C32="✗ Not Met",0,IF(C32="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Follow-up plan documented when a screening is positive or a result is abnormal (positive PHQ-9 → depression plan; elevated BMI → nutrition counseling)</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33">
+        <f>IF(C33="✓ Met",1,IF(C33="△ Partial",0.5,IF(C33="✗ Not Met",0,IF(C33="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>% Met</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Diagnosis Accuracy</t>
+        </is>
+      </c>
+      <c r="C38" s="36">
+        <f>COUNTIF(C10:C13,"✓ Met")+COUNTIF(C10:C13,"△ Partial")+COUNTIF(C10:C13,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D38" s="37">
+        <f>IFERROR(SUM(D10:D13)/C38,"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Specificity</t>
+        </is>
+      </c>
+      <c r="C39" s="36">
+        <f>COUNTIF(C16:C19,"✓ Met")+COUNTIF(C16:C19,"△ Partial")+COUNTIF(C16:C19,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D39" s="37">
+        <f>IFERROR(SUM(D16:D19)/C39,"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>SOAP Note Structure</t>
+        </is>
+      </c>
+      <c r="C40" s="36">
+        <f>COUNTIF(C22:C25,"✓ Met")+COUNTIF(C22:C25,"△ Partial")+COUNTIF(C22:C25,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D40" s="37">
+        <f>IFERROR(SUM(D22:D25)/C40,"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>HCC Capture</t>
+        </is>
+      </c>
+      <c r="C41" s="36">
+        <f>COUNTIF(C28:C29,"✓ Met")+COUNTIF(C28:C29,"△ Partial")+COUNTIF(C28:C29,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D41" s="37">
+        <f>IFERROR(SUM(D28:D29)/C41,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Supporting Quality Measures</t>
+        </is>
+      </c>
+      <c r="C42" s="36">
+        <f>COUNTIF(C32:C33,"✓ Met")+COUNTIF(C32:C33,"△ Partial")+COUNTIF(C32:C33,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D42" s="37">
+        <f>IFERROR(SUM(D32:D33)/C42,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OVERALL COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="D44" s="39">
+        <f>IFERROR(SUMPRODUCT(D38:D42,C38:C42)/SUM(C38:C42),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PERFORMANCE BAND</t>
+        </is>
+      </c>
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="18">
+        <f>IF(D44="","",IF(D44&gt;=0.95,"Excellent",IF(D44&gt;=0.90,"Meets Expectations",IF(D44&gt;=0.80,"Needs Improvement","Corrective Education Required"))))</f>
+        <v/>
+      </c>
+      <c r="E45" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001E7A6E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Clinical Documentation Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>One chart per sheet · tick each item · scoring &amp; rating are automatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>Provider:</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Date of Service:</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>How to use
+1. Fill in the yellow cells at top
+2. Rate each element (dropdown in column C)
+3. Overall % + Rating appear at the bottom
+4. Log the chart on the Audit Log tab when done</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Claim Number:</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Auditor:</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="51" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Category:</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Payer:</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="52" t="n"/>
+    </row>
+    <row r="7" ht="12" customHeight="1"/>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Documentation element</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Pts</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A · Diagnosis Accuracy   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>All reported diagnoses are clinically supported in the note</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="33">
+        <f>IF(C10="✓ Met",1,IF(C10="△ Partial",0.5,IF(C10="✗ Not Met",0,IF(C10="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Chronic conditions actively addressed at this visit (not just carried forward)</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="33">
+        <f>IF(C11="✓ Met",1,IF(C11="△ Partial",0.5,IF(C11="✗ Not Met",0,IF(C11="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>No unsupported or resolved conditions billed as active</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="33">
+        <f>IF(C12="✓ Met",1,IF(C12="△ Partial",0.5,IF(C12="✗ Not Met",0,IF(C12="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Problem list matches today's assessment &amp; plan</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="33">
+        <f>IF(C13="✓ Met",1,IF(C13="△ Partial",0.5,IF(C13="✗ Not Met",0,IF(C13="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B · Documentation Specificity   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>ICD-10 codes at highest available specificity (avoid 'unspecified')</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="33">
+        <f>IF(C16="✓ Met",1,IF(C16="△ Partial",0.5,IF(C16="✗ Not Met",0,IF(C16="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes: type + complications + control specified</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="33">
+        <f>IF(C17="✓ Met",1,IF(C17="△ Partial",0.5,IF(C17="✗ Not Met",0,IF(C17="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>S / O / A / P sections tell one consistent clinical story</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="33">
+        <f>IF(C18="✓ Met",1,IF(C18="△ Partial",0.5,IF(C18="✗ Not Met",0,IF(C18="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Note signed, dated, and closed by the rendering provider</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="33">
+        <f>IF(C19="✓ Met",1,IF(C19="△ Partial",0.5,IF(C19="✗ Not Met",0,IF(C19="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C · SOAP Note Structure   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Subjective — patient's history, symptoms, and concerns clearly documented</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="33">
+        <f>IF(C22="✓ Met",1,IF(C22="△ Partial",0.5,IF(C22="✗ Not Met",0,IF(C22="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Objective — exam findings, vitals, and relevant test results documented</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="33">
+        <f>IF(C23="✓ Met",1,IF(C23="△ Partial",0.5,IF(C23="✗ Not Met",0,IF(C23="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Assessment — each diagnosis explicitly assessed with clinical reasoning</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="33">
+        <f>IF(C24="✓ Met",1,IF(C24="△ Partial",0.5,IF(C24="✗ Not Met",0,IF(C24="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Plan — treatment plan documented (medication / referral / testing / follow-up)</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="33">
+        <f>IF(C25="✓ Met",1,IF(C25="△ Partial",0.5,IF(C25="✗ Not Met",0,IF(C25="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D · HCC Capture   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Prior-year HCCs recaptured (or explicitly resolved with rationale)</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="33">
+        <f>IF(C28="✓ Met",1,IF(C28="△ Partial",0.5,IF(C28="✗ Not Met",0,IF(C28="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Suspected undocumented chronic conditions captured with support</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="33">
+        <f>IF(C29="✓ Met",1,IF(C29="△ Partial",0.5,IF(C29="✗ Not Met",0,IF(C29="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E · Documentation Supporting Quality Measures   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Screening / measure results documented with specific values (PHQ-9, GAD-7, BMI, BP, HbA1c) — not just 'screened' or 'normal'</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="33">
+        <f>IF(C32="✓ Met",1,IF(C32="△ Partial",0.5,IF(C32="✗ Not Met",0,IF(C32="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Follow-up plan documented when a screening is positive or a result is abnormal (positive PHQ-9 → depression plan; elevated BMI → nutrition counseling)</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33">
+        <f>IF(C33="✓ Met",1,IF(C33="△ Partial",0.5,IF(C33="✗ Not Met",0,IF(C33="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>% Met</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Diagnosis Accuracy</t>
+        </is>
+      </c>
+      <c r="C38" s="36">
+        <f>COUNTIF(C10:C13,"✓ Met")+COUNTIF(C10:C13,"△ Partial")+COUNTIF(C10:C13,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D38" s="37">
+        <f>IFERROR(SUM(D10:D13)/C38,"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Specificity</t>
+        </is>
+      </c>
+      <c r="C39" s="36">
+        <f>COUNTIF(C16:C19,"✓ Met")+COUNTIF(C16:C19,"△ Partial")+COUNTIF(C16:C19,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D39" s="37">
+        <f>IFERROR(SUM(D16:D19)/C39,"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>SOAP Note Structure</t>
+        </is>
+      </c>
+      <c r="C40" s="36">
+        <f>COUNTIF(C22:C25,"✓ Met")+COUNTIF(C22:C25,"△ Partial")+COUNTIF(C22:C25,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D40" s="37">
+        <f>IFERROR(SUM(D22:D25)/C40,"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>HCC Capture</t>
+        </is>
+      </c>
+      <c r="C41" s="36">
+        <f>COUNTIF(C28:C29,"✓ Met")+COUNTIF(C28:C29,"△ Partial")+COUNTIF(C28:C29,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D41" s="37">
+        <f>IFERROR(SUM(D28:D29)/C41,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Supporting Quality Measures</t>
+        </is>
+      </c>
+      <c r="C42" s="36">
+        <f>COUNTIF(C32:C33,"✓ Met")+COUNTIF(C32:C33,"△ Partial")+COUNTIF(C32:C33,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D42" s="37">
+        <f>IFERROR(SUM(D32:D33)/C42,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OVERALL COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="D44" s="39">
+        <f>IFERROR(SUMPRODUCT(D38:D42,C38:C42)/SUM(C38:C42),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PERFORMANCE BAND</t>
+        </is>
+      </c>
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="18">
+        <f>IF(D44="","",IF(D44&gt;=0.95,"Excellent",IF(D44&gt;=0.90,"Meets Expectations",IF(D44&gt;=0.80,"Needs Improvement","Corrective Education Required"))))</f>
+        <v/>
+      </c>
+      <c r="E45" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001E7A6E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Clinical Documentation Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>One chart per sheet · tick each item · scoring &amp; rating are automatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>Provider:</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Date of Service:</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>How to use
+1. Fill in the yellow cells at top
+2. Rate each element (dropdown in column C)
+3. Overall % + Rating appear at the bottom
+4. Log the chart on the Audit Log tab when done</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Claim Number:</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Auditor:</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="51" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Category:</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Payer:</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="52" t="n"/>
+    </row>
+    <row r="7" ht="12" customHeight="1"/>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Documentation element</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Pts</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A · Diagnosis Accuracy   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>All reported diagnoses are clinically supported in the note</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="33">
+        <f>IF(C10="✓ Met",1,IF(C10="△ Partial",0.5,IF(C10="✗ Not Met",0,IF(C10="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Chronic conditions actively addressed at this visit (not just carried forward)</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="33">
+        <f>IF(C11="✓ Met",1,IF(C11="△ Partial",0.5,IF(C11="✗ Not Met",0,IF(C11="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>No unsupported or resolved conditions billed as active</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="33">
+        <f>IF(C12="✓ Met",1,IF(C12="△ Partial",0.5,IF(C12="✗ Not Met",0,IF(C12="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Problem list matches today's assessment &amp; plan</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="33">
+        <f>IF(C13="✓ Met",1,IF(C13="△ Partial",0.5,IF(C13="✗ Not Met",0,IF(C13="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B · Documentation Specificity   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>ICD-10 codes at highest available specificity (avoid 'unspecified')</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="33">
+        <f>IF(C16="✓ Met",1,IF(C16="△ Partial",0.5,IF(C16="✗ Not Met",0,IF(C16="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes: type + complications + control specified</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="33">
+        <f>IF(C17="✓ Met",1,IF(C17="△ Partial",0.5,IF(C17="✗ Not Met",0,IF(C17="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>S / O / A / P sections tell one consistent clinical story</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="33">
+        <f>IF(C18="✓ Met",1,IF(C18="△ Partial",0.5,IF(C18="✗ Not Met",0,IF(C18="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Note signed, dated, and closed by the rendering provider</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="33">
+        <f>IF(C19="✓ Met",1,IF(C19="△ Partial",0.5,IF(C19="✗ Not Met",0,IF(C19="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C · SOAP Note Structure   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Subjective — patient's history, symptoms, and concerns clearly documented</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="33">
+        <f>IF(C22="✓ Met",1,IF(C22="△ Partial",0.5,IF(C22="✗ Not Met",0,IF(C22="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Objective — exam findings, vitals, and relevant test results documented</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="33">
+        <f>IF(C23="✓ Met",1,IF(C23="△ Partial",0.5,IF(C23="✗ Not Met",0,IF(C23="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Assessment — each diagnosis explicitly assessed with clinical reasoning</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="33">
+        <f>IF(C24="✓ Met",1,IF(C24="△ Partial",0.5,IF(C24="✗ Not Met",0,IF(C24="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Plan — treatment plan documented (medication / referral / testing / follow-up)</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="33">
+        <f>IF(C25="✓ Met",1,IF(C25="△ Partial",0.5,IF(C25="✗ Not Met",0,IF(C25="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D · HCC Capture   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Prior-year HCCs recaptured (or explicitly resolved with rationale)</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="33">
+        <f>IF(C28="✓ Met",1,IF(C28="△ Partial",0.5,IF(C28="✗ Not Met",0,IF(C28="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Suspected undocumented chronic conditions captured with support</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="33">
+        <f>IF(C29="✓ Met",1,IF(C29="△ Partial",0.5,IF(C29="✗ Not Met",0,IF(C29="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E · Documentation Supporting Quality Measures   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Screening / measure results documented with specific values (PHQ-9, GAD-7, BMI, BP, HbA1c) — not just 'screened' or 'normal'</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="33">
+        <f>IF(C32="✓ Met",1,IF(C32="△ Partial",0.5,IF(C32="✗ Not Met",0,IF(C32="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Follow-up plan documented when a screening is positive or a result is abnormal (positive PHQ-9 → depression plan; elevated BMI → nutrition counseling)</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33">
+        <f>IF(C33="✓ Met",1,IF(C33="△ Partial",0.5,IF(C33="✗ Not Met",0,IF(C33="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>% Met</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Diagnosis Accuracy</t>
+        </is>
+      </c>
+      <c r="C38" s="36">
+        <f>COUNTIF(C10:C13,"✓ Met")+COUNTIF(C10:C13,"△ Partial")+COUNTIF(C10:C13,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D38" s="37">
+        <f>IFERROR(SUM(D10:D13)/C38,"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Specificity</t>
+        </is>
+      </c>
+      <c r="C39" s="36">
+        <f>COUNTIF(C16:C19,"✓ Met")+COUNTIF(C16:C19,"△ Partial")+COUNTIF(C16:C19,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D39" s="37">
+        <f>IFERROR(SUM(D16:D19)/C39,"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>SOAP Note Structure</t>
+        </is>
+      </c>
+      <c r="C40" s="36">
+        <f>COUNTIF(C22:C25,"✓ Met")+COUNTIF(C22:C25,"△ Partial")+COUNTIF(C22:C25,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D40" s="37">
+        <f>IFERROR(SUM(D22:D25)/C40,"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>HCC Capture</t>
+        </is>
+      </c>
+      <c r="C41" s="36">
+        <f>COUNTIF(C28:C29,"✓ Met")+COUNTIF(C28:C29,"△ Partial")+COUNTIF(C28:C29,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D41" s="37">
+        <f>IFERROR(SUM(D28:D29)/C41,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Supporting Quality Measures</t>
+        </is>
+      </c>
+      <c r="C42" s="36">
+        <f>COUNTIF(C32:C33,"✓ Met")+COUNTIF(C32:C33,"△ Partial")+COUNTIF(C32:C33,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D42" s="37">
+        <f>IFERROR(SUM(D32:D33)/C42,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OVERALL COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="D44" s="39">
+        <f>IFERROR(SUMPRODUCT(D38:D42,C38:C42)/SUM(C38:C42),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PERFORMANCE BAND</t>
+        </is>
+      </c>
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="18">
+        <f>IF(D44="","",IF(D44&gt;=0.95,"Excellent",IF(D44&gt;=0.90,"Meets Expectations",IF(D44&gt;=0.80,"Needs Improvement","Corrective Education Required"))))</f>
+        <v/>
+      </c>
+      <c r="E45" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001E7A6E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Clinical Documentation Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>One chart per sheet · tick each item · scoring &amp; rating are automatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>Provider:</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Date of Service:</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>How to use
+1. Fill in the yellow cells at top
+2. Rate each element (dropdown in column C)
+3. Overall % + Rating appear at the bottom
+4. Log the chart on the Audit Log tab when done</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Claim Number:</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Auditor:</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="51" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Category:</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Payer:</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="52" t="n"/>
+    </row>
+    <row r="7" ht="12" customHeight="1"/>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Documentation element</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Pts</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A · Diagnosis Accuracy   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>All reported diagnoses are clinically supported in the note</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="33">
+        <f>IF(C10="✓ Met",1,IF(C10="△ Partial",0.5,IF(C10="✗ Not Met",0,IF(C10="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Chronic conditions actively addressed at this visit (not just carried forward)</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="33">
+        <f>IF(C11="✓ Met",1,IF(C11="△ Partial",0.5,IF(C11="✗ Not Met",0,IF(C11="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>No unsupported or resolved conditions billed as active</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="33">
+        <f>IF(C12="✓ Met",1,IF(C12="△ Partial",0.5,IF(C12="✗ Not Met",0,IF(C12="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Problem list matches today's assessment &amp; plan</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="33">
+        <f>IF(C13="✓ Met",1,IF(C13="△ Partial",0.5,IF(C13="✗ Not Met",0,IF(C13="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B · Documentation Specificity   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>ICD-10 codes at highest available specificity (avoid 'unspecified')</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="33">
+        <f>IF(C16="✓ Met",1,IF(C16="△ Partial",0.5,IF(C16="✗ Not Met",0,IF(C16="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes: type + complications + control specified</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="33">
+        <f>IF(C17="✓ Met",1,IF(C17="△ Partial",0.5,IF(C17="✗ Not Met",0,IF(C17="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>S / O / A / P sections tell one consistent clinical story</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="33">
+        <f>IF(C18="✓ Met",1,IF(C18="△ Partial",0.5,IF(C18="✗ Not Met",0,IF(C18="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Note signed, dated, and closed by the rendering provider</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="33">
+        <f>IF(C19="✓ Met",1,IF(C19="△ Partial",0.5,IF(C19="✗ Not Met",0,IF(C19="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C · SOAP Note Structure   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Subjective — patient's history, symptoms, and concerns clearly documented</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="33">
+        <f>IF(C22="✓ Met",1,IF(C22="△ Partial",0.5,IF(C22="✗ Not Met",0,IF(C22="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Objective — exam findings, vitals, and relevant test results documented</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="33">
+        <f>IF(C23="✓ Met",1,IF(C23="△ Partial",0.5,IF(C23="✗ Not Met",0,IF(C23="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Assessment — each diagnosis explicitly assessed with clinical reasoning</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="33">
+        <f>IF(C24="✓ Met",1,IF(C24="△ Partial",0.5,IF(C24="✗ Not Met",0,IF(C24="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Plan — treatment plan documented (medication / referral / testing / follow-up)</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="33">
+        <f>IF(C25="✓ Met",1,IF(C25="△ Partial",0.5,IF(C25="✗ Not Met",0,IF(C25="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D · HCC Capture   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Prior-year HCCs recaptured (or explicitly resolved with rationale)</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="33">
+        <f>IF(C28="✓ Met",1,IF(C28="△ Partial",0.5,IF(C28="✗ Not Met",0,IF(C28="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Suspected undocumented chronic conditions captured with support</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="33">
+        <f>IF(C29="✓ Met",1,IF(C29="△ Partial",0.5,IF(C29="✗ Not Met",0,IF(C29="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E · Documentation Supporting Quality Measures   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Screening / measure results documented with specific values (PHQ-9, GAD-7, BMI, BP, HbA1c) — not just 'screened' or 'normal'</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="33">
+        <f>IF(C32="✓ Met",1,IF(C32="△ Partial",0.5,IF(C32="✗ Not Met",0,IF(C32="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Follow-up plan documented when a screening is positive or a result is abnormal (positive PHQ-9 → depression plan; elevated BMI → nutrition counseling)</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33">
+        <f>IF(C33="✓ Met",1,IF(C33="△ Partial",0.5,IF(C33="✗ Not Met",0,IF(C33="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>% Met</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Diagnosis Accuracy</t>
+        </is>
+      </c>
+      <c r="C38" s="36">
+        <f>COUNTIF(C10:C13,"✓ Met")+COUNTIF(C10:C13,"△ Partial")+COUNTIF(C10:C13,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D38" s="37">
+        <f>IFERROR(SUM(D10:D13)/C38,"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Specificity</t>
+        </is>
+      </c>
+      <c r="C39" s="36">
+        <f>COUNTIF(C16:C19,"✓ Met")+COUNTIF(C16:C19,"△ Partial")+COUNTIF(C16:C19,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D39" s="37">
+        <f>IFERROR(SUM(D16:D19)/C39,"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>SOAP Note Structure</t>
+        </is>
+      </c>
+      <c r="C40" s="36">
+        <f>COUNTIF(C22:C25,"✓ Met")+COUNTIF(C22:C25,"△ Partial")+COUNTIF(C22:C25,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D40" s="37">
+        <f>IFERROR(SUM(D22:D25)/C40,"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>HCC Capture</t>
+        </is>
+      </c>
+      <c r="C41" s="36">
+        <f>COUNTIF(C28:C29,"✓ Met")+COUNTIF(C28:C29,"△ Partial")+COUNTIF(C28:C29,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D41" s="37">
+        <f>IFERROR(SUM(D28:D29)/C41,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Supporting Quality Measures</t>
+        </is>
+      </c>
+      <c r="C42" s="36">
+        <f>COUNTIF(C32:C33,"✓ Met")+COUNTIF(C32:C33,"△ Partial")+COUNTIF(C32:C33,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D42" s="37">
+        <f>IFERROR(SUM(D32:D33)/C42,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OVERALL COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="D44" s="39">
+        <f>IFERROR(SUMPRODUCT(D38:D42,C38:C42)/SUM(C38:C42),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PERFORMANCE BAND</t>
+        </is>
+      </c>
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="18">
+        <f>IF(D44="","",IF(D44&gt;=0.95,"Excellent",IF(D44&gt;=0.90,"Meets Expectations",IF(D44&gt;=0.80,"Needs Improvement","Corrective Education Required"))))</f>
+        <v/>
+      </c>
+      <c r="E45" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001E7A6E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Clinical Documentation Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>One chart per sheet · tick each item · scoring &amp; rating are automatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>Provider:</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Date of Service:</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>How to use
+1. Fill in the yellow cells at top
+2. Rate each element (dropdown in column C)
+3. Overall % + Rating appear at the bottom
+4. Log the chart on the Audit Log tab when done</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Claim Number:</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Auditor:</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="51" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Category:</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Payer:</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="52" t="n"/>
+    </row>
+    <row r="7" ht="12" customHeight="1"/>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Documentation element</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Pts</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A · Diagnosis Accuracy   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>All reported diagnoses are clinically supported in the note</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="33">
+        <f>IF(C10="✓ Met",1,IF(C10="△ Partial",0.5,IF(C10="✗ Not Met",0,IF(C10="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Chronic conditions actively addressed at this visit (not just carried forward)</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="33">
+        <f>IF(C11="✓ Met",1,IF(C11="△ Partial",0.5,IF(C11="✗ Not Met",0,IF(C11="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>No unsupported or resolved conditions billed as active</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="33">
+        <f>IF(C12="✓ Met",1,IF(C12="△ Partial",0.5,IF(C12="✗ Not Met",0,IF(C12="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Problem list matches today's assessment &amp; plan</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="33">
+        <f>IF(C13="✓ Met",1,IF(C13="△ Partial",0.5,IF(C13="✗ Not Met",0,IF(C13="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B · Documentation Specificity   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>ICD-10 codes at highest available specificity (avoid 'unspecified')</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="33">
+        <f>IF(C16="✓ Met",1,IF(C16="△ Partial",0.5,IF(C16="✗ Not Met",0,IF(C16="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes: type + complications + control specified</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="33">
+        <f>IF(C17="✓ Met",1,IF(C17="△ Partial",0.5,IF(C17="✗ Not Met",0,IF(C17="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>S / O / A / P sections tell one consistent clinical story</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="33">
+        <f>IF(C18="✓ Met",1,IF(C18="△ Partial",0.5,IF(C18="✗ Not Met",0,IF(C18="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Note signed, dated, and closed by the rendering provider</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="33">
+        <f>IF(C19="✓ Met",1,IF(C19="△ Partial",0.5,IF(C19="✗ Not Met",0,IF(C19="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C · SOAP Note Structure   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Subjective — patient's history, symptoms, and concerns clearly documented</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="33">
+        <f>IF(C22="✓ Met",1,IF(C22="△ Partial",0.5,IF(C22="✗ Not Met",0,IF(C22="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Objective — exam findings, vitals, and relevant test results documented</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="33">
+        <f>IF(C23="✓ Met",1,IF(C23="△ Partial",0.5,IF(C23="✗ Not Met",0,IF(C23="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Assessment — each diagnosis explicitly assessed with clinical reasoning</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="33">
+        <f>IF(C24="✓ Met",1,IF(C24="△ Partial",0.5,IF(C24="✗ Not Met",0,IF(C24="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Plan — treatment plan documented (medication / referral / testing / follow-up)</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="33">
+        <f>IF(C25="✓ Met",1,IF(C25="△ Partial",0.5,IF(C25="✗ Not Met",0,IF(C25="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D · HCC Capture   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Prior-year HCCs recaptured (or explicitly resolved with rationale)</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="33">
+        <f>IF(C28="✓ Met",1,IF(C28="△ Partial",0.5,IF(C28="✗ Not Met",0,IF(C28="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Suspected undocumented chronic conditions captured with support</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="33">
+        <f>IF(C29="✓ Met",1,IF(C29="△ Partial",0.5,IF(C29="✗ Not Met",0,IF(C29="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E · Documentation Supporting Quality Measures   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Screening / measure results documented with specific values (PHQ-9, GAD-7, BMI, BP, HbA1c) — not just 'screened' or 'normal'</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="33">
+        <f>IF(C32="✓ Met",1,IF(C32="△ Partial",0.5,IF(C32="✗ Not Met",0,IF(C32="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Follow-up plan documented when a screening is positive or a result is abnormal (positive PHQ-9 → depression plan; elevated BMI → nutrition counseling)</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33">
+        <f>IF(C33="✓ Met",1,IF(C33="△ Partial",0.5,IF(C33="✗ Not Met",0,IF(C33="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>% Met</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Diagnosis Accuracy</t>
+        </is>
+      </c>
+      <c r="C38" s="36">
+        <f>COUNTIF(C10:C13,"✓ Met")+COUNTIF(C10:C13,"△ Partial")+COUNTIF(C10:C13,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D38" s="37">
+        <f>IFERROR(SUM(D10:D13)/C38,"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Specificity</t>
+        </is>
+      </c>
+      <c r="C39" s="36">
+        <f>COUNTIF(C16:C19,"✓ Met")+COUNTIF(C16:C19,"△ Partial")+COUNTIF(C16:C19,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D39" s="37">
+        <f>IFERROR(SUM(D16:D19)/C39,"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>SOAP Note Structure</t>
+        </is>
+      </c>
+      <c r="C40" s="36">
+        <f>COUNTIF(C22:C25,"✓ Met")+COUNTIF(C22:C25,"△ Partial")+COUNTIF(C22:C25,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D40" s="37">
+        <f>IFERROR(SUM(D22:D25)/C40,"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>HCC Capture</t>
+        </is>
+      </c>
+      <c r="C41" s="36">
+        <f>COUNTIF(C28:C29,"✓ Met")+COUNTIF(C28:C29,"△ Partial")+COUNTIF(C28:C29,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D41" s="37">
+        <f>IFERROR(SUM(D28:D29)/C41,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Supporting Quality Measures</t>
+        </is>
+      </c>
+      <c r="C42" s="36">
+        <f>COUNTIF(C32:C33,"✓ Met")+COUNTIF(C32:C33,"△ Partial")+COUNTIF(C32:C33,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D42" s="37">
+        <f>IFERROR(SUM(D32:D33)/C42,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OVERALL COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="D44" s="39">
+        <f>IFERROR(SUMPRODUCT(D38:D42,C38:C42)/SUM(C38:C42),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PERFORMANCE BAND</t>
+        </is>
+      </c>
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="18">
+        <f>IF(D44="","",IF(D44&gt;=0.95,"Excellent",IF(D44&gt;=0.90,"Meets Expectations",IF(D44&gt;=0.80,"Needs Improvement","Corrective Education Required"))))</f>
+        <v/>
+      </c>
+      <c r="E45" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001E7A6E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Clinical Documentation Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>One chart per sheet · tick each item · scoring &amp; rating are automatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>Provider:</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Date of Service:</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>How to use
+1. Fill in the yellow cells at top
+2. Rate each element (dropdown in column C)
+3. Overall % + Rating appear at the bottom
+4. Log the chart on the Audit Log tab when done</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Claim Number:</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Auditor:</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="51" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Category:</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Payer:</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="52" t="n"/>
+    </row>
+    <row r="7" ht="12" customHeight="1"/>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Documentation element</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Pts</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A · Diagnosis Accuracy   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>All reported diagnoses are clinically supported in the note</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="33">
+        <f>IF(C10="✓ Met",1,IF(C10="△ Partial",0.5,IF(C10="✗ Not Met",0,IF(C10="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Chronic conditions actively addressed at this visit (not just carried forward)</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="33">
+        <f>IF(C11="✓ Met",1,IF(C11="△ Partial",0.5,IF(C11="✗ Not Met",0,IF(C11="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>No unsupported or resolved conditions billed as active</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="33">
+        <f>IF(C12="✓ Met",1,IF(C12="△ Partial",0.5,IF(C12="✗ Not Met",0,IF(C12="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Problem list matches today's assessment &amp; plan</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="33">
+        <f>IF(C13="✓ Met",1,IF(C13="△ Partial",0.5,IF(C13="✗ Not Met",0,IF(C13="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B · Documentation Specificity   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>ICD-10 codes at highest available specificity (avoid 'unspecified')</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="33">
+        <f>IF(C16="✓ Met",1,IF(C16="△ Partial",0.5,IF(C16="✗ Not Met",0,IF(C16="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes: type + complications + control specified</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="33">
+        <f>IF(C17="✓ Met",1,IF(C17="△ Partial",0.5,IF(C17="✗ Not Met",0,IF(C17="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>S / O / A / P sections tell one consistent clinical story</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="33">
+        <f>IF(C18="✓ Met",1,IF(C18="△ Partial",0.5,IF(C18="✗ Not Met",0,IF(C18="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Note signed, dated, and closed by the rendering provider</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="33">
+        <f>IF(C19="✓ Met",1,IF(C19="△ Partial",0.5,IF(C19="✗ Not Met",0,IF(C19="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C · SOAP Note Structure   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Subjective — patient's history, symptoms, and concerns clearly documented</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="33">
+        <f>IF(C22="✓ Met",1,IF(C22="△ Partial",0.5,IF(C22="✗ Not Met",0,IF(C22="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Objective — exam findings, vitals, and relevant test results documented</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="33">
+        <f>IF(C23="✓ Met",1,IF(C23="△ Partial",0.5,IF(C23="✗ Not Met",0,IF(C23="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Assessment — each diagnosis explicitly assessed with clinical reasoning</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="33">
+        <f>IF(C24="✓ Met",1,IF(C24="△ Partial",0.5,IF(C24="✗ Not Met",0,IF(C24="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Plan — treatment plan documented (medication / referral / testing / follow-up)</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="33">
+        <f>IF(C25="✓ Met",1,IF(C25="△ Partial",0.5,IF(C25="✗ Not Met",0,IF(C25="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D · HCC Capture   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Prior-year HCCs recaptured (or explicitly resolved with rationale)</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="33">
+        <f>IF(C28="✓ Met",1,IF(C28="△ Partial",0.5,IF(C28="✗ Not Met",0,IF(C28="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Suspected undocumented chronic conditions captured with support</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="33">
+        <f>IF(C29="✓ Met",1,IF(C29="△ Partial",0.5,IF(C29="✗ Not Met",0,IF(C29="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E · Documentation Supporting Quality Measures   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Screening / measure results documented with specific values (PHQ-9, GAD-7, BMI, BP, HbA1c) — not just 'screened' or 'normal'</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="33">
+        <f>IF(C32="✓ Met",1,IF(C32="△ Partial",0.5,IF(C32="✗ Not Met",0,IF(C32="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Follow-up plan documented when a screening is positive or a result is abnormal (positive PHQ-9 → depression plan; elevated BMI → nutrition counseling)</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33">
+        <f>IF(C33="✓ Met",1,IF(C33="△ Partial",0.5,IF(C33="✗ Not Met",0,IF(C33="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>% Met</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Diagnosis Accuracy</t>
+        </is>
+      </c>
+      <c r="C38" s="36">
+        <f>COUNTIF(C10:C13,"✓ Met")+COUNTIF(C10:C13,"△ Partial")+COUNTIF(C10:C13,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D38" s="37">
+        <f>IFERROR(SUM(D10:D13)/C38,"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Specificity</t>
+        </is>
+      </c>
+      <c r="C39" s="36">
+        <f>COUNTIF(C16:C19,"✓ Met")+COUNTIF(C16:C19,"△ Partial")+COUNTIF(C16:C19,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D39" s="37">
+        <f>IFERROR(SUM(D16:D19)/C39,"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>SOAP Note Structure</t>
+        </is>
+      </c>
+      <c r="C40" s="36">
+        <f>COUNTIF(C22:C25,"✓ Met")+COUNTIF(C22:C25,"△ Partial")+COUNTIF(C22:C25,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D40" s="37">
+        <f>IFERROR(SUM(D22:D25)/C40,"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>HCC Capture</t>
+        </is>
+      </c>
+      <c r="C41" s="36">
+        <f>COUNTIF(C28:C29,"✓ Met")+COUNTIF(C28:C29,"△ Partial")+COUNTIF(C28:C29,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D41" s="37">
+        <f>IFERROR(SUM(D28:D29)/C41,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Supporting Quality Measures</t>
+        </is>
+      </c>
+      <c r="C42" s="36">
+        <f>COUNTIF(C32:C33,"✓ Met")+COUNTIF(C32:C33,"△ Partial")+COUNTIF(C32:C33,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D42" s="37">
+        <f>IFERROR(SUM(D32:D33)/C42,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OVERALL COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="D44" s="39">
+        <f>IFERROR(SUMPRODUCT(D38:D42,C38:C42)/SUM(C38:C42),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PERFORMANCE BAND</t>
+        </is>
+      </c>
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="18">
+        <f>IF(D44="","",IF(D44&gt;=0.95,"Excellent",IF(D44&gt;=0.90,"Meets Expectations",IF(D44&gt;=0.80,"Needs Improvement","Corrective Education Required"))))</f>
+        <v/>
+      </c>
+      <c r="E45" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001E7A6E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Clinical Documentation Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>One chart per sheet · tick each item · scoring &amp; rating are automatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>Provider:</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Date of Service:</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>How to use
+1. Fill in the yellow cells at top
+2. Rate each element (dropdown in column C)
+3. Overall % + Rating appear at the bottom
+4. Log the chart on the Audit Log tab when done</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Claim Number:</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Auditor:</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="51" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Category:</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Payer:</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="52" t="n"/>
+    </row>
+    <row r="7" ht="12" customHeight="1"/>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Documentation element</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Pts</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A · Diagnosis Accuracy   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>All reported diagnoses are clinically supported in the note</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="33">
+        <f>IF(C10="✓ Met",1,IF(C10="△ Partial",0.5,IF(C10="✗ Not Met",0,IF(C10="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Chronic conditions actively addressed at this visit (not just carried forward)</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="33">
+        <f>IF(C11="✓ Met",1,IF(C11="△ Partial",0.5,IF(C11="✗ Not Met",0,IF(C11="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>No unsupported or resolved conditions billed as active</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="33">
+        <f>IF(C12="✓ Met",1,IF(C12="△ Partial",0.5,IF(C12="✗ Not Met",0,IF(C12="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Problem list matches today's assessment &amp; plan</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="33">
+        <f>IF(C13="✓ Met",1,IF(C13="△ Partial",0.5,IF(C13="✗ Not Met",0,IF(C13="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B · Documentation Specificity   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>ICD-10 codes at highest available specificity (avoid 'unspecified')</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="33">
+        <f>IF(C16="✓ Met",1,IF(C16="△ Partial",0.5,IF(C16="✗ Not Met",0,IF(C16="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes: type + complications + control specified</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="33">
+        <f>IF(C17="✓ Met",1,IF(C17="△ Partial",0.5,IF(C17="✗ Not Met",0,IF(C17="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>S / O / A / P sections tell one consistent clinical story</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="33">
+        <f>IF(C18="✓ Met",1,IF(C18="△ Partial",0.5,IF(C18="✗ Not Met",0,IF(C18="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Note signed, dated, and closed by the rendering provider</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="33">
+        <f>IF(C19="✓ Met",1,IF(C19="△ Partial",0.5,IF(C19="✗ Not Met",0,IF(C19="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C · SOAP Note Structure   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Subjective — patient's history, symptoms, and concerns clearly documented</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="33">
+        <f>IF(C22="✓ Met",1,IF(C22="△ Partial",0.5,IF(C22="✗ Not Met",0,IF(C22="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Objective — exam findings, vitals, and relevant test results documented</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="33">
+        <f>IF(C23="✓ Met",1,IF(C23="△ Partial",0.5,IF(C23="✗ Not Met",0,IF(C23="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Assessment — each diagnosis explicitly assessed with clinical reasoning</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="33">
+        <f>IF(C24="✓ Met",1,IF(C24="△ Partial",0.5,IF(C24="✗ Not Met",0,IF(C24="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Plan — treatment plan documented (medication / referral / testing / follow-up)</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="33">
+        <f>IF(C25="✓ Met",1,IF(C25="△ Partial",0.5,IF(C25="✗ Not Met",0,IF(C25="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D · HCC Capture   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Prior-year HCCs recaptured (or explicitly resolved with rationale)</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="33">
+        <f>IF(C28="✓ Met",1,IF(C28="△ Partial",0.5,IF(C28="✗ Not Met",0,IF(C28="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Suspected undocumented chronic conditions captured with support</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="33">
+        <f>IF(C29="✓ Met",1,IF(C29="△ Partial",0.5,IF(C29="✗ Not Met",0,IF(C29="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E · Documentation Supporting Quality Measures   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Screening / measure results documented with specific values (PHQ-9, GAD-7, BMI, BP, HbA1c) — not just 'screened' or 'normal'</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="33">
+        <f>IF(C32="✓ Met",1,IF(C32="△ Partial",0.5,IF(C32="✗ Not Met",0,IF(C32="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Follow-up plan documented when a screening is positive or a result is abnormal (positive PHQ-9 → depression plan; elevated BMI → nutrition counseling)</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33">
+        <f>IF(C33="✓ Met",1,IF(C33="△ Partial",0.5,IF(C33="✗ Not Met",0,IF(C33="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>% Met</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Diagnosis Accuracy</t>
+        </is>
+      </c>
+      <c r="C38" s="36">
+        <f>COUNTIF(C10:C13,"✓ Met")+COUNTIF(C10:C13,"△ Partial")+COUNTIF(C10:C13,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D38" s="37">
+        <f>IFERROR(SUM(D10:D13)/C38,"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Specificity</t>
+        </is>
+      </c>
+      <c r="C39" s="36">
+        <f>COUNTIF(C16:C19,"✓ Met")+COUNTIF(C16:C19,"△ Partial")+COUNTIF(C16:C19,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D39" s="37">
+        <f>IFERROR(SUM(D16:D19)/C39,"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>SOAP Note Structure</t>
+        </is>
+      </c>
+      <c r="C40" s="36">
+        <f>COUNTIF(C22:C25,"✓ Met")+COUNTIF(C22:C25,"△ Partial")+COUNTIF(C22:C25,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D40" s="37">
+        <f>IFERROR(SUM(D22:D25)/C40,"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>HCC Capture</t>
+        </is>
+      </c>
+      <c r="C41" s="36">
+        <f>COUNTIF(C28:C29,"✓ Met")+COUNTIF(C28:C29,"△ Partial")+COUNTIF(C28:C29,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D41" s="37">
+        <f>IFERROR(SUM(D28:D29)/C41,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Supporting Quality Measures</t>
+        </is>
+      </c>
+      <c r="C42" s="36">
+        <f>COUNTIF(C32:C33,"✓ Met")+COUNTIF(C32:C33,"△ Partial")+COUNTIF(C32:C33,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D42" s="37">
+        <f>IFERROR(SUM(D32:D33)/C42,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OVERALL COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="D44" s="39">
+        <f>IFERROR(SUMPRODUCT(D38:D42,C38:C42)/SUM(C38:C42),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PERFORMANCE BAND</t>
+        </is>
+      </c>
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="18">
+        <f>IF(D44="","",IF(D44&gt;=0.95,"Excellent",IF(D44&gt;=0.90,"Meets Expectations",IF(D44&gt;=0.80,"Needs Improvement","Corrective Education Required"))))</f>
+        <v/>
+      </c>
+      <c r="E45" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001E7A6E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Clinical Documentation Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>One chart per sheet · tick each item · scoring &amp; rating are automatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>Provider:</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Date of Service:</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>How to use
+1. Fill in the yellow cells at top
+2. Rate each element (dropdown in column C)
+3. Overall % + Rating appear at the bottom
+4. Log the chart on the Audit Log tab when done</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Claim Number:</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Auditor:</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="51" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Category:</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Payer:</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="52" t="n"/>
+    </row>
+    <row r="7" ht="12" customHeight="1"/>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Documentation element</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Pts</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A · Diagnosis Accuracy   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>All reported diagnoses are clinically supported in the note</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="33">
+        <f>IF(C10="✓ Met",1,IF(C10="△ Partial",0.5,IF(C10="✗ Not Met",0,IF(C10="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Chronic conditions actively addressed at this visit (not just carried forward)</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="33">
+        <f>IF(C11="✓ Met",1,IF(C11="△ Partial",0.5,IF(C11="✗ Not Met",0,IF(C11="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>No unsupported or resolved conditions billed as active</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="33">
+        <f>IF(C12="✓ Met",1,IF(C12="△ Partial",0.5,IF(C12="✗ Not Met",0,IF(C12="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Problem list matches today's assessment &amp; plan</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="33">
+        <f>IF(C13="✓ Met",1,IF(C13="△ Partial",0.5,IF(C13="✗ Not Met",0,IF(C13="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B · Documentation Specificity   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>ICD-10 codes at highest available specificity (avoid 'unspecified')</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="33">
+        <f>IF(C16="✓ Met",1,IF(C16="△ Partial",0.5,IF(C16="✗ Not Met",0,IF(C16="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes: type + complications + control specified</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="33">
+        <f>IF(C17="✓ Met",1,IF(C17="△ Partial",0.5,IF(C17="✗ Not Met",0,IF(C17="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>S / O / A / P sections tell one consistent clinical story</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="33">
+        <f>IF(C18="✓ Met",1,IF(C18="△ Partial",0.5,IF(C18="✗ Not Met",0,IF(C18="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Note signed, dated, and closed by the rendering provider</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="33">
+        <f>IF(C19="✓ Met",1,IF(C19="△ Partial",0.5,IF(C19="✗ Not Met",0,IF(C19="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C · SOAP Note Structure   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Subjective — patient's history, symptoms, and concerns clearly documented</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="33">
+        <f>IF(C22="✓ Met",1,IF(C22="△ Partial",0.5,IF(C22="✗ Not Met",0,IF(C22="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Objective — exam findings, vitals, and relevant test results documented</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="33">
+        <f>IF(C23="✓ Met",1,IF(C23="△ Partial",0.5,IF(C23="✗ Not Met",0,IF(C23="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Assessment — each diagnosis explicitly assessed with clinical reasoning</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="33">
+        <f>IF(C24="✓ Met",1,IF(C24="△ Partial",0.5,IF(C24="✗ Not Met",0,IF(C24="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Plan — treatment plan documented (medication / referral / testing / follow-up)</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="33">
+        <f>IF(C25="✓ Met",1,IF(C25="△ Partial",0.5,IF(C25="✗ Not Met",0,IF(C25="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D · HCC Capture   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Prior-year HCCs recaptured (or explicitly resolved with rationale)</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="33">
+        <f>IF(C28="✓ Met",1,IF(C28="△ Partial",0.5,IF(C28="✗ Not Met",0,IF(C28="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Suspected undocumented chronic conditions captured with support</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="33">
+        <f>IF(C29="✓ Met",1,IF(C29="△ Partial",0.5,IF(C29="✗ Not Met",0,IF(C29="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E · Documentation Supporting Quality Measures   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Screening / measure results documented with specific values (PHQ-9, GAD-7, BMI, BP, HbA1c) — not just 'screened' or 'normal'</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="33">
+        <f>IF(C32="✓ Met",1,IF(C32="△ Partial",0.5,IF(C32="✗ Not Met",0,IF(C32="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Follow-up plan documented when a screening is positive or a result is abnormal (positive PHQ-9 → depression plan; elevated BMI → nutrition counseling)</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33">
+        <f>IF(C33="✓ Met",1,IF(C33="△ Partial",0.5,IF(C33="✗ Not Met",0,IF(C33="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>% Met</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Diagnosis Accuracy</t>
+        </is>
+      </c>
+      <c r="C38" s="36">
+        <f>COUNTIF(C10:C13,"✓ Met")+COUNTIF(C10:C13,"△ Partial")+COUNTIF(C10:C13,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D38" s="37">
+        <f>IFERROR(SUM(D10:D13)/C38,"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Specificity</t>
+        </is>
+      </c>
+      <c r="C39" s="36">
+        <f>COUNTIF(C16:C19,"✓ Met")+COUNTIF(C16:C19,"△ Partial")+COUNTIF(C16:C19,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D39" s="37">
+        <f>IFERROR(SUM(D16:D19)/C39,"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>SOAP Note Structure</t>
+        </is>
+      </c>
+      <c r="C40" s="36">
+        <f>COUNTIF(C22:C25,"✓ Met")+COUNTIF(C22:C25,"△ Partial")+COUNTIF(C22:C25,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D40" s="37">
+        <f>IFERROR(SUM(D22:D25)/C40,"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>HCC Capture</t>
+        </is>
+      </c>
+      <c r="C41" s="36">
+        <f>COUNTIF(C28:C29,"✓ Met")+COUNTIF(C28:C29,"△ Partial")+COUNTIF(C28:C29,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D41" s="37">
+        <f>IFERROR(SUM(D28:D29)/C41,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Supporting Quality Measures</t>
+        </is>
+      </c>
+      <c r="C42" s="36">
+        <f>COUNTIF(C32:C33,"✓ Met")+COUNTIF(C32:C33,"△ Partial")+COUNTIF(C32:C33,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D42" s="37">
+        <f>IFERROR(SUM(D32:D33)/C42,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OVERALL COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="D44" s="39">
+        <f>IFERROR(SUMPRODUCT(D38:D42,C38:C42)/SUM(C38:C42),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PERFORMANCE BAND</t>
+        </is>
+      </c>
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="18">
+        <f>IF(D44="","",IF(D44&gt;=0.95,"Excellent",IF(D44&gt;=0.90,"Meets Expectations",IF(D44&gt;=0.80,"Needs Improvement","Corrective Education Required"))))</f>
+        <v/>
+      </c>
+      <c r="E45" s="14" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/docs/Clinical_Documentation_Audit_Simple.xlsx
+++ b/docs/Clinical_Documentation_Audit_Simple.xlsx
@@ -1348,10 +1348,14 @@
       <c r="E4" s="28" t="inlineStr">
         <is>
           <t>How to audit a claim
-1. Click a Claim 01–10 tab (bottom of the workbook)
-2. Fill the yellow header + ratings — auto-scores
-3. Log the finished claim on the Audit Log tab
-4. Move to the next Claim tab · this Audit Checklist tab stays as the master template</t>
+1. Click Claim 01 → fill yellow cells → next Claim tab
+2. Log each finished claim on the Audit Log
+Start a new provider (after 10 claims)
+1. Ctrl+click tabs Claim 01 through Claim 10 to group them
+2. On any grouped tab, select the yellow cells + rating column + notes
+3. Press Delete → all 10 tabs clear at once
+4. Right-click any tab → Ungroup Sheets
+5. The Audit Log keeps every prior claim's summary — nothing is lost</t>
         </is>
       </c>
     </row>
@@ -2084,11 +2088,15 @@
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="28" t="inlineStr">
         <is>
-          <t>How to use
-1. Fill in the yellow cells at top
-2. Rate each element (dropdown in column C)
-3. Overall % + Rating appear at the bottom
-4. Log the chart on the Audit Log tab when done</t>
+          <t>How to audit a claim
+1. Click Claim 01 → fill yellow cells → next Claim tab
+2. Log each finished claim on the Audit Log
+Start a new provider (after 10 claims)
+1. Ctrl+click tabs Claim 01 through Claim 10 to group them
+2. On any grouped tab, select the yellow cells + rating column + notes
+3. Press Delete → all 10 tabs clear at once
+4. Right-click any tab → Ungroup Sheets
+5. The Audit Log keeps every prior claim's summary — nothing is lost</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2478,6 @@
       <c r="E33" s="10" t="n"/>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="35"/>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="34" t="inlineStr">
         <is>
@@ -2602,7 +2609,6 @@
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
-    <row r="43"/>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
         <is>
@@ -2696,11 +2702,15 @@
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="28" t="inlineStr">
         <is>
-          <t>How to use
-1. Fill in the yellow cells at top
-2. Rate each element (dropdown in column C)
-3. Overall % + Rating appear at the bottom
-4. Log the chart on the Audit Log tab when done</t>
+          <t>How to audit a claim
+1. Click Claim 01 → fill yellow cells → next Claim tab
+2. Log each finished claim on the Audit Log
+Start a new provider (after 10 claims)
+1. Ctrl+click tabs Claim 01 through Claim 10 to group them
+2. On any grouped tab, select the yellow cells + rating column + notes
+3. Press Delete → all 10 tabs clear at once
+4. Right-click any tab → Ungroup Sheets
+5. The Audit Log keeps every prior claim's summary — nothing is lost</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3092,6 @@
       <c r="E33" s="10" t="n"/>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="35"/>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="34" t="inlineStr">
         <is>
@@ -3214,7 +3223,6 @@
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
-    <row r="43"/>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
         <is>
@@ -7234,11 +7242,15 @@
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="28" t="inlineStr">
         <is>
-          <t>How to use
-1. Fill in the yellow cells at top
-2. Rate each element (dropdown in column C)
-3. Overall % + Rating appear at the bottom
-4. Log the chart on the Audit Log tab when done</t>
+          <t>How to audit a claim
+1. Click Claim 01 → fill yellow cells → next Claim tab
+2. Log each finished claim on the Audit Log
+Start a new provider (after 10 claims)
+1. Ctrl+click tabs Claim 01 through Claim 10 to group them
+2. On any grouped tab, select the yellow cells + rating column + notes
+3. Press Delete → all 10 tabs clear at once
+4. Right-click any tab → Ungroup Sheets
+5. The Audit Log keeps every prior claim's summary — nothing is lost</t>
         </is>
       </c>
     </row>
@@ -7620,7 +7632,6 @@
       <c r="E33" s="10" t="n"/>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="35"/>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="34" t="inlineStr">
         <is>
@@ -7752,7 +7763,6 @@
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
-    <row r="43"/>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
         <is>
@@ -7846,11 +7856,15 @@
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="28" t="inlineStr">
         <is>
-          <t>How to use
-1. Fill in the yellow cells at top
-2. Rate each element (dropdown in column C)
-3. Overall % + Rating appear at the bottom
-4. Log the chart on the Audit Log tab when done</t>
+          <t>How to audit a claim
+1. Click Claim 01 → fill yellow cells → next Claim tab
+2. Log each finished claim on the Audit Log
+Start a new provider (after 10 claims)
+1. Ctrl+click tabs Claim 01 through Claim 10 to group them
+2. On any grouped tab, select the yellow cells + rating column + notes
+3. Press Delete → all 10 tabs clear at once
+4. Right-click any tab → Ungroup Sheets
+5. The Audit Log keeps every prior claim's summary — nothing is lost</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8246,6 @@
       <c r="E33" s="10" t="n"/>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="35"/>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="34" t="inlineStr">
         <is>
@@ -8364,7 +8377,6 @@
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
-    <row r="43"/>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
         <is>
@@ -8458,11 +8470,15 @@
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="28" t="inlineStr">
         <is>
-          <t>How to use
-1. Fill in the yellow cells at top
-2. Rate each element (dropdown in column C)
-3. Overall % + Rating appear at the bottom
-4. Log the chart on the Audit Log tab when done</t>
+          <t>How to audit a claim
+1. Click Claim 01 → fill yellow cells → next Claim tab
+2. Log each finished claim on the Audit Log
+Start a new provider (after 10 claims)
+1. Ctrl+click tabs Claim 01 through Claim 10 to group them
+2. On any grouped tab, select the yellow cells + rating column + notes
+3. Press Delete → all 10 tabs clear at once
+4. Right-click any tab → Ungroup Sheets
+5. The Audit Log keeps every prior claim's summary — nothing is lost</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8860,6 @@
       <c r="E33" s="10" t="n"/>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="35"/>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="34" t="inlineStr">
         <is>
@@ -8976,7 +8991,6 @@
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
-    <row r="43"/>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
         <is>
@@ -9070,11 +9084,15 @@
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="28" t="inlineStr">
         <is>
-          <t>How to use
-1. Fill in the yellow cells at top
-2. Rate each element (dropdown in column C)
-3. Overall % + Rating appear at the bottom
-4. Log the chart on the Audit Log tab when done</t>
+          <t>How to audit a claim
+1. Click Claim 01 → fill yellow cells → next Claim tab
+2. Log each finished claim on the Audit Log
+Start a new provider (after 10 claims)
+1. Ctrl+click tabs Claim 01 through Claim 10 to group them
+2. On any grouped tab, select the yellow cells + rating column + notes
+3. Press Delete → all 10 tabs clear at once
+4. Right-click any tab → Ungroup Sheets
+5. The Audit Log keeps every prior claim's summary — nothing is lost</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9474,6 @@
       <c r="E33" s="10" t="n"/>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="35"/>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="34" t="inlineStr">
         <is>
@@ -9588,7 +9605,6 @@
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
-    <row r="43"/>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
         <is>
@@ -9682,11 +9698,15 @@
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="28" t="inlineStr">
         <is>
-          <t>How to use
-1. Fill in the yellow cells at top
-2. Rate each element (dropdown in column C)
-3. Overall % + Rating appear at the bottom
-4. Log the chart on the Audit Log tab when done</t>
+          <t>How to audit a claim
+1. Click Claim 01 → fill yellow cells → next Claim tab
+2. Log each finished claim on the Audit Log
+Start a new provider (after 10 claims)
+1. Ctrl+click tabs Claim 01 through Claim 10 to group them
+2. On any grouped tab, select the yellow cells + rating column + notes
+3. Press Delete → all 10 tabs clear at once
+4. Right-click any tab → Ungroup Sheets
+5. The Audit Log keeps every prior claim's summary — nothing is lost</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10088,6 @@
       <c r="E33" s="10" t="n"/>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="35"/>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="34" t="inlineStr">
         <is>
@@ -10200,7 +10219,6 @@
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
-    <row r="43"/>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
         <is>
@@ -10294,11 +10312,15 @@
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="28" t="inlineStr">
         <is>
-          <t>How to use
-1. Fill in the yellow cells at top
-2. Rate each element (dropdown in column C)
-3. Overall % + Rating appear at the bottom
-4. Log the chart on the Audit Log tab when done</t>
+          <t>How to audit a claim
+1. Click Claim 01 → fill yellow cells → next Claim tab
+2. Log each finished claim on the Audit Log
+Start a new provider (after 10 claims)
+1. Ctrl+click tabs Claim 01 through Claim 10 to group them
+2. On any grouped tab, select the yellow cells + rating column + notes
+3. Press Delete → all 10 tabs clear at once
+4. Right-click any tab → Ungroup Sheets
+5. The Audit Log keeps every prior claim's summary — nothing is lost</t>
         </is>
       </c>
     </row>
@@ -10680,7 +10702,6 @@
       <c r="E33" s="10" t="n"/>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="35"/>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="34" t="inlineStr">
         <is>
@@ -10812,7 +10833,6 @@
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
-    <row r="43"/>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
         <is>
@@ -10906,11 +10926,15 @@
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="28" t="inlineStr">
         <is>
-          <t>How to use
-1. Fill in the yellow cells at top
-2. Rate each element (dropdown in column C)
-3. Overall % + Rating appear at the bottom
-4. Log the chart on the Audit Log tab when done</t>
+          <t>How to audit a claim
+1. Click Claim 01 → fill yellow cells → next Claim tab
+2. Log each finished claim on the Audit Log
+Start a new provider (after 10 claims)
+1. Ctrl+click tabs Claim 01 through Claim 10 to group them
+2. On any grouped tab, select the yellow cells + rating column + notes
+3. Press Delete → all 10 tabs clear at once
+4. Right-click any tab → Ungroup Sheets
+5. The Audit Log keeps every prior claim's summary — nothing is lost</t>
         </is>
       </c>
     </row>
@@ -11292,7 +11316,6 @@
       <c r="E33" s="10" t="n"/>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="35"/>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="34" t="inlineStr">
         <is>
@@ -11424,7 +11447,6 @@
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
-    <row r="43"/>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
         <is>
@@ -11518,11 +11540,15 @@
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="28" t="inlineStr">
         <is>
-          <t>How to use
-1. Fill in the yellow cells at top
-2. Rate each element (dropdown in column C)
-3. Overall % + Rating appear at the bottom
-4. Log the chart on the Audit Log tab when done</t>
+          <t>How to audit a claim
+1. Click Claim 01 → fill yellow cells → next Claim tab
+2. Log each finished claim on the Audit Log
+Start a new provider (after 10 claims)
+1. Ctrl+click tabs Claim 01 through Claim 10 to group them
+2. On any grouped tab, select the yellow cells + rating column + notes
+3. Press Delete → all 10 tabs clear at once
+4. Right-click any tab → Ungroup Sheets
+5. The Audit Log keeps every prior claim's summary — nothing is lost</t>
         </is>
       </c>
     </row>
@@ -11904,7 +11930,6 @@
       <c r="E33" s="10" t="n"/>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="35"/>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="34" t="inlineStr">
         <is>
@@ -12036,7 +12061,6 @@
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
-    <row r="43"/>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
         <is>

--- a/docs/Clinical_Documentation_Audit_Simple.xlsx
+++ b/docs/Clinical_Documentation_Audit_Simple.xlsx
@@ -8,14 +8,22 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Checklist" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Log" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Reference" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly Report" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provider Metrics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claim 01" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claim 02" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claim 03" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claim 04" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claim 05" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claim 06" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claim 07" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claim 08" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claim 09" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claim 10" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Log" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Reference" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quarterly Report" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
-  <definedNames>
-    <definedName name="SaveRow">'Audit Checklist'!$A$49:$I$49</definedName>
-    <definedName name="InputCells">'Audit Checklist'!$B$4,'Audit Checklist'!$D$4,'Audit Checklist'!$B$5,'Audit Checklist'!$D$5,'Audit Checklist'!$B$6,'Audit Checklist'!$D$6,'Audit Checklist'!$C$10:$C$13,'Audit Checklist'!$C$16:$C$19,'Audit Checklist'!$C$22:$C$25,'Audit Checklist'!$C$28:$C$29,'Audit Checklist'!$C$32:$C$33,'Audit Checklist'!$E$10:$E$13,'Audit Checklist'!$E$16:$E$19,'Audit Checklist'!$E$22:$E$25,'Audit Checklist'!$E$28:$E$29,'Audit Checklist'!$E$32:$E$33</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -26,7 +34,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -176,6 +184,18 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
       <sz val="14"/>
     </font>
   </fonts>
@@ -391,7 +411,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -644,6 +664,41 @@
     <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="27" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1383,16 +1438,18 @@
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="28" t="inlineStr">
         <is>
-          <t>Workflow — one claim at a time
-1. Fill yellow header + ratings above
-2. Overall % + Rating auto-compute
-Save &amp; start a new claim
-▶ Ctrl+G → SaveRow → Enter → Ctrl+C
-   Go to Audit Log → paste as Values in next empty row
-✨ Ctrl+G → InputCells → Enter → Delete
-   Form clears · ready for the next claim
-After 10 claims per provider, the Audit Log holds all their
-results — provider metrics roll up automatically.</t>
+          <t>How to audit a claim
+1. Click a Claim 01–10 tab (bottom of the workbook)
+2. Fill yellow header + ratings — auto-scores
+3. Move to the next Claim tab · repeat
+Global metrics roll up automatically
+• Open the Provider Metrics tab — it pulls the 10 claim scores
+  live from the Claim tabs so you see the running provider average.
+Start a new provider (after 10 claims)
+1. Ctrl+click Claim 01 through Claim 10 to group them
+2. Select the yellow header + rating + note cells on any tab
+3. Press Delete → all 10 tabs clear at once
+4. Right-click any tab → Ungroup Sheets</t>
         </is>
       </c>
     </row>
@@ -1946,123 +2003,89 @@
       <c r="E45" s="14" t="n"/>
     </row>
     <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ▶ SAVE THIS CLAIM TO THE AUDIT LOG</t>
-        </is>
-      </c>
+      <c r="A46" s="62" t="n"/>
+      <c r="B46" s="62" t="n"/>
+      <c r="C46" s="62" t="n"/>
+      <c r="D46" s="62" t="n"/>
+      <c r="E46" s="62" t="n"/>
+      <c r="F46" s="62" t="n"/>
+      <c r="G46" s="62" t="n"/>
+      <c r="H46" s="62" t="n"/>
+      <c r="I46" s="62" t="n"/>
     </row>
     <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Press Ctrl+G → type SaveRow → Enter → Ctrl+C to copy this claim's summary. Then go to Audit Log, click the first empty row in column A, right-click → Paste Special → Values.</t>
-        </is>
-      </c>
+      <c r="A47" s="62" t="n"/>
+      <c r="B47" s="62" t="n"/>
+      <c r="C47" s="62" t="n"/>
+      <c r="D47" s="62" t="n"/>
+      <c r="E47" s="62" t="n"/>
+      <c r="F47" s="62" t="n"/>
+      <c r="G47" s="62" t="n"/>
+      <c r="H47" s="62" t="n"/>
+      <c r="I47" s="62" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="83" t="inlineStr">
-        <is>
-          <t>Audit Date</t>
-        </is>
-      </c>
-      <c r="B48" s="83" t="inlineStr">
-        <is>
-          <t>Provider</t>
-        </is>
-      </c>
-      <c r="C48" s="83" t="inlineStr">
-        <is>
-          <t>Claim #</t>
-        </is>
-      </c>
-      <c r="D48" s="83" t="inlineStr">
-        <is>
-          <t>DOS</t>
-        </is>
-      </c>
-      <c r="E48" s="83" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="F48" s="83" t="inlineStr">
-        <is>
-          <t>Compliance %</t>
-        </is>
-      </c>
-      <c r="G48" s="83" t="inlineStr">
-        <is>
-          <t>Rating</t>
-        </is>
-      </c>
-      <c r="H48" s="83" t="inlineStr">
-        <is>
-          <t>Deficiencies</t>
-        </is>
-      </c>
-      <c r="I48" s="83" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
+      <c r="A48" s="62" t="n"/>
+      <c r="B48" s="62" t="n"/>
+      <c r="C48" s="62" t="n"/>
+      <c r="D48" s="62" t="n"/>
+      <c r="E48" s="62" t="n"/>
+      <c r="F48" s="62" t="n"/>
+      <c r="G48" s="62" t="n"/>
+      <c r="H48" s="62" t="n"/>
+      <c r="I48" s="62" t="n"/>
     </row>
     <row r="49" ht="26" customHeight="1">
-      <c r="A49" s="84">
-        <f>TODAY()</f>
-        <v/>
-      </c>
-      <c r="B49" s="32">
-        <f>$B$4</f>
-        <v/>
-      </c>
-      <c r="C49" s="32">
-        <f>$B$5</f>
-        <v/>
-      </c>
-      <c r="D49" s="84">
-        <f>$D$4</f>
-        <v/>
-      </c>
-      <c r="E49" s="32">
-        <f>$B$6</f>
-        <v/>
-      </c>
-      <c r="F49" s="85">
-        <f>$I$44</f>
-        <v/>
-      </c>
-      <c r="G49" s="32">
-        <f>$I$45</f>
-        <v/>
-      </c>
-      <c r="H49" s="66" t="inlineStr"/>
-      <c r="I49" s="66" t="inlineStr"/>
+      <c r="A49" s="62" t="n"/>
+      <c r="B49" s="62" t="n"/>
+      <c r="C49" s="62" t="n"/>
+      <c r="D49" s="62" t="n"/>
+      <c r="E49" s="62" t="n"/>
+      <c r="F49" s="62" t="n"/>
+      <c r="G49" s="62" t="n"/>
+      <c r="H49" s="62" t="n"/>
+      <c r="I49" s="62" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="62" t="n"/>
+      <c r="B50" s="62" t="n"/>
+      <c r="C50" s="62" t="n"/>
+      <c r="D50" s="62" t="n"/>
+      <c r="E50" s="62" t="n"/>
+      <c r="F50" s="62" t="n"/>
+      <c r="G50" s="62" t="n"/>
+      <c r="H50" s="62" t="n"/>
+      <c r="I50" s="62" t="n"/>
     </row>
     <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ✨ CLEAR THE FORM TO START A NEW CLAIM</t>
-        </is>
-      </c>
+      <c r="A51" s="62" t="n"/>
+      <c r="B51" s="62" t="n"/>
+      <c r="C51" s="62" t="n"/>
+      <c r="D51" s="62" t="n"/>
+      <c r="E51" s="62" t="n"/>
+      <c r="F51" s="62" t="n"/>
+      <c r="G51" s="62" t="n"/>
+      <c r="H51" s="62" t="n"/>
+      <c r="I51" s="62" t="n"/>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Press Ctrl+G → type InputCells → Enter → press Delete. All yellow header, rating, and note cells clear at once — ready for the next claim.</t>
-        </is>
-      </c>
+      <c r="A52" s="62" t="n"/>
+      <c r="B52" s="62" t="n"/>
+      <c r="C52" s="62" t="n"/>
+      <c r="D52" s="62" t="n"/>
+      <c r="E52" s="62" t="n"/>
+      <c r="F52" s="62" t="n"/>
+      <c r="G52" s="62" t="n"/>
+      <c r="H52" s="62" t="n"/>
+      <c r="I52" s="62" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="11">
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A52:I52"/>
     <mergeCell ref="A44:C44"/>
-    <mergeCell ref="A51:I51"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A46:I46"/>
-    <mergeCell ref="A47:I47"/>
     <mergeCell ref="E4:E6"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A36:E36"/>
@@ -2191,7 +2214,2095 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001E7A6E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Clinical Documentation Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>One chart per sheet · tick each item · scoring &amp; rating are automatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>Provider:</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Date of Service:</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>How to audit a claim
+1. Click a Claim 01–10 tab (bottom of the workbook)
+2. Fill yellow header + ratings — auto-scores
+3. Move to the next Claim tab · repeat
+Global metrics roll up automatically
+• Open the Provider Metrics tab — it pulls the 10 claim scores
+  live from the Claim tabs so you see the running provider average.
+Start a new provider (after 10 claims)
+1. Ctrl+click Claim 01 through Claim 10 to group them
+2. Select the yellow header + rating + note cells on any tab
+3. Press Delete → all 10 tabs clear at once
+4. Right-click any tab → Ungroup Sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Claim Number:</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Auditor:</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="51" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Category:</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Payer:</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="52" t="n"/>
+    </row>
+    <row r="7" ht="12" customHeight="1"/>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Documentation element</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Pts</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A · Diagnosis Accuracy   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>All reported diagnoses are clinically supported in the note</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="33">
+        <f>IF(C10="✓ Met",1,IF(C10="△ Partial",0.5,IF(C10="✗ Not Met",0,IF(C10="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Chronic conditions actively addressed at this visit (not just carried forward)</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="33">
+        <f>IF(C11="✓ Met",1,IF(C11="△ Partial",0.5,IF(C11="✗ Not Met",0,IF(C11="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>No unsupported or resolved conditions billed as active</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="33">
+        <f>IF(C12="✓ Met",1,IF(C12="△ Partial",0.5,IF(C12="✗ Not Met",0,IF(C12="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Problem list matches today's assessment &amp; plan</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="33">
+        <f>IF(C13="✓ Met",1,IF(C13="△ Partial",0.5,IF(C13="✗ Not Met",0,IF(C13="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B · Documentation Specificity   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>ICD-10 codes at highest available specificity (avoid 'unspecified')</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="33">
+        <f>IF(C16="✓ Met",1,IF(C16="△ Partial",0.5,IF(C16="✗ Not Met",0,IF(C16="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes: type + complications + control specified</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="33">
+        <f>IF(C17="✓ Met",1,IF(C17="△ Partial",0.5,IF(C17="✗ Not Met",0,IF(C17="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>S / O / A / P sections tell one consistent clinical story</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="33">
+        <f>IF(C18="✓ Met",1,IF(C18="△ Partial",0.5,IF(C18="✗ Not Met",0,IF(C18="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Note signed, dated, and closed by the rendering provider</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="33">
+        <f>IF(C19="✓ Met",1,IF(C19="△ Partial",0.5,IF(C19="✗ Not Met",0,IF(C19="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C · SOAP Note Structure   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Subjective — patient's history, symptoms, and concerns clearly documented</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="33">
+        <f>IF(C22="✓ Met",1,IF(C22="△ Partial",0.5,IF(C22="✗ Not Met",0,IF(C22="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Objective — exam findings, vitals, and relevant test results documented</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="33">
+        <f>IF(C23="✓ Met",1,IF(C23="△ Partial",0.5,IF(C23="✗ Not Met",0,IF(C23="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Assessment — each diagnosis explicitly assessed with clinical reasoning</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="33">
+        <f>IF(C24="✓ Met",1,IF(C24="△ Partial",0.5,IF(C24="✗ Not Met",0,IF(C24="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Plan — treatment plan documented (medication / referral / testing / follow-up)</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="33">
+        <f>IF(C25="✓ Met",1,IF(C25="△ Partial",0.5,IF(C25="✗ Not Met",0,IF(C25="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D · HCC Capture   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Prior-year HCCs recaptured (or explicitly resolved with rationale)</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="33">
+        <f>IF(C28="✓ Met",1,IF(C28="△ Partial",0.5,IF(C28="✗ Not Met",0,IF(C28="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Suspected undocumented chronic conditions captured with support</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="33">
+        <f>IF(C29="✓ Met",1,IF(C29="△ Partial",0.5,IF(C29="✗ Not Met",0,IF(C29="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E · Documentation Supporting Quality Measures   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Screening / measure results documented with specific values (PHQ-9, GAD-7, BMI, BP, HbA1c) — not just 'screened' or 'normal'</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="33">
+        <f>IF(C32="✓ Met",1,IF(C32="△ Partial",0.5,IF(C32="✗ Not Met",0,IF(C32="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Follow-up plan documented when a screening is positive or a result is abnormal (positive PHQ-9 → depression plan; elevated BMI → nutrition counseling)</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33">
+        <f>IF(C33="✓ Met",1,IF(C33="△ Partial",0.5,IF(C33="✗ Not Met",0,IF(C33="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>% Met</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Diagnosis Accuracy</t>
+        </is>
+      </c>
+      <c r="C38" s="36">
+        <f>COUNTIF(C10:C13,"✓ Met")+COUNTIF(C10:C13,"△ Partial")+COUNTIF(C10:C13,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D38" s="37">
+        <f>IFERROR(SUM(D10:D13)/C38,"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Specificity</t>
+        </is>
+      </c>
+      <c r="C39" s="36">
+        <f>COUNTIF(C16:C19,"✓ Met")+COUNTIF(C16:C19,"△ Partial")+COUNTIF(C16:C19,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D39" s="37">
+        <f>IFERROR(SUM(D16:D19)/C39,"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>SOAP Note Structure</t>
+        </is>
+      </c>
+      <c r="C40" s="36">
+        <f>COUNTIF(C22:C25,"✓ Met")+COUNTIF(C22:C25,"△ Partial")+COUNTIF(C22:C25,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D40" s="37">
+        <f>IFERROR(SUM(D22:D25)/C40,"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>HCC Capture</t>
+        </is>
+      </c>
+      <c r="C41" s="36">
+        <f>COUNTIF(C28:C29,"✓ Met")+COUNTIF(C28:C29,"△ Partial")+COUNTIF(C28:C29,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D41" s="37">
+        <f>IFERROR(SUM(D28:D29)/C41,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Supporting Quality Measures</t>
+        </is>
+      </c>
+      <c r="C42" s="36">
+        <f>COUNTIF(C32:C33,"✓ Met")+COUNTIF(C32:C33,"△ Partial")+COUNTIF(C32:C33,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D42" s="37">
+        <f>IFERROR(SUM(D32:D33)/C42,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OVERALL COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="D44" s="39">
+        <f>IFERROR(SUMPRODUCT(D38:D42,C38:C42)/SUM(C38:C42),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PERFORMANCE BAND</t>
+        </is>
+      </c>
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="18">
+        <f>IF(D44="","",IF(D44&gt;=0.95,"Excellent",IF(D44&gt;=0.90,"Meets Expectations",IF(D44&gt;=0.80,"Needs Improvement","Corrective Education Required"))))</f>
+        <v/>
+      </c>
+      <c r="E45" s="14" t="n"/>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="62" t="n"/>
+      <c r="B46" s="62" t="n"/>
+      <c r="C46" s="62" t="n"/>
+      <c r="D46" s="62" t="n"/>
+      <c r="E46" s="62" t="n"/>
+      <c r="F46" s="62" t="n"/>
+      <c r="G46" s="62" t="n"/>
+      <c r="H46" s="62" t="n"/>
+      <c r="I46" s="62" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="62" t="n"/>
+      <c r="B47" s="62" t="n"/>
+      <c r="C47" s="62" t="n"/>
+      <c r="D47" s="62" t="n"/>
+      <c r="E47" s="62" t="n"/>
+      <c r="F47" s="62" t="n"/>
+      <c r="G47" s="62" t="n"/>
+      <c r="H47" s="62" t="n"/>
+      <c r="I47" s="62" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="62" t="n"/>
+      <c r="B48" s="62" t="n"/>
+      <c r="C48" s="62" t="n"/>
+      <c r="D48" s="62" t="n"/>
+      <c r="E48" s="62" t="n"/>
+      <c r="F48" s="62" t="n"/>
+      <c r="G48" s="62" t="n"/>
+      <c r="H48" s="62" t="n"/>
+      <c r="I48" s="62" t="n"/>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="62" t="n"/>
+      <c r="B49" s="62" t="n"/>
+      <c r="C49" s="62" t="n"/>
+      <c r="D49" s="62" t="n"/>
+      <c r="E49" s="62" t="n"/>
+      <c r="F49" s="62" t="n"/>
+      <c r="G49" s="62" t="n"/>
+      <c r="H49" s="62" t="n"/>
+      <c r="I49" s="62" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="62" t="n"/>
+      <c r="B50" s="62" t="n"/>
+      <c r="C50" s="62" t="n"/>
+      <c r="D50" s="62" t="n"/>
+      <c r="E50" s="62" t="n"/>
+      <c r="F50" s="62" t="n"/>
+      <c r="G50" s="62" t="n"/>
+      <c r="H50" s="62" t="n"/>
+      <c r="I50" s="62" t="n"/>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="62" t="n"/>
+      <c r="B51" s="62" t="n"/>
+      <c r="C51" s="62" t="n"/>
+      <c r="D51" s="62" t="n"/>
+      <c r="E51" s="62" t="n"/>
+      <c r="F51" s="62" t="n"/>
+      <c r="G51" s="62" t="n"/>
+      <c r="H51" s="62" t="n"/>
+      <c r="I51" s="62" t="n"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="62" t="n"/>
+      <c r="B52" s="62" t="n"/>
+      <c r="C52" s="62" t="n"/>
+      <c r="D52" s="62" t="n"/>
+      <c r="E52" s="62" t="n"/>
+      <c r="F52" s="62" t="n"/>
+      <c r="G52" s="62" t="n"/>
+      <c r="H52" s="62" t="n"/>
+      <c r="I52" s="62" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001E7A6E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Clinical Documentation Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>One chart per sheet · tick each item · scoring &amp; rating are automatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>Provider:</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Date of Service:</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>How to audit a claim
+1. Click a Claim 01–10 tab (bottom of the workbook)
+2. Fill yellow header + ratings — auto-scores
+3. Move to the next Claim tab · repeat
+Global metrics roll up automatically
+• Open the Provider Metrics tab — it pulls the 10 claim scores
+  live from the Claim tabs so you see the running provider average.
+Start a new provider (after 10 claims)
+1. Ctrl+click Claim 01 through Claim 10 to group them
+2. Select the yellow header + rating + note cells on any tab
+3. Press Delete → all 10 tabs clear at once
+4. Right-click any tab → Ungroup Sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Claim Number:</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Auditor:</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="51" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Category:</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Payer:</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="52" t="n"/>
+    </row>
+    <row r="7" ht="12" customHeight="1"/>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Documentation element</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Pts</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A · Diagnosis Accuracy   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>All reported diagnoses are clinically supported in the note</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="33">
+        <f>IF(C10="✓ Met",1,IF(C10="△ Partial",0.5,IF(C10="✗ Not Met",0,IF(C10="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Chronic conditions actively addressed at this visit (not just carried forward)</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="33">
+        <f>IF(C11="✓ Met",1,IF(C11="△ Partial",0.5,IF(C11="✗ Not Met",0,IF(C11="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>No unsupported or resolved conditions billed as active</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="33">
+        <f>IF(C12="✓ Met",1,IF(C12="△ Partial",0.5,IF(C12="✗ Not Met",0,IF(C12="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Problem list matches today's assessment &amp; plan</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="33">
+        <f>IF(C13="✓ Met",1,IF(C13="△ Partial",0.5,IF(C13="✗ Not Met",0,IF(C13="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B · Documentation Specificity   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>ICD-10 codes at highest available specificity (avoid 'unspecified')</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="33">
+        <f>IF(C16="✓ Met",1,IF(C16="△ Partial",0.5,IF(C16="✗ Not Met",0,IF(C16="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes: type + complications + control specified</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="33">
+        <f>IF(C17="✓ Met",1,IF(C17="△ Partial",0.5,IF(C17="✗ Not Met",0,IF(C17="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>S / O / A / P sections tell one consistent clinical story</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="33">
+        <f>IF(C18="✓ Met",1,IF(C18="△ Partial",0.5,IF(C18="✗ Not Met",0,IF(C18="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Note signed, dated, and closed by the rendering provider</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="33">
+        <f>IF(C19="✓ Met",1,IF(C19="△ Partial",0.5,IF(C19="✗ Not Met",0,IF(C19="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C · SOAP Note Structure   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Subjective — patient's history, symptoms, and concerns clearly documented</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="33">
+        <f>IF(C22="✓ Met",1,IF(C22="△ Partial",0.5,IF(C22="✗ Not Met",0,IF(C22="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Objective — exam findings, vitals, and relevant test results documented</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="33">
+        <f>IF(C23="✓ Met",1,IF(C23="△ Partial",0.5,IF(C23="✗ Not Met",0,IF(C23="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Assessment — each diagnosis explicitly assessed with clinical reasoning</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="33">
+        <f>IF(C24="✓ Met",1,IF(C24="△ Partial",0.5,IF(C24="✗ Not Met",0,IF(C24="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Plan — treatment plan documented (medication / referral / testing / follow-up)</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="33">
+        <f>IF(C25="✓ Met",1,IF(C25="△ Partial",0.5,IF(C25="✗ Not Met",0,IF(C25="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D · HCC Capture   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Prior-year HCCs recaptured (or explicitly resolved with rationale)</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="33">
+        <f>IF(C28="✓ Met",1,IF(C28="△ Partial",0.5,IF(C28="✗ Not Met",0,IF(C28="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Suspected undocumented chronic conditions captured with support</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="33">
+        <f>IF(C29="✓ Met",1,IF(C29="△ Partial",0.5,IF(C29="✗ Not Met",0,IF(C29="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E · Documentation Supporting Quality Measures   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Screening / measure results documented with specific values (PHQ-9, GAD-7, BMI, BP, HbA1c) — not just 'screened' or 'normal'</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="33">
+        <f>IF(C32="✓ Met",1,IF(C32="△ Partial",0.5,IF(C32="✗ Not Met",0,IF(C32="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Follow-up plan documented when a screening is positive or a result is abnormal (positive PHQ-9 → depression plan; elevated BMI → nutrition counseling)</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33">
+        <f>IF(C33="✓ Met",1,IF(C33="△ Partial",0.5,IF(C33="✗ Not Met",0,IF(C33="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>% Met</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Diagnosis Accuracy</t>
+        </is>
+      </c>
+      <c r="C38" s="36">
+        <f>COUNTIF(C10:C13,"✓ Met")+COUNTIF(C10:C13,"△ Partial")+COUNTIF(C10:C13,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D38" s="37">
+        <f>IFERROR(SUM(D10:D13)/C38,"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Specificity</t>
+        </is>
+      </c>
+      <c r="C39" s="36">
+        <f>COUNTIF(C16:C19,"✓ Met")+COUNTIF(C16:C19,"△ Partial")+COUNTIF(C16:C19,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D39" s="37">
+        <f>IFERROR(SUM(D16:D19)/C39,"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>SOAP Note Structure</t>
+        </is>
+      </c>
+      <c r="C40" s="36">
+        <f>COUNTIF(C22:C25,"✓ Met")+COUNTIF(C22:C25,"△ Partial")+COUNTIF(C22:C25,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D40" s="37">
+        <f>IFERROR(SUM(D22:D25)/C40,"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>HCC Capture</t>
+        </is>
+      </c>
+      <c r="C41" s="36">
+        <f>COUNTIF(C28:C29,"✓ Met")+COUNTIF(C28:C29,"△ Partial")+COUNTIF(C28:C29,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D41" s="37">
+        <f>IFERROR(SUM(D28:D29)/C41,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Supporting Quality Measures</t>
+        </is>
+      </c>
+      <c r="C42" s="36">
+        <f>COUNTIF(C32:C33,"✓ Met")+COUNTIF(C32:C33,"△ Partial")+COUNTIF(C32:C33,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D42" s="37">
+        <f>IFERROR(SUM(D32:D33)/C42,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OVERALL COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="D44" s="39">
+        <f>IFERROR(SUMPRODUCT(D38:D42,C38:C42)/SUM(C38:C42),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PERFORMANCE BAND</t>
+        </is>
+      </c>
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="18">
+        <f>IF(D44="","",IF(D44&gt;=0.95,"Excellent",IF(D44&gt;=0.90,"Meets Expectations",IF(D44&gt;=0.80,"Needs Improvement","Corrective Education Required"))))</f>
+        <v/>
+      </c>
+      <c r="E45" s="14" t="n"/>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="62" t="n"/>
+      <c r="B46" s="62" t="n"/>
+      <c r="C46" s="62" t="n"/>
+      <c r="D46" s="62" t="n"/>
+      <c r="E46" s="62" t="n"/>
+      <c r="F46" s="62" t="n"/>
+      <c r="G46" s="62" t="n"/>
+      <c r="H46" s="62" t="n"/>
+      <c r="I46" s="62" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="62" t="n"/>
+      <c r="B47" s="62" t="n"/>
+      <c r="C47" s="62" t="n"/>
+      <c r="D47" s="62" t="n"/>
+      <c r="E47" s="62" t="n"/>
+      <c r="F47" s="62" t="n"/>
+      <c r="G47" s="62" t="n"/>
+      <c r="H47" s="62" t="n"/>
+      <c r="I47" s="62" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="62" t="n"/>
+      <c r="B48" s="62" t="n"/>
+      <c r="C48" s="62" t="n"/>
+      <c r="D48" s="62" t="n"/>
+      <c r="E48" s="62" t="n"/>
+      <c r="F48" s="62" t="n"/>
+      <c r="G48" s="62" t="n"/>
+      <c r="H48" s="62" t="n"/>
+      <c r="I48" s="62" t="n"/>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="62" t="n"/>
+      <c r="B49" s="62" t="n"/>
+      <c r="C49" s="62" t="n"/>
+      <c r="D49" s="62" t="n"/>
+      <c r="E49" s="62" t="n"/>
+      <c r="F49" s="62" t="n"/>
+      <c r="G49" s="62" t="n"/>
+      <c r="H49" s="62" t="n"/>
+      <c r="I49" s="62" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="62" t="n"/>
+      <c r="B50" s="62" t="n"/>
+      <c r="C50" s="62" t="n"/>
+      <c r="D50" s="62" t="n"/>
+      <c r="E50" s="62" t="n"/>
+      <c r="F50" s="62" t="n"/>
+      <c r="G50" s="62" t="n"/>
+      <c r="H50" s="62" t="n"/>
+      <c r="I50" s="62" t="n"/>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="62" t="n"/>
+      <c r="B51" s="62" t="n"/>
+      <c r="C51" s="62" t="n"/>
+      <c r="D51" s="62" t="n"/>
+      <c r="E51" s="62" t="n"/>
+      <c r="F51" s="62" t="n"/>
+      <c r="G51" s="62" t="n"/>
+      <c r="H51" s="62" t="n"/>
+      <c r="I51" s="62" t="n"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="62" t="n"/>
+      <c r="B52" s="62" t="n"/>
+      <c r="C52" s="62" t="n"/>
+      <c r="D52" s="62" t="n"/>
+      <c r="E52" s="62" t="n"/>
+      <c r="F52" s="62" t="n"/>
+      <c r="G52" s="62" t="n"/>
+      <c r="H52" s="62" t="n"/>
+      <c r="I52" s="62" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001E7A6E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Clinical Documentation Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>One chart per sheet · tick each item · scoring &amp; rating are automatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>Provider:</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Date of Service:</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>How to audit a claim
+1. Click a Claim 01–10 tab (bottom of the workbook)
+2. Fill yellow header + ratings — auto-scores
+3. Move to the next Claim tab · repeat
+Global metrics roll up automatically
+• Open the Provider Metrics tab — it pulls the 10 claim scores
+  live from the Claim tabs so you see the running provider average.
+Start a new provider (after 10 claims)
+1. Ctrl+click Claim 01 through Claim 10 to group them
+2. Select the yellow header + rating + note cells on any tab
+3. Press Delete → all 10 tabs clear at once
+4. Right-click any tab → Ungroup Sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Claim Number:</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Auditor:</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="51" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Category:</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Payer:</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="52" t="n"/>
+    </row>
+    <row r="7" ht="12" customHeight="1"/>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Documentation element</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Pts</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A · Diagnosis Accuracy   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>All reported diagnoses are clinically supported in the note</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="33">
+        <f>IF(C10="✓ Met",1,IF(C10="△ Partial",0.5,IF(C10="✗ Not Met",0,IF(C10="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Chronic conditions actively addressed at this visit (not just carried forward)</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="33">
+        <f>IF(C11="✓ Met",1,IF(C11="△ Partial",0.5,IF(C11="✗ Not Met",0,IF(C11="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>No unsupported or resolved conditions billed as active</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="33">
+        <f>IF(C12="✓ Met",1,IF(C12="△ Partial",0.5,IF(C12="✗ Not Met",0,IF(C12="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Problem list matches today's assessment &amp; plan</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="33">
+        <f>IF(C13="✓ Met",1,IF(C13="△ Partial",0.5,IF(C13="✗ Not Met",0,IF(C13="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B · Documentation Specificity   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>ICD-10 codes at highest available specificity (avoid 'unspecified')</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="33">
+        <f>IF(C16="✓ Met",1,IF(C16="△ Partial",0.5,IF(C16="✗ Not Met",0,IF(C16="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes: type + complications + control specified</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="33">
+        <f>IF(C17="✓ Met",1,IF(C17="△ Partial",0.5,IF(C17="✗ Not Met",0,IF(C17="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>S / O / A / P sections tell one consistent clinical story</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="33">
+        <f>IF(C18="✓ Met",1,IF(C18="△ Partial",0.5,IF(C18="✗ Not Met",0,IF(C18="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Note signed, dated, and closed by the rendering provider</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="33">
+        <f>IF(C19="✓ Met",1,IF(C19="△ Partial",0.5,IF(C19="✗ Not Met",0,IF(C19="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C · SOAP Note Structure   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Subjective — patient's history, symptoms, and concerns clearly documented</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="33">
+        <f>IF(C22="✓ Met",1,IF(C22="△ Partial",0.5,IF(C22="✗ Not Met",0,IF(C22="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Objective — exam findings, vitals, and relevant test results documented</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="33">
+        <f>IF(C23="✓ Met",1,IF(C23="△ Partial",0.5,IF(C23="✗ Not Met",0,IF(C23="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Assessment — each diagnosis explicitly assessed with clinical reasoning</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="33">
+        <f>IF(C24="✓ Met",1,IF(C24="△ Partial",0.5,IF(C24="✗ Not Met",0,IF(C24="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Plan — treatment plan documented (medication / referral / testing / follow-up)</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="33">
+        <f>IF(C25="✓ Met",1,IF(C25="△ Partial",0.5,IF(C25="✗ Not Met",0,IF(C25="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D · HCC Capture   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Prior-year HCCs recaptured (or explicitly resolved with rationale)</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="33">
+        <f>IF(C28="✓ Met",1,IF(C28="△ Partial",0.5,IF(C28="✗ Not Met",0,IF(C28="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Suspected undocumented chronic conditions captured with support</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="33">
+        <f>IF(C29="✓ Met",1,IF(C29="△ Partial",0.5,IF(C29="✗ Not Met",0,IF(C29="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E · Documentation Supporting Quality Measures   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Screening / measure results documented with specific values (PHQ-9, GAD-7, BMI, BP, HbA1c) — not just 'screened' or 'normal'</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="33">
+        <f>IF(C32="✓ Met",1,IF(C32="△ Partial",0.5,IF(C32="✗ Not Met",0,IF(C32="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Follow-up plan documented when a screening is positive or a result is abnormal (positive PHQ-9 → depression plan; elevated BMI → nutrition counseling)</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33">
+        <f>IF(C33="✓ Met",1,IF(C33="△ Partial",0.5,IF(C33="✗ Not Met",0,IF(C33="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>% Met</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Diagnosis Accuracy</t>
+        </is>
+      </c>
+      <c r="C38" s="36">
+        <f>COUNTIF(C10:C13,"✓ Met")+COUNTIF(C10:C13,"△ Partial")+COUNTIF(C10:C13,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D38" s="37">
+        <f>IFERROR(SUM(D10:D13)/C38,"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Specificity</t>
+        </is>
+      </c>
+      <c r="C39" s="36">
+        <f>COUNTIF(C16:C19,"✓ Met")+COUNTIF(C16:C19,"△ Partial")+COUNTIF(C16:C19,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D39" s="37">
+        <f>IFERROR(SUM(D16:D19)/C39,"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>SOAP Note Structure</t>
+        </is>
+      </c>
+      <c r="C40" s="36">
+        <f>COUNTIF(C22:C25,"✓ Met")+COUNTIF(C22:C25,"△ Partial")+COUNTIF(C22:C25,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D40" s="37">
+        <f>IFERROR(SUM(D22:D25)/C40,"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>HCC Capture</t>
+        </is>
+      </c>
+      <c r="C41" s="36">
+        <f>COUNTIF(C28:C29,"✓ Met")+COUNTIF(C28:C29,"△ Partial")+COUNTIF(C28:C29,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D41" s="37">
+        <f>IFERROR(SUM(D28:D29)/C41,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Supporting Quality Measures</t>
+        </is>
+      </c>
+      <c r="C42" s="36">
+        <f>COUNTIF(C32:C33,"✓ Met")+COUNTIF(C32:C33,"△ Partial")+COUNTIF(C32:C33,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D42" s="37">
+        <f>IFERROR(SUM(D32:D33)/C42,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OVERALL COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="D44" s="39">
+        <f>IFERROR(SUMPRODUCT(D38:D42,C38:C42)/SUM(C38:C42),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PERFORMANCE BAND</t>
+        </is>
+      </c>
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="18">
+        <f>IF(D44="","",IF(D44&gt;=0.95,"Excellent",IF(D44&gt;=0.90,"Meets Expectations",IF(D44&gt;=0.80,"Needs Improvement","Corrective Education Required"))))</f>
+        <v/>
+      </c>
+      <c r="E45" s="14" t="n"/>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="62" t="n"/>
+      <c r="B46" s="62" t="n"/>
+      <c r="C46" s="62" t="n"/>
+      <c r="D46" s="62" t="n"/>
+      <c r="E46" s="62" t="n"/>
+      <c r="F46" s="62" t="n"/>
+      <c r="G46" s="62" t="n"/>
+      <c r="H46" s="62" t="n"/>
+      <c r="I46" s="62" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="62" t="n"/>
+      <c r="B47" s="62" t="n"/>
+      <c r="C47" s="62" t="n"/>
+      <c r="D47" s="62" t="n"/>
+      <c r="E47" s="62" t="n"/>
+      <c r="F47" s="62" t="n"/>
+      <c r="G47" s="62" t="n"/>
+      <c r="H47" s="62" t="n"/>
+      <c r="I47" s="62" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="62" t="n"/>
+      <c r="B48" s="62" t="n"/>
+      <c r="C48" s="62" t="n"/>
+      <c r="D48" s="62" t="n"/>
+      <c r="E48" s="62" t="n"/>
+      <c r="F48" s="62" t="n"/>
+      <c r="G48" s="62" t="n"/>
+      <c r="H48" s="62" t="n"/>
+      <c r="I48" s="62" t="n"/>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="62" t="n"/>
+      <c r="B49" s="62" t="n"/>
+      <c r="C49" s="62" t="n"/>
+      <c r="D49" s="62" t="n"/>
+      <c r="E49" s="62" t="n"/>
+      <c r="F49" s="62" t="n"/>
+      <c r="G49" s="62" t="n"/>
+      <c r="H49" s="62" t="n"/>
+      <c r="I49" s="62" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="62" t="n"/>
+      <c r="B50" s="62" t="n"/>
+      <c r="C50" s="62" t="n"/>
+      <c r="D50" s="62" t="n"/>
+      <c r="E50" s="62" t="n"/>
+      <c r="F50" s="62" t="n"/>
+      <c r="G50" s="62" t="n"/>
+      <c r="H50" s="62" t="n"/>
+      <c r="I50" s="62" t="n"/>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="62" t="n"/>
+      <c r="B51" s="62" t="n"/>
+      <c r="C51" s="62" t="n"/>
+      <c r="D51" s="62" t="n"/>
+      <c r="E51" s="62" t="n"/>
+      <c r="F51" s="62" t="n"/>
+      <c r="G51" s="62" t="n"/>
+      <c r="H51" s="62" t="n"/>
+      <c r="I51" s="62" t="n"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="62" t="n"/>
+      <c r="B52" s="62" t="n"/>
+      <c r="C52" s="62" t="n"/>
+      <c r="D52" s="62" t="n"/>
+      <c r="E52" s="62" t="n"/>
+      <c r="F52" s="62" t="n"/>
+      <c r="G52" s="62" t="n"/>
+      <c r="H52" s="62" t="n"/>
+      <c r="I52" s="62" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001E40AF"/>
@@ -4996,7 +7107,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00334155"/>
@@ -5757,7 +7868,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00B45309"/>
@@ -6335,4 +8446,5468 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00B45309"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="68" t="inlineStr">
+        <is>
+          <t>Provider Metrics — Rollup Across the 10 Claim Tabs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="69" t="inlineStr">
+        <is>
+          <t>Live rollup of the current provider's 10 claims. As you fill each Claim tab, this tab shows the running provider average, distribution across bands, and overall Performance Band.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Provider (from Claim 01)</t>
+        </is>
+      </c>
+      <c r="D4" s="88">
+        <f>'Claim 01'!B4</f>
+        <v/>
+      </c>
+      <c r="E4" s="53" t="n"/>
+      <c r="F4" s="54" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="92" t="inlineStr">
+        <is>
+          <t>Claims completed</t>
+        </is>
+      </c>
+      <c r="B6" s="45" t="n"/>
+      <c r="C6" s="45" t="n"/>
+      <c r="D6" s="92" t="inlineStr">
+        <is>
+          <t>Average compliance %</t>
+        </is>
+      </c>
+      <c r="E6" s="45" t="n"/>
+      <c r="F6" s="45" t="n"/>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="93">
+        <f>COUNT('Claim 01:Claim 10'!I44)</f>
+        <v/>
+      </c>
+      <c r="B7" s="94" t="n"/>
+      <c r="C7" s="94" t="n"/>
+      <c r="D7" s="95">
+        <f>IFERROR(AVERAGE('Claim 01:Claim 10'!I44),"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="94" t="n"/>
+      <c r="F7" s="94" t="n"/>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="B8" s="94" t="n"/>
+      <c r="C8" s="94" t="n"/>
+      <c r="E8" s="94" t="n"/>
+      <c r="F8" s="94" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="92" t="inlineStr">
+        <is>
+          <t>Meeting Expectations (≥90%)</t>
+        </is>
+      </c>
+      <c r="B10" s="45" t="n"/>
+      <c r="C10" s="45" t="n"/>
+      <c r="D10" s="92" t="inlineStr">
+        <is>
+          <t>Corrective Required (&lt;80%)</t>
+        </is>
+      </c>
+      <c r="E10" s="45" t="n"/>
+      <c r="F10" s="45" t="n"/>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="93">
+        <f>COUNTIFS(E17:E26,"&gt;=0.9",E17:E26,"&lt;&gt;")</f>
+        <v/>
+      </c>
+      <c r="B11" s="94" t="n"/>
+      <c r="C11" s="94" t="n"/>
+      <c r="D11" s="93">
+        <f>COUNTIFS(E17:E26,"&lt;0.8",E17:E26,"&gt;0")</f>
+        <v/>
+      </c>
+      <c r="E11" s="94" t="n"/>
+      <c r="F11" s="94" t="n"/>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="B12" s="94" t="n"/>
+      <c r="C12" s="94" t="n"/>
+      <c r="E12" s="94" t="n"/>
+      <c r="F12" s="94" t="n"/>
+    </row>
+    <row r="14" ht="12" customHeight="1"/>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Per-Claim Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Provider</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Claim #</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>DOS</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Compliance %</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="10">
+        <f>'Claim 01'!B4</f>
+        <v/>
+      </c>
+      <c r="C17" s="9">
+        <f>'Claim 01'!B5</f>
+        <v/>
+      </c>
+      <c r="D17" s="97">
+        <f>'Claim 01'!D4</f>
+        <v/>
+      </c>
+      <c r="E17" s="12">
+        <f>IFERROR('Claim 01'!I44,"")</f>
+        <v/>
+      </c>
+      <c r="F17" s="9">
+        <f>IFERROR('Claim 01'!I45,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="10">
+        <f>'Claim 02'!B4</f>
+        <v/>
+      </c>
+      <c r="C18" s="9">
+        <f>'Claim 02'!B5</f>
+        <v/>
+      </c>
+      <c r="D18" s="97">
+        <f>'Claim 02'!D4</f>
+        <v/>
+      </c>
+      <c r="E18" s="12">
+        <f>IFERROR('Claim 02'!I44,"")</f>
+        <v/>
+      </c>
+      <c r="F18" s="9">
+        <f>IFERROR('Claim 02'!I45,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="10">
+        <f>'Claim 03'!B4</f>
+        <v/>
+      </c>
+      <c r="C19" s="9">
+        <f>'Claim 03'!B5</f>
+        <v/>
+      </c>
+      <c r="D19" s="97">
+        <f>'Claim 03'!D4</f>
+        <v/>
+      </c>
+      <c r="E19" s="12">
+        <f>IFERROR('Claim 03'!I44,"")</f>
+        <v/>
+      </c>
+      <c r="F19" s="9">
+        <f>IFERROR('Claim 03'!I45,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="10">
+        <f>'Claim 04'!B4</f>
+        <v/>
+      </c>
+      <c r="C20" s="9">
+        <f>'Claim 04'!B5</f>
+        <v/>
+      </c>
+      <c r="D20" s="97">
+        <f>'Claim 04'!D4</f>
+        <v/>
+      </c>
+      <c r="E20" s="12">
+        <f>IFERROR('Claim 04'!I44,"")</f>
+        <v/>
+      </c>
+      <c r="F20" s="9">
+        <f>IFERROR('Claim 04'!I45,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="10">
+        <f>'Claim 05'!B4</f>
+        <v/>
+      </c>
+      <c r="C21" s="9">
+        <f>'Claim 05'!B5</f>
+        <v/>
+      </c>
+      <c r="D21" s="97">
+        <f>'Claim 05'!D4</f>
+        <v/>
+      </c>
+      <c r="E21" s="12">
+        <f>IFERROR('Claim 05'!I44,"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="9">
+        <f>IFERROR('Claim 05'!I45,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" s="10">
+        <f>'Claim 06'!B4</f>
+        <v/>
+      </c>
+      <c r="C22" s="9">
+        <f>'Claim 06'!B5</f>
+        <v/>
+      </c>
+      <c r="D22" s="97">
+        <f>'Claim 06'!D4</f>
+        <v/>
+      </c>
+      <c r="E22" s="12">
+        <f>IFERROR('Claim 06'!I44,"")</f>
+        <v/>
+      </c>
+      <c r="F22" s="9">
+        <f>IFERROR('Claim 06'!I45,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B23" s="10">
+        <f>'Claim 07'!B4</f>
+        <v/>
+      </c>
+      <c r="C23" s="9">
+        <f>'Claim 07'!B5</f>
+        <v/>
+      </c>
+      <c r="D23" s="97">
+        <f>'Claim 07'!D4</f>
+        <v/>
+      </c>
+      <c r="E23" s="12">
+        <f>IFERROR('Claim 07'!I44,"")</f>
+        <v/>
+      </c>
+      <c r="F23" s="9">
+        <f>IFERROR('Claim 07'!I45,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B24" s="10">
+        <f>'Claim 08'!B4</f>
+        <v/>
+      </c>
+      <c r="C24" s="9">
+        <f>'Claim 08'!B5</f>
+        <v/>
+      </c>
+      <c r="D24" s="97">
+        <f>'Claim 08'!D4</f>
+        <v/>
+      </c>
+      <c r="E24" s="12">
+        <f>IFERROR('Claim 08'!I44,"")</f>
+        <v/>
+      </c>
+      <c r="F24" s="9">
+        <f>IFERROR('Claim 08'!I45,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B25" s="10">
+        <f>'Claim 09'!B4</f>
+        <v/>
+      </c>
+      <c r="C25" s="9">
+        <f>'Claim 09'!B5</f>
+        <v/>
+      </c>
+      <c r="D25" s="97">
+        <f>'Claim 09'!D4</f>
+        <v/>
+      </c>
+      <c r="E25" s="12">
+        <f>IFERROR('Claim 09'!I44,"")</f>
+        <v/>
+      </c>
+      <c r="F25" s="9">
+        <f>IFERROR('Claim 09'!I45,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B26" s="10">
+        <f>'Claim 10'!B4</f>
+        <v/>
+      </c>
+      <c r="C26" s="9">
+        <f>'Claim 10'!B5</f>
+        <v/>
+      </c>
+      <c r="D26" s="97">
+        <f>'Claim 10'!D4</f>
+        <v/>
+      </c>
+      <c r="E26" s="12">
+        <f>IFERROR('Claim 10'!I44,"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="9">
+        <f>IFERROR('Claim 10'!I45,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OVERALL PROVIDER PERFORMANCE BAND</t>
+        </is>
+      </c>
+      <c r="E28" s="98">
+        <f>IF(D7="","",IF(D7&gt;=0.95,"Excellent",IF(D7&gt;=0.9,"Meets Expectations",IF(D7&gt;=0.8,"Needs Improvement","Corrective Education Required"))))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Band Distribution (10 claims)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="71" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="B31" s="45" t="n"/>
+      <c r="C31" s="45" t="n"/>
+      <c r="D31" s="45" t="n"/>
+      <c r="E31" s="45" t="n"/>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="99" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+      <c r="B32" s="100" t="n"/>
+      <c r="C32" s="100" t="n"/>
+      <c r="D32" s="100" t="n"/>
+      <c r="E32" s="100" t="n"/>
+      <c r="F32" s="18">
+        <f>COUNTIF(F17:F26,"Excellent")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="101" t="inlineStr">
+        <is>
+          <t>Meets Expectations</t>
+        </is>
+      </c>
+      <c r="B33" s="102" t="n"/>
+      <c r="C33" s="102" t="n"/>
+      <c r="D33" s="102" t="n"/>
+      <c r="E33" s="102" t="n"/>
+      <c r="F33" s="18">
+        <f>COUNTIF(F17:F26,"Meets Expectations")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="103" t="inlineStr">
+        <is>
+          <t>Needs Improvement</t>
+        </is>
+      </c>
+      <c r="B34" s="104" t="n"/>
+      <c r="C34" s="104" t="n"/>
+      <c r="D34" s="104" t="n"/>
+      <c r="E34" s="104" t="n"/>
+      <c r="F34" s="18">
+        <f>COUNTIF(F17:F26,"Needs Improvement")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="105" t="inlineStr">
+        <is>
+          <t>Corrective Education Required</t>
+        </is>
+      </c>
+      <c r="B35" s="106" t="n"/>
+      <c r="C35" s="106" t="n"/>
+      <c r="D35" s="106" t="n"/>
+      <c r="E35" s="106" t="n"/>
+      <c r="F35" s="18">
+        <f>COUNTIF(F17:F26,"Corrective Education Required")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A11:C12"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A7:C8"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D11:F12"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="D7:F8"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="B4:C4"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E17:E26">
+    <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="3">
+      <formula>0.95</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="between" dxfId="0">
+      <formula>0.9</formula>
+      <formula>0.9499</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="between" dxfId="1">
+      <formula>0.8</formula>
+      <formula>0.8999</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="between" dxfId="2">
+      <formula>0.0001</formula>
+      <formula>0.7999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17:F26">
+    <cfRule type="expression" priority="5" dxfId="3">
+      <formula>F17="Excellent"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="0">
+      <formula>F17="Meets Expectations"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" dxfId="1">
+      <formula>F17="Needs Improvement"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" dxfId="2">
+      <formula>F17="Corrective Education Required"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D7">
+    <cfRule type="cellIs" priority="9" operator="greaterThanOrEqual" dxfId="3">
+      <formula>0.95</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="between" dxfId="0">
+      <formula>0.9</formula>
+      <formula>0.9499</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="11" operator="between" dxfId="1">
+      <formula>0.8</formula>
+      <formula>0.8999</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="between" dxfId="2">
+      <formula>0.0001</formula>
+      <formula>0.7999</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E28">
+    <cfRule type="expression" priority="13" dxfId="3">
+      <formula>E28="Excellent"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="14" dxfId="0">
+      <formula>E28="Meets Expectations"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="15" dxfId="1">
+      <formula>E28="Needs Improvement"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="16" dxfId="2">
+      <formula>E28="Corrective Education Required"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001E7A6E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Clinical Documentation Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>One chart per sheet · tick each item · scoring &amp; rating are automatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>Provider:</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Date of Service:</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>How to audit a claim
+1. Click a Claim 01–10 tab (bottom of the workbook)
+2. Fill yellow header + ratings — auto-scores
+3. Move to the next Claim tab · repeat
+Global metrics roll up automatically
+• Open the Provider Metrics tab — it pulls the 10 claim scores
+  live from the Claim tabs so you see the running provider average.
+Start a new provider (after 10 claims)
+1. Ctrl+click Claim 01 through Claim 10 to group them
+2. Select the yellow header + rating + note cells on any tab
+3. Press Delete → all 10 tabs clear at once
+4. Right-click any tab → Ungroup Sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Claim Number:</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Auditor:</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="51" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Category:</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Payer:</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="52" t="n"/>
+    </row>
+    <row r="7" ht="12" customHeight="1"/>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Documentation element</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Pts</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A · Diagnosis Accuracy   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>All reported diagnoses are clinically supported in the note</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="33">
+        <f>IF(C10="✓ Met",1,IF(C10="△ Partial",0.5,IF(C10="✗ Not Met",0,IF(C10="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Chronic conditions actively addressed at this visit (not just carried forward)</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="33">
+        <f>IF(C11="✓ Met",1,IF(C11="△ Partial",0.5,IF(C11="✗ Not Met",0,IF(C11="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>No unsupported or resolved conditions billed as active</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="33">
+        <f>IF(C12="✓ Met",1,IF(C12="△ Partial",0.5,IF(C12="✗ Not Met",0,IF(C12="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Problem list matches today's assessment &amp; plan</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="33">
+        <f>IF(C13="✓ Met",1,IF(C13="△ Partial",0.5,IF(C13="✗ Not Met",0,IF(C13="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B · Documentation Specificity   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>ICD-10 codes at highest available specificity (avoid 'unspecified')</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="33">
+        <f>IF(C16="✓ Met",1,IF(C16="△ Partial",0.5,IF(C16="✗ Not Met",0,IF(C16="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes: type + complications + control specified</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="33">
+        <f>IF(C17="✓ Met",1,IF(C17="△ Partial",0.5,IF(C17="✗ Not Met",0,IF(C17="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>S / O / A / P sections tell one consistent clinical story</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="33">
+        <f>IF(C18="✓ Met",1,IF(C18="△ Partial",0.5,IF(C18="✗ Not Met",0,IF(C18="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Note signed, dated, and closed by the rendering provider</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="33">
+        <f>IF(C19="✓ Met",1,IF(C19="△ Partial",0.5,IF(C19="✗ Not Met",0,IF(C19="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C · SOAP Note Structure   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Subjective — patient's history, symptoms, and concerns clearly documented</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="33">
+        <f>IF(C22="✓ Met",1,IF(C22="△ Partial",0.5,IF(C22="✗ Not Met",0,IF(C22="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Objective — exam findings, vitals, and relevant test results documented</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="33">
+        <f>IF(C23="✓ Met",1,IF(C23="△ Partial",0.5,IF(C23="✗ Not Met",0,IF(C23="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Assessment — each diagnosis explicitly assessed with clinical reasoning</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="33">
+        <f>IF(C24="✓ Met",1,IF(C24="△ Partial",0.5,IF(C24="✗ Not Met",0,IF(C24="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Plan — treatment plan documented (medication / referral / testing / follow-up)</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="33">
+        <f>IF(C25="✓ Met",1,IF(C25="△ Partial",0.5,IF(C25="✗ Not Met",0,IF(C25="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D · HCC Capture   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Prior-year HCCs recaptured (or explicitly resolved with rationale)</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="33">
+        <f>IF(C28="✓ Met",1,IF(C28="△ Partial",0.5,IF(C28="✗ Not Met",0,IF(C28="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Suspected undocumented chronic conditions captured with support</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="33">
+        <f>IF(C29="✓ Met",1,IF(C29="△ Partial",0.5,IF(C29="✗ Not Met",0,IF(C29="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E · Documentation Supporting Quality Measures   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Screening / measure results documented with specific values (PHQ-9, GAD-7, BMI, BP, HbA1c) — not just 'screened' or 'normal'</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="33">
+        <f>IF(C32="✓ Met",1,IF(C32="△ Partial",0.5,IF(C32="✗ Not Met",0,IF(C32="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Follow-up plan documented when a screening is positive or a result is abnormal (positive PHQ-9 → depression plan; elevated BMI → nutrition counseling)</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33">
+        <f>IF(C33="✓ Met",1,IF(C33="△ Partial",0.5,IF(C33="✗ Not Met",0,IF(C33="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>% Met</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Diagnosis Accuracy</t>
+        </is>
+      </c>
+      <c r="C38" s="36">
+        <f>COUNTIF(C10:C13,"✓ Met")+COUNTIF(C10:C13,"△ Partial")+COUNTIF(C10:C13,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D38" s="37">
+        <f>IFERROR(SUM(D10:D13)/C38,"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Specificity</t>
+        </is>
+      </c>
+      <c r="C39" s="36">
+        <f>COUNTIF(C16:C19,"✓ Met")+COUNTIF(C16:C19,"△ Partial")+COUNTIF(C16:C19,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D39" s="37">
+        <f>IFERROR(SUM(D16:D19)/C39,"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>SOAP Note Structure</t>
+        </is>
+      </c>
+      <c r="C40" s="36">
+        <f>COUNTIF(C22:C25,"✓ Met")+COUNTIF(C22:C25,"△ Partial")+COUNTIF(C22:C25,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D40" s="37">
+        <f>IFERROR(SUM(D22:D25)/C40,"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>HCC Capture</t>
+        </is>
+      </c>
+      <c r="C41" s="36">
+        <f>COUNTIF(C28:C29,"✓ Met")+COUNTIF(C28:C29,"△ Partial")+COUNTIF(C28:C29,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D41" s="37">
+        <f>IFERROR(SUM(D28:D29)/C41,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Supporting Quality Measures</t>
+        </is>
+      </c>
+      <c r="C42" s="36">
+        <f>COUNTIF(C32:C33,"✓ Met")+COUNTIF(C32:C33,"△ Partial")+COUNTIF(C32:C33,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D42" s="37">
+        <f>IFERROR(SUM(D32:D33)/C42,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OVERALL COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="D44" s="39">
+        <f>IFERROR(SUMPRODUCT(D38:D42,C38:C42)/SUM(C38:C42),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PERFORMANCE BAND</t>
+        </is>
+      </c>
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="18">
+        <f>IF(D44="","",IF(D44&gt;=0.95,"Excellent",IF(D44&gt;=0.90,"Meets Expectations",IF(D44&gt;=0.80,"Needs Improvement","Corrective Education Required"))))</f>
+        <v/>
+      </c>
+      <c r="E45" s="14" t="n"/>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="62" t="n"/>
+      <c r="B46" s="62" t="n"/>
+      <c r="C46" s="62" t="n"/>
+      <c r="D46" s="62" t="n"/>
+      <c r="E46" s="62" t="n"/>
+      <c r="F46" s="62" t="n"/>
+      <c r="G46" s="62" t="n"/>
+      <c r="H46" s="62" t="n"/>
+      <c r="I46" s="62" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="62" t="n"/>
+      <c r="B47" s="62" t="n"/>
+      <c r="C47" s="62" t="n"/>
+      <c r="D47" s="62" t="n"/>
+      <c r="E47" s="62" t="n"/>
+      <c r="F47" s="62" t="n"/>
+      <c r="G47" s="62" t="n"/>
+      <c r="H47" s="62" t="n"/>
+      <c r="I47" s="62" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="62" t="n"/>
+      <c r="B48" s="62" t="n"/>
+      <c r="C48" s="62" t="n"/>
+      <c r="D48" s="62" t="n"/>
+      <c r="E48" s="62" t="n"/>
+      <c r="F48" s="62" t="n"/>
+      <c r="G48" s="62" t="n"/>
+      <c r="H48" s="62" t="n"/>
+      <c r="I48" s="62" t="n"/>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="62" t="n"/>
+      <c r="B49" s="62" t="n"/>
+      <c r="C49" s="62" t="n"/>
+      <c r="D49" s="62" t="n"/>
+      <c r="E49" s="62" t="n"/>
+      <c r="F49" s="62" t="n"/>
+      <c r="G49" s="62" t="n"/>
+      <c r="H49" s="62" t="n"/>
+      <c r="I49" s="62" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="62" t="n"/>
+      <c r="B50" s="62" t="n"/>
+      <c r="C50" s="62" t="n"/>
+      <c r="D50" s="62" t="n"/>
+      <c r="E50" s="62" t="n"/>
+      <c r="F50" s="62" t="n"/>
+      <c r="G50" s="62" t="n"/>
+      <c r="H50" s="62" t="n"/>
+      <c r="I50" s="62" t="n"/>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="62" t="n"/>
+      <c r="B51" s="62" t="n"/>
+      <c r="C51" s="62" t="n"/>
+      <c r="D51" s="62" t="n"/>
+      <c r="E51" s="62" t="n"/>
+      <c r="F51" s="62" t="n"/>
+      <c r="G51" s="62" t="n"/>
+      <c r="H51" s="62" t="n"/>
+      <c r="I51" s="62" t="n"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="62" t="n"/>
+      <c r="B52" s="62" t="n"/>
+      <c r="C52" s="62" t="n"/>
+      <c r="D52" s="62" t="n"/>
+      <c r="E52" s="62" t="n"/>
+      <c r="F52" s="62" t="n"/>
+      <c r="G52" s="62" t="n"/>
+      <c r="H52" s="62" t="n"/>
+      <c r="I52" s="62" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001E7A6E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Clinical Documentation Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>One chart per sheet · tick each item · scoring &amp; rating are automatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>Provider:</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Date of Service:</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>How to audit a claim
+1. Click a Claim 01–10 tab (bottom of the workbook)
+2. Fill yellow header + ratings — auto-scores
+3. Move to the next Claim tab · repeat
+Global metrics roll up automatically
+• Open the Provider Metrics tab — it pulls the 10 claim scores
+  live from the Claim tabs so you see the running provider average.
+Start a new provider (after 10 claims)
+1. Ctrl+click Claim 01 through Claim 10 to group them
+2. Select the yellow header + rating + note cells on any tab
+3. Press Delete → all 10 tabs clear at once
+4. Right-click any tab → Ungroup Sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Claim Number:</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Auditor:</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="51" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Category:</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Payer:</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="52" t="n"/>
+    </row>
+    <row r="7" ht="12" customHeight="1"/>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Documentation element</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Pts</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A · Diagnosis Accuracy   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>All reported diagnoses are clinically supported in the note</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="33">
+        <f>IF(C10="✓ Met",1,IF(C10="△ Partial",0.5,IF(C10="✗ Not Met",0,IF(C10="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Chronic conditions actively addressed at this visit (not just carried forward)</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="33">
+        <f>IF(C11="✓ Met",1,IF(C11="△ Partial",0.5,IF(C11="✗ Not Met",0,IF(C11="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>No unsupported or resolved conditions billed as active</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="33">
+        <f>IF(C12="✓ Met",1,IF(C12="△ Partial",0.5,IF(C12="✗ Not Met",0,IF(C12="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Problem list matches today's assessment &amp; plan</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="33">
+        <f>IF(C13="✓ Met",1,IF(C13="△ Partial",0.5,IF(C13="✗ Not Met",0,IF(C13="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B · Documentation Specificity   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>ICD-10 codes at highest available specificity (avoid 'unspecified')</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="33">
+        <f>IF(C16="✓ Met",1,IF(C16="△ Partial",0.5,IF(C16="✗ Not Met",0,IF(C16="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes: type + complications + control specified</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="33">
+        <f>IF(C17="✓ Met",1,IF(C17="△ Partial",0.5,IF(C17="✗ Not Met",0,IF(C17="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>S / O / A / P sections tell one consistent clinical story</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="33">
+        <f>IF(C18="✓ Met",1,IF(C18="△ Partial",0.5,IF(C18="✗ Not Met",0,IF(C18="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Note signed, dated, and closed by the rendering provider</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="33">
+        <f>IF(C19="✓ Met",1,IF(C19="△ Partial",0.5,IF(C19="✗ Not Met",0,IF(C19="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C · SOAP Note Structure   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Subjective — patient's history, symptoms, and concerns clearly documented</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="33">
+        <f>IF(C22="✓ Met",1,IF(C22="△ Partial",0.5,IF(C22="✗ Not Met",0,IF(C22="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Objective — exam findings, vitals, and relevant test results documented</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="33">
+        <f>IF(C23="✓ Met",1,IF(C23="△ Partial",0.5,IF(C23="✗ Not Met",0,IF(C23="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Assessment — each diagnosis explicitly assessed with clinical reasoning</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="33">
+        <f>IF(C24="✓ Met",1,IF(C24="△ Partial",0.5,IF(C24="✗ Not Met",0,IF(C24="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Plan — treatment plan documented (medication / referral / testing / follow-up)</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="33">
+        <f>IF(C25="✓ Met",1,IF(C25="△ Partial",0.5,IF(C25="✗ Not Met",0,IF(C25="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D · HCC Capture   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Prior-year HCCs recaptured (or explicitly resolved with rationale)</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="33">
+        <f>IF(C28="✓ Met",1,IF(C28="△ Partial",0.5,IF(C28="✗ Not Met",0,IF(C28="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Suspected undocumented chronic conditions captured with support</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="33">
+        <f>IF(C29="✓ Met",1,IF(C29="△ Partial",0.5,IF(C29="✗ Not Met",0,IF(C29="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E · Documentation Supporting Quality Measures   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Screening / measure results documented with specific values (PHQ-9, GAD-7, BMI, BP, HbA1c) — not just 'screened' or 'normal'</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="33">
+        <f>IF(C32="✓ Met",1,IF(C32="△ Partial",0.5,IF(C32="✗ Not Met",0,IF(C32="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Follow-up plan documented when a screening is positive or a result is abnormal (positive PHQ-9 → depression plan; elevated BMI → nutrition counseling)</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33">
+        <f>IF(C33="✓ Met",1,IF(C33="△ Partial",0.5,IF(C33="✗ Not Met",0,IF(C33="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>% Met</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Diagnosis Accuracy</t>
+        </is>
+      </c>
+      <c r="C38" s="36">
+        <f>COUNTIF(C10:C13,"✓ Met")+COUNTIF(C10:C13,"△ Partial")+COUNTIF(C10:C13,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D38" s="37">
+        <f>IFERROR(SUM(D10:D13)/C38,"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Specificity</t>
+        </is>
+      </c>
+      <c r="C39" s="36">
+        <f>COUNTIF(C16:C19,"✓ Met")+COUNTIF(C16:C19,"△ Partial")+COUNTIF(C16:C19,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D39" s="37">
+        <f>IFERROR(SUM(D16:D19)/C39,"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>SOAP Note Structure</t>
+        </is>
+      </c>
+      <c r="C40" s="36">
+        <f>COUNTIF(C22:C25,"✓ Met")+COUNTIF(C22:C25,"△ Partial")+COUNTIF(C22:C25,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D40" s="37">
+        <f>IFERROR(SUM(D22:D25)/C40,"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>HCC Capture</t>
+        </is>
+      </c>
+      <c r="C41" s="36">
+        <f>COUNTIF(C28:C29,"✓ Met")+COUNTIF(C28:C29,"△ Partial")+COUNTIF(C28:C29,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D41" s="37">
+        <f>IFERROR(SUM(D28:D29)/C41,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Supporting Quality Measures</t>
+        </is>
+      </c>
+      <c r="C42" s="36">
+        <f>COUNTIF(C32:C33,"✓ Met")+COUNTIF(C32:C33,"△ Partial")+COUNTIF(C32:C33,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D42" s="37">
+        <f>IFERROR(SUM(D32:D33)/C42,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OVERALL COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="D44" s="39">
+        <f>IFERROR(SUMPRODUCT(D38:D42,C38:C42)/SUM(C38:C42),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PERFORMANCE BAND</t>
+        </is>
+      </c>
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="18">
+        <f>IF(D44="","",IF(D44&gt;=0.95,"Excellent",IF(D44&gt;=0.90,"Meets Expectations",IF(D44&gt;=0.80,"Needs Improvement","Corrective Education Required"))))</f>
+        <v/>
+      </c>
+      <c r="E45" s="14" t="n"/>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="62" t="n"/>
+      <c r="B46" s="62" t="n"/>
+      <c r="C46" s="62" t="n"/>
+      <c r="D46" s="62" t="n"/>
+      <c r="E46" s="62" t="n"/>
+      <c r="F46" s="62" t="n"/>
+      <c r="G46" s="62" t="n"/>
+      <c r="H46" s="62" t="n"/>
+      <c r="I46" s="62" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="62" t="n"/>
+      <c r="B47" s="62" t="n"/>
+      <c r="C47" s="62" t="n"/>
+      <c r="D47" s="62" t="n"/>
+      <c r="E47" s="62" t="n"/>
+      <c r="F47" s="62" t="n"/>
+      <c r="G47" s="62" t="n"/>
+      <c r="H47" s="62" t="n"/>
+      <c r="I47" s="62" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="62" t="n"/>
+      <c r="B48" s="62" t="n"/>
+      <c r="C48" s="62" t="n"/>
+      <c r="D48" s="62" t="n"/>
+      <c r="E48" s="62" t="n"/>
+      <c r="F48" s="62" t="n"/>
+      <c r="G48" s="62" t="n"/>
+      <c r="H48" s="62" t="n"/>
+      <c r="I48" s="62" t="n"/>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="62" t="n"/>
+      <c r="B49" s="62" t="n"/>
+      <c r="C49" s="62" t="n"/>
+      <c r="D49" s="62" t="n"/>
+      <c r="E49" s="62" t="n"/>
+      <c r="F49" s="62" t="n"/>
+      <c r="G49" s="62" t="n"/>
+      <c r="H49" s="62" t="n"/>
+      <c r="I49" s="62" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="62" t="n"/>
+      <c r="B50" s="62" t="n"/>
+      <c r="C50" s="62" t="n"/>
+      <c r="D50" s="62" t="n"/>
+      <c r="E50" s="62" t="n"/>
+      <c r="F50" s="62" t="n"/>
+      <c r="G50" s="62" t="n"/>
+      <c r="H50" s="62" t="n"/>
+      <c r="I50" s="62" t="n"/>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="62" t="n"/>
+      <c r="B51" s="62" t="n"/>
+      <c r="C51" s="62" t="n"/>
+      <c r="D51" s="62" t="n"/>
+      <c r="E51" s="62" t="n"/>
+      <c r="F51" s="62" t="n"/>
+      <c r="G51" s="62" t="n"/>
+      <c r="H51" s="62" t="n"/>
+      <c r="I51" s="62" t="n"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="62" t="n"/>
+      <c r="B52" s="62" t="n"/>
+      <c r="C52" s="62" t="n"/>
+      <c r="D52" s="62" t="n"/>
+      <c r="E52" s="62" t="n"/>
+      <c r="F52" s="62" t="n"/>
+      <c r="G52" s="62" t="n"/>
+      <c r="H52" s="62" t="n"/>
+      <c r="I52" s="62" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001E7A6E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Clinical Documentation Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>One chart per sheet · tick each item · scoring &amp; rating are automatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>Provider:</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Date of Service:</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>How to audit a claim
+1. Click a Claim 01–10 tab (bottom of the workbook)
+2. Fill yellow header + ratings — auto-scores
+3. Move to the next Claim tab · repeat
+Global metrics roll up automatically
+• Open the Provider Metrics tab — it pulls the 10 claim scores
+  live from the Claim tabs so you see the running provider average.
+Start a new provider (after 10 claims)
+1. Ctrl+click Claim 01 through Claim 10 to group them
+2. Select the yellow header + rating + note cells on any tab
+3. Press Delete → all 10 tabs clear at once
+4. Right-click any tab → Ungroup Sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Claim Number:</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Auditor:</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="51" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Category:</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Payer:</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="52" t="n"/>
+    </row>
+    <row r="7" ht="12" customHeight="1"/>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Documentation element</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Pts</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A · Diagnosis Accuracy   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>All reported diagnoses are clinically supported in the note</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="33">
+        <f>IF(C10="✓ Met",1,IF(C10="△ Partial",0.5,IF(C10="✗ Not Met",0,IF(C10="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Chronic conditions actively addressed at this visit (not just carried forward)</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="33">
+        <f>IF(C11="✓ Met",1,IF(C11="△ Partial",0.5,IF(C11="✗ Not Met",0,IF(C11="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>No unsupported or resolved conditions billed as active</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="33">
+        <f>IF(C12="✓ Met",1,IF(C12="△ Partial",0.5,IF(C12="✗ Not Met",0,IF(C12="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Problem list matches today's assessment &amp; plan</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="33">
+        <f>IF(C13="✓ Met",1,IF(C13="△ Partial",0.5,IF(C13="✗ Not Met",0,IF(C13="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B · Documentation Specificity   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>ICD-10 codes at highest available specificity (avoid 'unspecified')</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="33">
+        <f>IF(C16="✓ Met",1,IF(C16="△ Partial",0.5,IF(C16="✗ Not Met",0,IF(C16="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes: type + complications + control specified</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="33">
+        <f>IF(C17="✓ Met",1,IF(C17="△ Partial",0.5,IF(C17="✗ Not Met",0,IF(C17="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>S / O / A / P sections tell one consistent clinical story</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="33">
+        <f>IF(C18="✓ Met",1,IF(C18="△ Partial",0.5,IF(C18="✗ Not Met",0,IF(C18="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Note signed, dated, and closed by the rendering provider</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="33">
+        <f>IF(C19="✓ Met",1,IF(C19="△ Partial",0.5,IF(C19="✗ Not Met",0,IF(C19="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C · SOAP Note Structure   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Subjective — patient's history, symptoms, and concerns clearly documented</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="33">
+        <f>IF(C22="✓ Met",1,IF(C22="△ Partial",0.5,IF(C22="✗ Not Met",0,IF(C22="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Objective — exam findings, vitals, and relevant test results documented</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="33">
+        <f>IF(C23="✓ Met",1,IF(C23="△ Partial",0.5,IF(C23="✗ Not Met",0,IF(C23="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Assessment — each diagnosis explicitly assessed with clinical reasoning</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="33">
+        <f>IF(C24="✓ Met",1,IF(C24="△ Partial",0.5,IF(C24="✗ Not Met",0,IF(C24="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Plan — treatment plan documented (medication / referral / testing / follow-up)</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="33">
+        <f>IF(C25="✓ Met",1,IF(C25="△ Partial",0.5,IF(C25="✗ Not Met",0,IF(C25="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D · HCC Capture   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Prior-year HCCs recaptured (or explicitly resolved with rationale)</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="33">
+        <f>IF(C28="✓ Met",1,IF(C28="△ Partial",0.5,IF(C28="✗ Not Met",0,IF(C28="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Suspected undocumented chronic conditions captured with support</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="33">
+        <f>IF(C29="✓ Met",1,IF(C29="△ Partial",0.5,IF(C29="✗ Not Met",0,IF(C29="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E · Documentation Supporting Quality Measures   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Screening / measure results documented with specific values (PHQ-9, GAD-7, BMI, BP, HbA1c) — not just 'screened' or 'normal'</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="33">
+        <f>IF(C32="✓ Met",1,IF(C32="△ Partial",0.5,IF(C32="✗ Not Met",0,IF(C32="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Follow-up plan documented when a screening is positive or a result is abnormal (positive PHQ-9 → depression plan; elevated BMI → nutrition counseling)</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33">
+        <f>IF(C33="✓ Met",1,IF(C33="△ Partial",0.5,IF(C33="✗ Not Met",0,IF(C33="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>% Met</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Diagnosis Accuracy</t>
+        </is>
+      </c>
+      <c r="C38" s="36">
+        <f>COUNTIF(C10:C13,"✓ Met")+COUNTIF(C10:C13,"△ Partial")+COUNTIF(C10:C13,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D38" s="37">
+        <f>IFERROR(SUM(D10:D13)/C38,"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Specificity</t>
+        </is>
+      </c>
+      <c r="C39" s="36">
+        <f>COUNTIF(C16:C19,"✓ Met")+COUNTIF(C16:C19,"△ Partial")+COUNTIF(C16:C19,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D39" s="37">
+        <f>IFERROR(SUM(D16:D19)/C39,"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>SOAP Note Structure</t>
+        </is>
+      </c>
+      <c r="C40" s="36">
+        <f>COUNTIF(C22:C25,"✓ Met")+COUNTIF(C22:C25,"△ Partial")+COUNTIF(C22:C25,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D40" s="37">
+        <f>IFERROR(SUM(D22:D25)/C40,"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>HCC Capture</t>
+        </is>
+      </c>
+      <c r="C41" s="36">
+        <f>COUNTIF(C28:C29,"✓ Met")+COUNTIF(C28:C29,"△ Partial")+COUNTIF(C28:C29,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D41" s="37">
+        <f>IFERROR(SUM(D28:D29)/C41,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Supporting Quality Measures</t>
+        </is>
+      </c>
+      <c r="C42" s="36">
+        <f>COUNTIF(C32:C33,"✓ Met")+COUNTIF(C32:C33,"△ Partial")+COUNTIF(C32:C33,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D42" s="37">
+        <f>IFERROR(SUM(D32:D33)/C42,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OVERALL COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="D44" s="39">
+        <f>IFERROR(SUMPRODUCT(D38:D42,C38:C42)/SUM(C38:C42),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PERFORMANCE BAND</t>
+        </is>
+      </c>
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="18">
+        <f>IF(D44="","",IF(D44&gt;=0.95,"Excellent",IF(D44&gt;=0.90,"Meets Expectations",IF(D44&gt;=0.80,"Needs Improvement","Corrective Education Required"))))</f>
+        <v/>
+      </c>
+      <c r="E45" s="14" t="n"/>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="62" t="n"/>
+      <c r="B46" s="62" t="n"/>
+      <c r="C46" s="62" t="n"/>
+      <c r="D46" s="62" t="n"/>
+      <c r="E46" s="62" t="n"/>
+      <c r="F46" s="62" t="n"/>
+      <c r="G46" s="62" t="n"/>
+      <c r="H46" s="62" t="n"/>
+      <c r="I46" s="62" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="62" t="n"/>
+      <c r="B47" s="62" t="n"/>
+      <c r="C47" s="62" t="n"/>
+      <c r="D47" s="62" t="n"/>
+      <c r="E47" s="62" t="n"/>
+      <c r="F47" s="62" t="n"/>
+      <c r="G47" s="62" t="n"/>
+      <c r="H47" s="62" t="n"/>
+      <c r="I47" s="62" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="62" t="n"/>
+      <c r="B48" s="62" t="n"/>
+      <c r="C48" s="62" t="n"/>
+      <c r="D48" s="62" t="n"/>
+      <c r="E48" s="62" t="n"/>
+      <c r="F48" s="62" t="n"/>
+      <c r="G48" s="62" t="n"/>
+      <c r="H48" s="62" t="n"/>
+      <c r="I48" s="62" t="n"/>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="62" t="n"/>
+      <c r="B49" s="62" t="n"/>
+      <c r="C49" s="62" t="n"/>
+      <c r="D49" s="62" t="n"/>
+      <c r="E49" s="62" t="n"/>
+      <c r="F49" s="62" t="n"/>
+      <c r="G49" s="62" t="n"/>
+      <c r="H49" s="62" t="n"/>
+      <c r="I49" s="62" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="62" t="n"/>
+      <c r="B50" s="62" t="n"/>
+      <c r="C50" s="62" t="n"/>
+      <c r="D50" s="62" t="n"/>
+      <c r="E50" s="62" t="n"/>
+      <c r="F50" s="62" t="n"/>
+      <c r="G50" s="62" t="n"/>
+      <c r="H50" s="62" t="n"/>
+      <c r="I50" s="62" t="n"/>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="62" t="n"/>
+      <c r="B51" s="62" t="n"/>
+      <c r="C51" s="62" t="n"/>
+      <c r="D51" s="62" t="n"/>
+      <c r="E51" s="62" t="n"/>
+      <c r="F51" s="62" t="n"/>
+      <c r="G51" s="62" t="n"/>
+      <c r="H51" s="62" t="n"/>
+      <c r="I51" s="62" t="n"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="62" t="n"/>
+      <c r="B52" s="62" t="n"/>
+      <c r="C52" s="62" t="n"/>
+      <c r="D52" s="62" t="n"/>
+      <c r="E52" s="62" t="n"/>
+      <c r="F52" s="62" t="n"/>
+      <c r="G52" s="62" t="n"/>
+      <c r="H52" s="62" t="n"/>
+      <c r="I52" s="62" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001E7A6E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Clinical Documentation Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>One chart per sheet · tick each item · scoring &amp; rating are automatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>Provider:</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Date of Service:</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>How to audit a claim
+1. Click a Claim 01–10 tab (bottom of the workbook)
+2. Fill yellow header + ratings — auto-scores
+3. Move to the next Claim tab · repeat
+Global metrics roll up automatically
+• Open the Provider Metrics tab — it pulls the 10 claim scores
+  live from the Claim tabs so you see the running provider average.
+Start a new provider (after 10 claims)
+1. Ctrl+click Claim 01 through Claim 10 to group them
+2. Select the yellow header + rating + note cells on any tab
+3. Press Delete → all 10 tabs clear at once
+4. Right-click any tab → Ungroup Sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Claim Number:</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Auditor:</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="51" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Category:</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Payer:</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="52" t="n"/>
+    </row>
+    <row r="7" ht="12" customHeight="1"/>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Documentation element</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Pts</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A · Diagnosis Accuracy   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>All reported diagnoses are clinically supported in the note</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="33">
+        <f>IF(C10="✓ Met",1,IF(C10="△ Partial",0.5,IF(C10="✗ Not Met",0,IF(C10="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Chronic conditions actively addressed at this visit (not just carried forward)</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="33">
+        <f>IF(C11="✓ Met",1,IF(C11="△ Partial",0.5,IF(C11="✗ Not Met",0,IF(C11="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>No unsupported or resolved conditions billed as active</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="33">
+        <f>IF(C12="✓ Met",1,IF(C12="△ Partial",0.5,IF(C12="✗ Not Met",0,IF(C12="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Problem list matches today's assessment &amp; plan</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="33">
+        <f>IF(C13="✓ Met",1,IF(C13="△ Partial",0.5,IF(C13="✗ Not Met",0,IF(C13="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B · Documentation Specificity   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>ICD-10 codes at highest available specificity (avoid 'unspecified')</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="33">
+        <f>IF(C16="✓ Met",1,IF(C16="△ Partial",0.5,IF(C16="✗ Not Met",0,IF(C16="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes: type + complications + control specified</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="33">
+        <f>IF(C17="✓ Met",1,IF(C17="△ Partial",0.5,IF(C17="✗ Not Met",0,IF(C17="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>S / O / A / P sections tell one consistent clinical story</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="33">
+        <f>IF(C18="✓ Met",1,IF(C18="△ Partial",0.5,IF(C18="✗ Not Met",0,IF(C18="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Note signed, dated, and closed by the rendering provider</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="33">
+        <f>IF(C19="✓ Met",1,IF(C19="△ Partial",0.5,IF(C19="✗ Not Met",0,IF(C19="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C · SOAP Note Structure   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Subjective — patient's history, symptoms, and concerns clearly documented</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="33">
+        <f>IF(C22="✓ Met",1,IF(C22="△ Partial",0.5,IF(C22="✗ Not Met",0,IF(C22="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Objective — exam findings, vitals, and relevant test results documented</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="33">
+        <f>IF(C23="✓ Met",1,IF(C23="△ Partial",0.5,IF(C23="✗ Not Met",0,IF(C23="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Assessment — each diagnosis explicitly assessed with clinical reasoning</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="33">
+        <f>IF(C24="✓ Met",1,IF(C24="△ Partial",0.5,IF(C24="✗ Not Met",0,IF(C24="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Plan — treatment plan documented (medication / referral / testing / follow-up)</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="33">
+        <f>IF(C25="✓ Met",1,IF(C25="△ Partial",0.5,IF(C25="✗ Not Met",0,IF(C25="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D · HCC Capture   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Prior-year HCCs recaptured (or explicitly resolved with rationale)</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="33">
+        <f>IF(C28="✓ Met",1,IF(C28="△ Partial",0.5,IF(C28="✗ Not Met",0,IF(C28="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Suspected undocumented chronic conditions captured with support</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="33">
+        <f>IF(C29="✓ Met",1,IF(C29="△ Partial",0.5,IF(C29="✗ Not Met",0,IF(C29="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E · Documentation Supporting Quality Measures   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Screening / measure results documented with specific values (PHQ-9, GAD-7, BMI, BP, HbA1c) — not just 'screened' or 'normal'</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="33">
+        <f>IF(C32="✓ Met",1,IF(C32="△ Partial",0.5,IF(C32="✗ Not Met",0,IF(C32="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Follow-up plan documented when a screening is positive or a result is abnormal (positive PHQ-9 → depression plan; elevated BMI → nutrition counseling)</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33">
+        <f>IF(C33="✓ Met",1,IF(C33="△ Partial",0.5,IF(C33="✗ Not Met",0,IF(C33="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>% Met</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Diagnosis Accuracy</t>
+        </is>
+      </c>
+      <c r="C38" s="36">
+        <f>COUNTIF(C10:C13,"✓ Met")+COUNTIF(C10:C13,"△ Partial")+COUNTIF(C10:C13,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D38" s="37">
+        <f>IFERROR(SUM(D10:D13)/C38,"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Specificity</t>
+        </is>
+      </c>
+      <c r="C39" s="36">
+        <f>COUNTIF(C16:C19,"✓ Met")+COUNTIF(C16:C19,"△ Partial")+COUNTIF(C16:C19,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D39" s="37">
+        <f>IFERROR(SUM(D16:D19)/C39,"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>SOAP Note Structure</t>
+        </is>
+      </c>
+      <c r="C40" s="36">
+        <f>COUNTIF(C22:C25,"✓ Met")+COUNTIF(C22:C25,"△ Partial")+COUNTIF(C22:C25,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D40" s="37">
+        <f>IFERROR(SUM(D22:D25)/C40,"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>HCC Capture</t>
+        </is>
+      </c>
+      <c r="C41" s="36">
+        <f>COUNTIF(C28:C29,"✓ Met")+COUNTIF(C28:C29,"△ Partial")+COUNTIF(C28:C29,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D41" s="37">
+        <f>IFERROR(SUM(D28:D29)/C41,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Supporting Quality Measures</t>
+        </is>
+      </c>
+      <c r="C42" s="36">
+        <f>COUNTIF(C32:C33,"✓ Met")+COUNTIF(C32:C33,"△ Partial")+COUNTIF(C32:C33,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D42" s="37">
+        <f>IFERROR(SUM(D32:D33)/C42,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OVERALL COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="D44" s="39">
+        <f>IFERROR(SUMPRODUCT(D38:D42,C38:C42)/SUM(C38:C42),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PERFORMANCE BAND</t>
+        </is>
+      </c>
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="18">
+        <f>IF(D44="","",IF(D44&gt;=0.95,"Excellent",IF(D44&gt;=0.90,"Meets Expectations",IF(D44&gt;=0.80,"Needs Improvement","Corrective Education Required"))))</f>
+        <v/>
+      </c>
+      <c r="E45" s="14" t="n"/>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="62" t="n"/>
+      <c r="B46" s="62" t="n"/>
+      <c r="C46" s="62" t="n"/>
+      <c r="D46" s="62" t="n"/>
+      <c r="E46" s="62" t="n"/>
+      <c r="F46" s="62" t="n"/>
+      <c r="G46" s="62" t="n"/>
+      <c r="H46" s="62" t="n"/>
+      <c r="I46" s="62" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="62" t="n"/>
+      <c r="B47" s="62" t="n"/>
+      <c r="C47" s="62" t="n"/>
+      <c r="D47" s="62" t="n"/>
+      <c r="E47" s="62" t="n"/>
+      <c r="F47" s="62" t="n"/>
+      <c r="G47" s="62" t="n"/>
+      <c r="H47" s="62" t="n"/>
+      <c r="I47" s="62" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="62" t="n"/>
+      <c r="B48" s="62" t="n"/>
+      <c r="C48" s="62" t="n"/>
+      <c r="D48" s="62" t="n"/>
+      <c r="E48" s="62" t="n"/>
+      <c r="F48" s="62" t="n"/>
+      <c r="G48" s="62" t="n"/>
+      <c r="H48" s="62" t="n"/>
+      <c r="I48" s="62" t="n"/>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="62" t="n"/>
+      <c r="B49" s="62" t="n"/>
+      <c r="C49" s="62" t="n"/>
+      <c r="D49" s="62" t="n"/>
+      <c r="E49" s="62" t="n"/>
+      <c r="F49" s="62" t="n"/>
+      <c r="G49" s="62" t="n"/>
+      <c r="H49" s="62" t="n"/>
+      <c r="I49" s="62" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="62" t="n"/>
+      <c r="B50" s="62" t="n"/>
+      <c r="C50" s="62" t="n"/>
+      <c r="D50" s="62" t="n"/>
+      <c r="E50" s="62" t="n"/>
+      <c r="F50" s="62" t="n"/>
+      <c r="G50" s="62" t="n"/>
+      <c r="H50" s="62" t="n"/>
+      <c r="I50" s="62" t="n"/>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="62" t="n"/>
+      <c r="B51" s="62" t="n"/>
+      <c r="C51" s="62" t="n"/>
+      <c r="D51" s="62" t="n"/>
+      <c r="E51" s="62" t="n"/>
+      <c r="F51" s="62" t="n"/>
+      <c r="G51" s="62" t="n"/>
+      <c r="H51" s="62" t="n"/>
+      <c r="I51" s="62" t="n"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="62" t="n"/>
+      <c r="B52" s="62" t="n"/>
+      <c r="C52" s="62" t="n"/>
+      <c r="D52" s="62" t="n"/>
+      <c r="E52" s="62" t="n"/>
+      <c r="F52" s="62" t="n"/>
+      <c r="G52" s="62" t="n"/>
+      <c r="H52" s="62" t="n"/>
+      <c r="I52" s="62" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001E7A6E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Clinical Documentation Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>One chart per sheet · tick each item · scoring &amp; rating are automatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>Provider:</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Date of Service:</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>How to audit a claim
+1. Click a Claim 01–10 tab (bottom of the workbook)
+2. Fill yellow header + ratings — auto-scores
+3. Move to the next Claim tab · repeat
+Global metrics roll up automatically
+• Open the Provider Metrics tab — it pulls the 10 claim scores
+  live from the Claim tabs so you see the running provider average.
+Start a new provider (after 10 claims)
+1. Ctrl+click Claim 01 through Claim 10 to group them
+2. Select the yellow header + rating + note cells on any tab
+3. Press Delete → all 10 tabs clear at once
+4. Right-click any tab → Ungroup Sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Claim Number:</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Auditor:</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="51" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Category:</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Payer:</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="52" t="n"/>
+    </row>
+    <row r="7" ht="12" customHeight="1"/>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Documentation element</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Pts</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A · Diagnosis Accuracy   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>All reported diagnoses are clinically supported in the note</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="33">
+        <f>IF(C10="✓ Met",1,IF(C10="△ Partial",0.5,IF(C10="✗ Not Met",0,IF(C10="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Chronic conditions actively addressed at this visit (not just carried forward)</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="33">
+        <f>IF(C11="✓ Met",1,IF(C11="△ Partial",0.5,IF(C11="✗ Not Met",0,IF(C11="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>No unsupported or resolved conditions billed as active</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="33">
+        <f>IF(C12="✓ Met",1,IF(C12="△ Partial",0.5,IF(C12="✗ Not Met",0,IF(C12="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Problem list matches today's assessment &amp; plan</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="33">
+        <f>IF(C13="✓ Met",1,IF(C13="△ Partial",0.5,IF(C13="✗ Not Met",0,IF(C13="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B · Documentation Specificity   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>ICD-10 codes at highest available specificity (avoid 'unspecified')</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="33">
+        <f>IF(C16="✓ Met",1,IF(C16="△ Partial",0.5,IF(C16="✗ Not Met",0,IF(C16="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes: type + complications + control specified</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="33">
+        <f>IF(C17="✓ Met",1,IF(C17="△ Partial",0.5,IF(C17="✗ Not Met",0,IF(C17="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>S / O / A / P sections tell one consistent clinical story</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="33">
+        <f>IF(C18="✓ Met",1,IF(C18="△ Partial",0.5,IF(C18="✗ Not Met",0,IF(C18="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Note signed, dated, and closed by the rendering provider</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="33">
+        <f>IF(C19="✓ Met",1,IF(C19="△ Partial",0.5,IF(C19="✗ Not Met",0,IF(C19="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C · SOAP Note Structure   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Subjective — patient's history, symptoms, and concerns clearly documented</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="33">
+        <f>IF(C22="✓ Met",1,IF(C22="△ Partial",0.5,IF(C22="✗ Not Met",0,IF(C22="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Objective — exam findings, vitals, and relevant test results documented</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="33">
+        <f>IF(C23="✓ Met",1,IF(C23="△ Partial",0.5,IF(C23="✗ Not Met",0,IF(C23="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Assessment — each diagnosis explicitly assessed with clinical reasoning</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="33">
+        <f>IF(C24="✓ Met",1,IF(C24="△ Partial",0.5,IF(C24="✗ Not Met",0,IF(C24="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Plan — treatment plan documented (medication / referral / testing / follow-up)</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="33">
+        <f>IF(C25="✓ Met",1,IF(C25="△ Partial",0.5,IF(C25="✗ Not Met",0,IF(C25="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D · HCC Capture   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Prior-year HCCs recaptured (or explicitly resolved with rationale)</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="33">
+        <f>IF(C28="✓ Met",1,IF(C28="△ Partial",0.5,IF(C28="✗ Not Met",0,IF(C28="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Suspected undocumented chronic conditions captured with support</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="33">
+        <f>IF(C29="✓ Met",1,IF(C29="△ Partial",0.5,IF(C29="✗ Not Met",0,IF(C29="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E · Documentation Supporting Quality Measures   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Screening / measure results documented with specific values (PHQ-9, GAD-7, BMI, BP, HbA1c) — not just 'screened' or 'normal'</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="33">
+        <f>IF(C32="✓ Met",1,IF(C32="△ Partial",0.5,IF(C32="✗ Not Met",0,IF(C32="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Follow-up plan documented when a screening is positive or a result is abnormal (positive PHQ-9 → depression plan; elevated BMI → nutrition counseling)</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33">
+        <f>IF(C33="✓ Met",1,IF(C33="△ Partial",0.5,IF(C33="✗ Not Met",0,IF(C33="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>% Met</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Diagnosis Accuracy</t>
+        </is>
+      </c>
+      <c r="C38" s="36">
+        <f>COUNTIF(C10:C13,"✓ Met")+COUNTIF(C10:C13,"△ Partial")+COUNTIF(C10:C13,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D38" s="37">
+        <f>IFERROR(SUM(D10:D13)/C38,"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Specificity</t>
+        </is>
+      </c>
+      <c r="C39" s="36">
+        <f>COUNTIF(C16:C19,"✓ Met")+COUNTIF(C16:C19,"△ Partial")+COUNTIF(C16:C19,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D39" s="37">
+        <f>IFERROR(SUM(D16:D19)/C39,"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>SOAP Note Structure</t>
+        </is>
+      </c>
+      <c r="C40" s="36">
+        <f>COUNTIF(C22:C25,"✓ Met")+COUNTIF(C22:C25,"△ Partial")+COUNTIF(C22:C25,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D40" s="37">
+        <f>IFERROR(SUM(D22:D25)/C40,"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>HCC Capture</t>
+        </is>
+      </c>
+      <c r="C41" s="36">
+        <f>COUNTIF(C28:C29,"✓ Met")+COUNTIF(C28:C29,"△ Partial")+COUNTIF(C28:C29,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D41" s="37">
+        <f>IFERROR(SUM(D28:D29)/C41,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Supporting Quality Measures</t>
+        </is>
+      </c>
+      <c r="C42" s="36">
+        <f>COUNTIF(C32:C33,"✓ Met")+COUNTIF(C32:C33,"△ Partial")+COUNTIF(C32:C33,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D42" s="37">
+        <f>IFERROR(SUM(D32:D33)/C42,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OVERALL COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="D44" s="39">
+        <f>IFERROR(SUMPRODUCT(D38:D42,C38:C42)/SUM(C38:C42),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PERFORMANCE BAND</t>
+        </is>
+      </c>
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="18">
+        <f>IF(D44="","",IF(D44&gt;=0.95,"Excellent",IF(D44&gt;=0.90,"Meets Expectations",IF(D44&gt;=0.80,"Needs Improvement","Corrective Education Required"))))</f>
+        <v/>
+      </c>
+      <c r="E45" s="14" t="n"/>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="62" t="n"/>
+      <c r="B46" s="62" t="n"/>
+      <c r="C46" s="62" t="n"/>
+      <c r="D46" s="62" t="n"/>
+      <c r="E46" s="62" t="n"/>
+      <c r="F46" s="62" t="n"/>
+      <c r="G46" s="62" t="n"/>
+      <c r="H46" s="62" t="n"/>
+      <c r="I46" s="62" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="62" t="n"/>
+      <c r="B47" s="62" t="n"/>
+      <c r="C47" s="62" t="n"/>
+      <c r="D47" s="62" t="n"/>
+      <c r="E47" s="62" t="n"/>
+      <c r="F47" s="62" t="n"/>
+      <c r="G47" s="62" t="n"/>
+      <c r="H47" s="62" t="n"/>
+      <c r="I47" s="62" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="62" t="n"/>
+      <c r="B48" s="62" t="n"/>
+      <c r="C48" s="62" t="n"/>
+      <c r="D48" s="62" t="n"/>
+      <c r="E48" s="62" t="n"/>
+      <c r="F48" s="62" t="n"/>
+      <c r="G48" s="62" t="n"/>
+      <c r="H48" s="62" t="n"/>
+      <c r="I48" s="62" t="n"/>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="62" t="n"/>
+      <c r="B49" s="62" t="n"/>
+      <c r="C49" s="62" t="n"/>
+      <c r="D49" s="62" t="n"/>
+      <c r="E49" s="62" t="n"/>
+      <c r="F49" s="62" t="n"/>
+      <c r="G49" s="62" t="n"/>
+      <c r="H49" s="62" t="n"/>
+      <c r="I49" s="62" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="62" t="n"/>
+      <c r="B50" s="62" t="n"/>
+      <c r="C50" s="62" t="n"/>
+      <c r="D50" s="62" t="n"/>
+      <c r="E50" s="62" t="n"/>
+      <c r="F50" s="62" t="n"/>
+      <c r="G50" s="62" t="n"/>
+      <c r="H50" s="62" t="n"/>
+      <c r="I50" s="62" t="n"/>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="62" t="n"/>
+      <c r="B51" s="62" t="n"/>
+      <c r="C51" s="62" t="n"/>
+      <c r="D51" s="62" t="n"/>
+      <c r="E51" s="62" t="n"/>
+      <c r="F51" s="62" t="n"/>
+      <c r="G51" s="62" t="n"/>
+      <c r="H51" s="62" t="n"/>
+      <c r="I51" s="62" t="n"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="62" t="n"/>
+      <c r="B52" s="62" t="n"/>
+      <c r="C52" s="62" t="n"/>
+      <c r="D52" s="62" t="n"/>
+      <c r="E52" s="62" t="n"/>
+      <c r="F52" s="62" t="n"/>
+      <c r="G52" s="62" t="n"/>
+      <c r="H52" s="62" t="n"/>
+      <c r="I52" s="62" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001E7A6E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Clinical Documentation Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>One chart per sheet · tick each item · scoring &amp; rating are automatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>Provider:</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Date of Service:</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>How to audit a claim
+1. Click a Claim 01–10 tab (bottom of the workbook)
+2. Fill yellow header + ratings — auto-scores
+3. Move to the next Claim tab · repeat
+Global metrics roll up automatically
+• Open the Provider Metrics tab — it pulls the 10 claim scores
+  live from the Claim tabs so you see the running provider average.
+Start a new provider (after 10 claims)
+1. Ctrl+click Claim 01 through Claim 10 to group them
+2. Select the yellow header + rating + note cells on any tab
+3. Press Delete → all 10 tabs clear at once
+4. Right-click any tab → Ungroup Sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Claim Number:</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Auditor:</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="51" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Category:</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Payer:</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="52" t="n"/>
+    </row>
+    <row r="7" ht="12" customHeight="1"/>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Documentation element</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Pts</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A · Diagnosis Accuracy   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>All reported diagnoses are clinically supported in the note</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="33">
+        <f>IF(C10="✓ Met",1,IF(C10="△ Partial",0.5,IF(C10="✗ Not Met",0,IF(C10="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Chronic conditions actively addressed at this visit (not just carried forward)</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="33">
+        <f>IF(C11="✓ Met",1,IF(C11="△ Partial",0.5,IF(C11="✗ Not Met",0,IF(C11="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>No unsupported or resolved conditions billed as active</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="33">
+        <f>IF(C12="✓ Met",1,IF(C12="△ Partial",0.5,IF(C12="✗ Not Met",0,IF(C12="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Problem list matches today's assessment &amp; plan</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="33">
+        <f>IF(C13="✓ Met",1,IF(C13="△ Partial",0.5,IF(C13="✗ Not Met",0,IF(C13="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B · Documentation Specificity   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>ICD-10 codes at highest available specificity (avoid 'unspecified')</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="33">
+        <f>IF(C16="✓ Met",1,IF(C16="△ Partial",0.5,IF(C16="✗ Not Met",0,IF(C16="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes: type + complications + control specified</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="33">
+        <f>IF(C17="✓ Met",1,IF(C17="△ Partial",0.5,IF(C17="✗ Not Met",0,IF(C17="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>S / O / A / P sections tell one consistent clinical story</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="33">
+        <f>IF(C18="✓ Met",1,IF(C18="△ Partial",0.5,IF(C18="✗ Not Met",0,IF(C18="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Note signed, dated, and closed by the rendering provider</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="33">
+        <f>IF(C19="✓ Met",1,IF(C19="△ Partial",0.5,IF(C19="✗ Not Met",0,IF(C19="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C · SOAP Note Structure   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Subjective — patient's history, symptoms, and concerns clearly documented</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="33">
+        <f>IF(C22="✓ Met",1,IF(C22="△ Partial",0.5,IF(C22="✗ Not Met",0,IF(C22="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Objective — exam findings, vitals, and relevant test results documented</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="33">
+        <f>IF(C23="✓ Met",1,IF(C23="△ Partial",0.5,IF(C23="✗ Not Met",0,IF(C23="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Assessment — each diagnosis explicitly assessed with clinical reasoning</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="33">
+        <f>IF(C24="✓ Met",1,IF(C24="△ Partial",0.5,IF(C24="✗ Not Met",0,IF(C24="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Plan — treatment plan documented (medication / referral / testing / follow-up)</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="33">
+        <f>IF(C25="✓ Met",1,IF(C25="△ Partial",0.5,IF(C25="✗ Not Met",0,IF(C25="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D · HCC Capture   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Prior-year HCCs recaptured (or explicitly resolved with rationale)</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="33">
+        <f>IF(C28="✓ Met",1,IF(C28="△ Partial",0.5,IF(C28="✗ Not Met",0,IF(C28="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Suspected undocumented chronic conditions captured with support</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="33">
+        <f>IF(C29="✓ Met",1,IF(C29="△ Partial",0.5,IF(C29="✗ Not Met",0,IF(C29="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E · Documentation Supporting Quality Measures   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Screening / measure results documented with specific values (PHQ-9, GAD-7, BMI, BP, HbA1c) — not just 'screened' or 'normal'</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="33">
+        <f>IF(C32="✓ Met",1,IF(C32="△ Partial",0.5,IF(C32="✗ Not Met",0,IF(C32="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Follow-up plan documented when a screening is positive or a result is abnormal (positive PHQ-9 → depression plan; elevated BMI → nutrition counseling)</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33">
+        <f>IF(C33="✓ Met",1,IF(C33="△ Partial",0.5,IF(C33="✗ Not Met",0,IF(C33="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>% Met</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Diagnosis Accuracy</t>
+        </is>
+      </c>
+      <c r="C38" s="36">
+        <f>COUNTIF(C10:C13,"✓ Met")+COUNTIF(C10:C13,"△ Partial")+COUNTIF(C10:C13,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D38" s="37">
+        <f>IFERROR(SUM(D10:D13)/C38,"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Specificity</t>
+        </is>
+      </c>
+      <c r="C39" s="36">
+        <f>COUNTIF(C16:C19,"✓ Met")+COUNTIF(C16:C19,"△ Partial")+COUNTIF(C16:C19,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D39" s="37">
+        <f>IFERROR(SUM(D16:D19)/C39,"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>SOAP Note Structure</t>
+        </is>
+      </c>
+      <c r="C40" s="36">
+        <f>COUNTIF(C22:C25,"✓ Met")+COUNTIF(C22:C25,"△ Partial")+COUNTIF(C22:C25,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D40" s="37">
+        <f>IFERROR(SUM(D22:D25)/C40,"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>HCC Capture</t>
+        </is>
+      </c>
+      <c r="C41" s="36">
+        <f>COUNTIF(C28:C29,"✓ Met")+COUNTIF(C28:C29,"△ Partial")+COUNTIF(C28:C29,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D41" s="37">
+        <f>IFERROR(SUM(D28:D29)/C41,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Supporting Quality Measures</t>
+        </is>
+      </c>
+      <c r="C42" s="36">
+        <f>COUNTIF(C32:C33,"✓ Met")+COUNTIF(C32:C33,"△ Partial")+COUNTIF(C32:C33,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D42" s="37">
+        <f>IFERROR(SUM(D32:D33)/C42,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OVERALL COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="D44" s="39">
+        <f>IFERROR(SUMPRODUCT(D38:D42,C38:C42)/SUM(C38:C42),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PERFORMANCE BAND</t>
+        </is>
+      </c>
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="18">
+        <f>IF(D44="","",IF(D44&gt;=0.95,"Excellent",IF(D44&gt;=0.90,"Meets Expectations",IF(D44&gt;=0.80,"Needs Improvement","Corrective Education Required"))))</f>
+        <v/>
+      </c>
+      <c r="E45" s="14" t="n"/>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="62" t="n"/>
+      <c r="B46" s="62" t="n"/>
+      <c r="C46" s="62" t="n"/>
+      <c r="D46" s="62" t="n"/>
+      <c r="E46" s="62" t="n"/>
+      <c r="F46" s="62" t="n"/>
+      <c r="G46" s="62" t="n"/>
+      <c r="H46" s="62" t="n"/>
+      <c r="I46" s="62" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="62" t="n"/>
+      <c r="B47" s="62" t="n"/>
+      <c r="C47" s="62" t="n"/>
+      <c r="D47" s="62" t="n"/>
+      <c r="E47" s="62" t="n"/>
+      <c r="F47" s="62" t="n"/>
+      <c r="G47" s="62" t="n"/>
+      <c r="H47" s="62" t="n"/>
+      <c r="I47" s="62" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="62" t="n"/>
+      <c r="B48" s="62" t="n"/>
+      <c r="C48" s="62" t="n"/>
+      <c r="D48" s="62" t="n"/>
+      <c r="E48" s="62" t="n"/>
+      <c r="F48" s="62" t="n"/>
+      <c r="G48" s="62" t="n"/>
+      <c r="H48" s="62" t="n"/>
+      <c r="I48" s="62" t="n"/>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="62" t="n"/>
+      <c r="B49" s="62" t="n"/>
+      <c r="C49" s="62" t="n"/>
+      <c r="D49" s="62" t="n"/>
+      <c r="E49" s="62" t="n"/>
+      <c r="F49" s="62" t="n"/>
+      <c r="G49" s="62" t="n"/>
+      <c r="H49" s="62" t="n"/>
+      <c r="I49" s="62" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="62" t="n"/>
+      <c r="B50" s="62" t="n"/>
+      <c r="C50" s="62" t="n"/>
+      <c r="D50" s="62" t="n"/>
+      <c r="E50" s="62" t="n"/>
+      <c r="F50" s="62" t="n"/>
+      <c r="G50" s="62" t="n"/>
+      <c r="H50" s="62" t="n"/>
+      <c r="I50" s="62" t="n"/>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="62" t="n"/>
+      <c r="B51" s="62" t="n"/>
+      <c r="C51" s="62" t="n"/>
+      <c r="D51" s="62" t="n"/>
+      <c r="E51" s="62" t="n"/>
+      <c r="F51" s="62" t="n"/>
+      <c r="G51" s="62" t="n"/>
+      <c r="H51" s="62" t="n"/>
+      <c r="I51" s="62" t="n"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="62" t="n"/>
+      <c r="B52" s="62" t="n"/>
+      <c r="C52" s="62" t="n"/>
+      <c r="D52" s="62" t="n"/>
+      <c r="E52" s="62" t="n"/>
+      <c r="F52" s="62" t="n"/>
+      <c r="G52" s="62" t="n"/>
+      <c r="H52" s="62" t="n"/>
+      <c r="I52" s="62" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001E7A6E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>Clinical Documentation Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>One chart per sheet · tick each item · scoring &amp; rating are automatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>Provider:</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>Date of Service:</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="28" t="inlineStr">
+        <is>
+          <t>How to audit a claim
+1. Click a Claim 01–10 tab (bottom of the workbook)
+2. Fill yellow header + ratings — auto-scores
+3. Move to the next Claim tab · repeat
+Global metrics roll up automatically
+• Open the Provider Metrics tab — it pulls the 10 claim scores
+  live from the Claim tabs so you see the running provider average.
+Start a new provider (after 10 claims)
+1. Ctrl+click Claim 01 through Claim 10 to group them
+2. Select the yellow header + rating + note cells on any tab
+3. Press Delete → all 10 tabs clear at once
+4. Right-click any tab → Ungroup Sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Claim Number:</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Auditor:</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="51" t="n"/>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Category:</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Payer:</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="52" t="n"/>
+    </row>
+    <row r="7" ht="12" customHeight="1"/>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>Documentation element</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n"/>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>Pts</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A · Diagnosis Accuracy   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="31" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>All reported diagnoses are clinically supported in the note</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="33">
+        <f>IF(C10="✓ Met",1,IF(C10="△ Partial",0.5,IF(C10="✗ Not Met",0,IF(C10="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E10" s="10" t="n"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Chronic conditions actively addressed at this visit (not just carried forward)</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="n"/>
+      <c r="D11" s="33">
+        <f>IF(C11="✓ Met",1,IF(C11="△ Partial",0.5,IF(C11="✗ Not Met",0,IF(C11="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E11" s="10" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>No unsupported or resolved conditions billed as active</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="n"/>
+      <c r="D12" s="33">
+        <f>IF(C12="✓ Met",1,IF(C12="△ Partial",0.5,IF(C12="✗ Not Met",0,IF(C12="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E12" s="10" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Problem list matches today's assessment &amp; plan</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="33">
+        <f>IF(C13="✓ Met",1,IF(C13="△ Partial",0.5,IF(C13="✗ Not Met",0,IF(C13="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E13" s="10" t="n"/>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B · Documentation Specificity   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="31" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>ICD-10 codes at highest available specificity (avoid 'unspecified')</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="33">
+        <f>IF(C16="✓ Met",1,IF(C16="△ Partial",0.5,IF(C16="✗ Not Met",0,IF(C16="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E16" s="10" t="n"/>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Diabetes: type + complications + control specified</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="n"/>
+      <c r="D17" s="33">
+        <f>IF(C17="✓ Met",1,IF(C17="△ Partial",0.5,IF(C17="✗ Not Met",0,IF(C17="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E17" s="10" t="n"/>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>S / O / A / P sections tell one consistent clinical story</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="33">
+        <f>IF(C18="✓ Met",1,IF(C18="△ Partial",0.5,IF(C18="✗ Not Met",0,IF(C18="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E18" s="10" t="n"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Note signed, dated, and closed by the rendering provider</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="33">
+        <f>IF(C19="✓ Met",1,IF(C19="△ Partial",0.5,IF(C19="✗ Not Met",0,IF(C19="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E19" s="10" t="n"/>
+    </row>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C · SOAP Note Structure   (4 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Subjective — patient's history, symptoms, and concerns clearly documented</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n"/>
+      <c r="D22" s="33">
+        <f>IF(C22="✓ Met",1,IF(C22="△ Partial",0.5,IF(C22="✗ Not Met",0,IF(C22="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E22" s="10" t="n"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Objective — exam findings, vitals, and relevant test results documented</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="33">
+        <f>IF(C23="✓ Met",1,IF(C23="△ Partial",0.5,IF(C23="✗ Not Met",0,IF(C23="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E23" s="10" t="n"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Assessment — each diagnosis explicitly assessed with clinical reasoning</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="33">
+        <f>IF(C24="✓ Met",1,IF(C24="△ Partial",0.5,IF(C24="✗ Not Met",0,IF(C24="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Plan — treatment plan documented (medication / referral / testing / follow-up)</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="33">
+        <f>IF(C25="✓ Met",1,IF(C25="△ Partial",0.5,IF(C25="✗ Not Met",0,IF(C25="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="6" customHeight="1"/>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D · HCC Capture   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Prior-year HCCs recaptured (or explicitly resolved with rationale)</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="33">
+        <f>IF(C28="✓ Met",1,IF(C28="△ Partial",0.5,IF(C28="✗ Not Met",0,IF(C28="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E28" s="10" t="n"/>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="31" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Suspected undocumented chronic conditions captured with support</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n"/>
+      <c r="D29" s="33">
+        <f>IF(C29="✓ Met",1,IF(C29="△ Partial",0.5,IF(C29="✗ Not Met",0,IF(C29="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  E · Documentation Supporting Quality Measures   (2 items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="31" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Screening / measure results documented with specific values (PHQ-9, GAD-7, BMI, BP, HbA1c) — not just 'screened' or 'normal'</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="33">
+        <f>IF(C32="✓ Met",1,IF(C32="△ Partial",0.5,IF(C32="✗ Not Met",0,IF(C32="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Follow-up plan documented when a screening is positive or a result is abnormal (positive PHQ-9 → depression plan; elevated BMI → nutrition counseling)</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="33">
+        <f>IF(C33="✓ Met",1,IF(C33="△ Partial",0.5,IF(C33="✗ Not Met",0,IF(C33="N/A","",""))))</f>
+        <v/>
+      </c>
+      <c r="E33" s="10" t="n"/>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>§</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>% Met</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Diagnosis Accuracy</t>
+        </is>
+      </c>
+      <c r="C38" s="36">
+        <f>COUNTIF(C10:C13,"✓ Met")+COUNTIF(C10:C13,"△ Partial")+COUNTIF(C10:C13,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D38" s="37">
+        <f>IFERROR(SUM(D10:D13)/C38,"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Specificity</t>
+        </is>
+      </c>
+      <c r="C39" s="36">
+        <f>COUNTIF(C16:C19,"✓ Met")+COUNTIF(C16:C19,"△ Partial")+COUNTIF(C16:C19,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D39" s="37">
+        <f>IFERROR(SUM(D16:D19)/C39,"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>SOAP Note Structure</t>
+        </is>
+      </c>
+      <c r="C40" s="36">
+        <f>COUNTIF(C22:C25,"✓ Met")+COUNTIF(C22:C25,"△ Partial")+COUNTIF(C22:C25,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D40" s="37">
+        <f>IFERROR(SUM(D22:D25)/C40,"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="35" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>HCC Capture</t>
+        </is>
+      </c>
+      <c r="C41" s="36">
+        <f>COUNTIF(C28:C29,"✓ Met")+COUNTIF(C28:C29,"△ Partial")+COUNTIF(C28:C29,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D41" s="37">
+        <f>IFERROR(SUM(D28:D29)/C41,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="35" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Documentation Supporting Quality Measures</t>
+        </is>
+      </c>
+      <c r="C42" s="36">
+        <f>COUNTIF(C32:C33,"✓ Met")+COUNTIF(C32:C33,"△ Partial")+COUNTIF(C32:C33,"✗ Not Met")</f>
+        <v/>
+      </c>
+      <c r="D42" s="37">
+        <f>IFERROR(SUM(D32:D33)/C42,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43"/>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OVERALL COMPLIANCE</t>
+        </is>
+      </c>
+      <c r="D44" s="39">
+        <f>IFERROR(SUMPRODUCT(D38:D42,C38:C42)/SUM(C38:C42),"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  PERFORMANCE BAND</t>
+        </is>
+      </c>
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" s="54" t="n"/>
+      <c r="D45" s="18">
+        <f>IF(D44="","",IF(D44&gt;=0.95,"Excellent",IF(D44&gt;=0.90,"Meets Expectations",IF(D44&gt;=0.80,"Needs Improvement","Corrective Education Required"))))</f>
+        <v/>
+      </c>
+      <c r="E45" s="14" t="n"/>
+    </row>
+    <row r="46" ht="28" customHeight="1">
+      <c r="A46" s="62" t="n"/>
+      <c r="B46" s="62" t="n"/>
+      <c r="C46" s="62" t="n"/>
+      <c r="D46" s="62" t="n"/>
+      <c r="E46" s="62" t="n"/>
+      <c r="F46" s="62" t="n"/>
+      <c r="G46" s="62" t="n"/>
+      <c r="H46" s="62" t="n"/>
+      <c r="I46" s="62" t="n"/>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="62" t="n"/>
+      <c r="B47" s="62" t="n"/>
+      <c r="C47" s="62" t="n"/>
+      <c r="D47" s="62" t="n"/>
+      <c r="E47" s="62" t="n"/>
+      <c r="F47" s="62" t="n"/>
+      <c r="G47" s="62" t="n"/>
+      <c r="H47" s="62" t="n"/>
+      <c r="I47" s="62" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="62" t="n"/>
+      <c r="B48" s="62" t="n"/>
+      <c r="C48" s="62" t="n"/>
+      <c r="D48" s="62" t="n"/>
+      <c r="E48" s="62" t="n"/>
+      <c r="F48" s="62" t="n"/>
+      <c r="G48" s="62" t="n"/>
+      <c r="H48" s="62" t="n"/>
+      <c r="I48" s="62" t="n"/>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="62" t="n"/>
+      <c r="B49" s="62" t="n"/>
+      <c r="C49" s="62" t="n"/>
+      <c r="D49" s="62" t="n"/>
+      <c r="E49" s="62" t="n"/>
+      <c r="F49" s="62" t="n"/>
+      <c r="G49" s="62" t="n"/>
+      <c r="H49" s="62" t="n"/>
+      <c r="I49" s="62" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="62" t="n"/>
+      <c r="B50" s="62" t="n"/>
+      <c r="C50" s="62" t="n"/>
+      <c r="D50" s="62" t="n"/>
+      <c r="E50" s="62" t="n"/>
+      <c r="F50" s="62" t="n"/>
+      <c r="G50" s="62" t="n"/>
+      <c r="H50" s="62" t="n"/>
+      <c r="I50" s="62" t="n"/>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="62" t="n"/>
+      <c r="B51" s="62" t="n"/>
+      <c r="C51" s="62" t="n"/>
+      <c r="D51" s="62" t="n"/>
+      <c r="E51" s="62" t="n"/>
+      <c r="F51" s="62" t="n"/>
+      <c r="G51" s="62" t="n"/>
+      <c r="H51" s="62" t="n"/>
+      <c r="I51" s="62" t="n"/>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="62" t="n"/>
+      <c r="B52" s="62" t="n"/>
+      <c r="C52" s="62" t="n"/>
+      <c r="D52" s="62" t="n"/>
+      <c r="E52" s="62" t="n"/>
+      <c r="F52" s="62" t="n"/>
+      <c r="G52" s="62" t="n"/>
+      <c r="H52" s="62" t="n"/>
+      <c r="I52" s="62" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="E4:E6"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A27:E27"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/docs/Clinical_Documentation_Audit_Simple.xlsx
+++ b/docs/Clinical_Documentation_Audit_Simple.xlsx
@@ -272,7 +272,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -407,11 +407,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -699,6 +708,8 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1839,7 +1850,6 @@
       <c r="E33" s="10" t="n"/>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="35"/>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="34" t="inlineStr">
         <is>
@@ -1975,7 +1985,6 @@
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
-    <row r="43"/>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
         <is>
@@ -2654,7 +2663,6 @@
       <c r="E33" s="10" t="n"/>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="35"/>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="34" t="inlineStr">
         <is>
@@ -2786,7 +2794,6 @@
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
-    <row r="43"/>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
         <is>
@@ -2904,6 +2911,17 @@
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="A27:E27"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Diabetes,Chronic Kidney Disease,Annual Wellness Visit,High RAF Patient,Random Selection"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Medicare Advantage,Commercial,Medicaid,Dual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C10:C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓ Met,△ Partial,✗ Not Met,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
@@ -3350,7 +3368,6 @@
       <c r="E33" s="10" t="n"/>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="35"/>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="34" t="inlineStr">
         <is>
@@ -3482,7 +3499,6 @@
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
-    <row r="43"/>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
         <is>
@@ -3600,6 +3616,17 @@
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="A27:E27"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Diabetes,Chronic Kidney Disease,Annual Wellness Visit,High RAF Patient,Random Selection"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Medicare Advantage,Commercial,Medicaid,Dual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C10:C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓ Met,△ Partial,✗ Not Met,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
@@ -4046,7 +4073,6 @@
       <c r="E33" s="10" t="n"/>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="35"/>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="34" t="inlineStr">
         <is>
@@ -4178,7 +4204,6 @@
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
-    <row r="43"/>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
         <is>
@@ -4296,6 +4321,17 @@
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="A27:E27"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Diabetes,Chronic Kidney Disease,Annual Wellness Visit,High RAF Patient,Random Selection"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Medicare Advantage,Commercial,Medicaid,Dual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C10:C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓ Met,△ Partial,✗ Not Met,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
@@ -8487,6 +8523,7 @@
           <t>Provider (from Claim 01)</t>
         </is>
       </c>
+      <c r="C4" s="54" t="n"/>
       <c r="D4" s="88">
         <f>'Claim 01'!B4</f>
         <v/>
@@ -8500,35 +8537,37 @@
           <t>Claims completed</t>
         </is>
       </c>
-      <c r="B6" s="45" t="n"/>
-      <c r="C6" s="45" t="n"/>
+      <c r="B6" s="53" t="n"/>
+      <c r="C6" s="54" t="n"/>
       <c r="D6" s="92" t="inlineStr">
         <is>
           <t>Average compliance %</t>
         </is>
       </c>
-      <c r="E6" s="45" t="n"/>
-      <c r="F6" s="45" t="n"/>
+      <c r="E6" s="53" t="n"/>
+      <c r="F6" s="54" t="n"/>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="93">
         <f>COUNT('Claim 01:Claim 10'!I44)</f>
         <v/>
       </c>
-      <c r="B7" s="94" t="n"/>
-      <c r="C7" s="94" t="n"/>
+      <c r="B7" s="107" t="n"/>
+      <c r="C7" s="59" t="n"/>
       <c r="D7" s="95">
         <f>IFERROR(AVERAGE('Claim 01:Claim 10'!I44),"")</f>
         <v/>
       </c>
-      <c r="E7" s="94" t="n"/>
-      <c r="F7" s="94" t="n"/>
+      <c r="E7" s="107" t="n"/>
+      <c r="F7" s="59" t="n"/>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="B8" s="94" t="n"/>
-      <c r="C8" s="94" t="n"/>
-      <c r="E8" s="94" t="n"/>
-      <c r="F8" s="94" t="n"/>
+      <c r="A8" s="60" t="n"/>
+      <c r="B8" s="108" t="n"/>
+      <c r="C8" s="61" t="n"/>
+      <c r="D8" s="60" t="n"/>
+      <c r="E8" s="108" t="n"/>
+      <c r="F8" s="61" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="92" t="inlineStr">
@@ -8536,35 +8575,37 @@
           <t>Meeting Expectations (≥90%)</t>
         </is>
       </c>
-      <c r="B10" s="45" t="n"/>
-      <c r="C10" s="45" t="n"/>
+      <c r="B10" s="53" t="n"/>
+      <c r="C10" s="54" t="n"/>
       <c r="D10" s="92" t="inlineStr">
         <is>
           <t>Corrective Required (&lt;80%)</t>
         </is>
       </c>
-      <c r="E10" s="45" t="n"/>
-      <c r="F10" s="45" t="n"/>
+      <c r="E10" s="53" t="n"/>
+      <c r="F10" s="54" t="n"/>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="93">
         <f>COUNTIFS(E17:E26,"&gt;=0.9",E17:E26,"&lt;&gt;")</f>
         <v/>
       </c>
-      <c r="B11" s="94" t="n"/>
-      <c r="C11" s="94" t="n"/>
+      <c r="B11" s="107" t="n"/>
+      <c r="C11" s="59" t="n"/>
       <c r="D11" s="93">
         <f>COUNTIFS(E17:E26,"&lt;0.8",E17:E26,"&gt;0")</f>
         <v/>
       </c>
-      <c r="E11" s="94" t="n"/>
-      <c r="F11" s="94" t="n"/>
+      <c r="E11" s="107" t="n"/>
+      <c r="F11" s="59" t="n"/>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="B12" s="94" t="n"/>
-      <c r="C12" s="94" t="n"/>
-      <c r="E12" s="94" t="n"/>
-      <c r="F12" s="94" t="n"/>
+      <c r="A12" s="60" t="n"/>
+      <c r="B12" s="108" t="n"/>
+      <c r="C12" s="61" t="n"/>
+      <c r="D12" s="60" t="n"/>
+      <c r="E12" s="108" t="n"/>
+      <c r="F12" s="61" t="n"/>
     </row>
     <row r="14" ht="12" customHeight="1"/>
     <row r="15" ht="26" customHeight="1">
@@ -8862,10 +8903,14 @@
           <t xml:space="preserve">  OVERALL PROVIDER PERFORMANCE BAND</t>
         </is>
       </c>
+      <c r="B28" s="53" t="n"/>
+      <c r="C28" s="53" t="n"/>
+      <c r="D28" s="54" t="n"/>
       <c r="E28" s="98">
         <f>IF(D7="","",IF(D7&gt;=0.95,"Excellent",IF(D7&gt;=0.9,"Meets Expectations",IF(D7&gt;=0.8,"Needs Improvement","Corrective Education Required"))))</f>
         <v/>
       </c>
+      <c r="F28" s="54" t="n"/>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="96" t="inlineStr">
@@ -8880,10 +8925,10 @@
           <t>Band</t>
         </is>
       </c>
-      <c r="B31" s="45" t="n"/>
-      <c r="C31" s="45" t="n"/>
-      <c r="D31" s="45" t="n"/>
-      <c r="E31" s="45" t="n"/>
+      <c r="B31" s="53" t="n"/>
+      <c r="C31" s="53" t="n"/>
+      <c r="D31" s="53" t="n"/>
+      <c r="E31" s="54" t="n"/>
       <c r="F31" s="6" t="inlineStr">
         <is>
           <t>Count</t>
@@ -8896,10 +8941,10 @@
           <t>Excellent</t>
         </is>
       </c>
-      <c r="B32" s="100" t="n"/>
-      <c r="C32" s="100" t="n"/>
-      <c r="D32" s="100" t="n"/>
-      <c r="E32" s="100" t="n"/>
+      <c r="B32" s="53" t="n"/>
+      <c r="C32" s="53" t="n"/>
+      <c r="D32" s="53" t="n"/>
+      <c r="E32" s="54" t="n"/>
       <c r="F32" s="18">
         <f>COUNTIF(F17:F26,"Excellent")</f>
         <v/>
@@ -8911,10 +8956,10 @@
           <t>Meets Expectations</t>
         </is>
       </c>
-      <c r="B33" s="102" t="n"/>
-      <c r="C33" s="102" t="n"/>
-      <c r="D33" s="102" t="n"/>
-      <c r="E33" s="102" t="n"/>
+      <c r="B33" s="53" t="n"/>
+      <c r="C33" s="53" t="n"/>
+      <c r="D33" s="53" t="n"/>
+      <c r="E33" s="54" t="n"/>
       <c r="F33" s="18">
         <f>COUNTIF(F17:F26,"Meets Expectations")</f>
         <v/>
@@ -8926,10 +8971,10 @@
           <t>Needs Improvement</t>
         </is>
       </c>
-      <c r="B34" s="104" t="n"/>
-      <c r="C34" s="104" t="n"/>
-      <c r="D34" s="104" t="n"/>
-      <c r="E34" s="104" t="n"/>
+      <c r="B34" s="53" t="n"/>
+      <c r="C34" s="53" t="n"/>
+      <c r="D34" s="53" t="n"/>
+      <c r="E34" s="54" t="n"/>
       <c r="F34" s="18">
         <f>COUNTIF(F17:F26,"Needs Improvement")</f>
         <v/>
@@ -8941,10 +8986,10 @@
           <t>Corrective Education Required</t>
         </is>
       </c>
-      <c r="B35" s="106" t="n"/>
-      <c r="C35" s="106" t="n"/>
-      <c r="D35" s="106" t="n"/>
-      <c r="E35" s="106" t="n"/>
+      <c r="B35" s="53" t="n"/>
+      <c r="C35" s="53" t="n"/>
+      <c r="D35" s="53" t="n"/>
+      <c r="E35" s="54" t="n"/>
       <c r="F35" s="18">
         <f>COUNTIF(F17:F26,"Corrective Education Required")</f>
         <v/>
@@ -9480,7 +9525,6 @@
       <c r="E33" s="10" t="n"/>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="35"/>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="34" t="inlineStr">
         <is>
@@ -9612,7 +9656,6 @@
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
-    <row r="43"/>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
         <is>
@@ -9730,6 +9773,17 @@
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="A27:E27"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Diabetes,Chronic Kidney Disease,Annual Wellness Visit,High RAF Patient,Random Selection"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Medicare Advantage,Commercial,Medicaid,Dual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C10:C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓ Met,△ Partial,✗ Not Met,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
@@ -10176,7 +10230,6 @@
       <c r="E33" s="10" t="n"/>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="35"/>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="34" t="inlineStr">
         <is>
@@ -10308,7 +10361,6 @@
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
-    <row r="43"/>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
         <is>
@@ -10426,6 +10478,17 @@
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="A27:E27"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Diabetes,Chronic Kidney Disease,Annual Wellness Visit,High RAF Patient,Random Selection"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Medicare Advantage,Commercial,Medicaid,Dual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C10:C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓ Met,△ Partial,✗ Not Met,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
@@ -10872,7 +10935,6 @@
       <c r="E33" s="10" t="n"/>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="35"/>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="34" t="inlineStr">
         <is>
@@ -11004,7 +11066,6 @@
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
-    <row r="43"/>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
         <is>
@@ -11122,6 +11183,17 @@
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="A27:E27"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Diabetes,Chronic Kidney Disease,Annual Wellness Visit,High RAF Patient,Random Selection"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Medicare Advantage,Commercial,Medicaid,Dual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C10:C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓ Met,△ Partial,✗ Not Met,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
@@ -11568,7 +11640,6 @@
       <c r="E33" s="10" t="n"/>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="35"/>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="34" t="inlineStr">
         <is>
@@ -11700,7 +11771,6 @@
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
-    <row r="43"/>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
         <is>
@@ -11818,6 +11888,17 @@
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="A27:E27"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Diabetes,Chronic Kidney Disease,Annual Wellness Visit,High RAF Patient,Random Selection"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Medicare Advantage,Commercial,Medicaid,Dual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C10:C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓ Met,△ Partial,✗ Not Met,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
@@ -12264,7 +12345,6 @@
       <c r="E33" s="10" t="n"/>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="35"/>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="34" t="inlineStr">
         <is>
@@ -12396,7 +12476,6 @@
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
-    <row r="43"/>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
         <is>
@@ -12514,6 +12593,17 @@
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="A27:E27"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Diabetes,Chronic Kidney Disease,Annual Wellness Visit,High RAF Patient,Random Selection"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Medicare Advantage,Commercial,Medicaid,Dual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C10:C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓ Met,△ Partial,✗ Not Met,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
@@ -12960,7 +13050,6 @@
       <c r="E33" s="10" t="n"/>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="35"/>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="34" t="inlineStr">
         <is>
@@ -13092,7 +13181,6 @@
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
-    <row r="43"/>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
         <is>
@@ -13210,6 +13298,17 @@
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="A27:E27"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Diabetes,Chronic Kidney Disease,Annual Wellness Visit,High RAF Patient,Random Selection"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Medicare Advantage,Commercial,Medicaid,Dual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C10:C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓ Met,△ Partial,✗ Not Met,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>
@@ -13656,7 +13755,6 @@
       <c r="E33" s="10" t="n"/>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="35"/>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="34" t="inlineStr">
         <is>
@@ -13788,7 +13886,6 @@
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
-    <row r="43"/>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
         <is>
@@ -13906,6 +14003,17 @@
     <mergeCell ref="A9:E9"/>
     <mergeCell ref="A27:E27"/>
   </mergeCells>
+  <dataValidations count="3">
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Diabetes,Chronic Kidney Disease,Annual Wellness Visit,High RAF Patient,Random Selection"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Medicare Advantage,Commercial,Medicaid,Dual"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C10:C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓ Met,△ Partial,✗ Not Met,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="1" fitToWidth="1"/>

--- a/docs/Clinical_Documentation_Audit_Simple.xlsx
+++ b/docs/Clinical_Documentation_Audit_Simple.xlsx
@@ -1850,6 +1850,7 @@
       <c r="E33" s="10" t="n"/>
     </row>
     <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="34" t="inlineStr">
         <is>
@@ -1985,6 +1986,7 @@
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
+    <row r="43"/>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
         <is>
@@ -8549,13 +8551,13 @@
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="93">
-        <f>COUNT('Claim 01:Claim 10'!I44)</f>
+        <f>COUNT('Claim 01:Claim 10'!D44)</f>
         <v/>
       </c>
       <c r="B7" s="107" t="n"/>
       <c r="C7" s="59" t="n"/>
       <c r="D7" s="95">
-        <f>IFERROR(AVERAGE('Claim 01:Claim 10'!I44),"")</f>
+        <f>IFERROR(AVERAGE('Claim 01:Claim 10'!D44),"")</f>
         <v/>
       </c>
       <c r="E7" s="107" t="n"/>
@@ -8664,11 +8666,11 @@
         <v/>
       </c>
       <c r="E17" s="12">
-        <f>IFERROR('Claim 01'!I44,"")</f>
+        <f>IFERROR('Claim 01'!D44,"")</f>
         <v/>
       </c>
       <c r="F17" s="9">
-        <f>IFERROR('Claim 01'!I45,"")</f>
+        <f>IFERROR('Claim 01'!D45,"")</f>
         <v/>
       </c>
     </row>
@@ -8689,11 +8691,11 @@
         <v/>
       </c>
       <c r="E18" s="12">
-        <f>IFERROR('Claim 02'!I44,"")</f>
+        <f>IFERROR('Claim 02'!D44,"")</f>
         <v/>
       </c>
       <c r="F18" s="9">
-        <f>IFERROR('Claim 02'!I45,"")</f>
+        <f>IFERROR('Claim 02'!D45,"")</f>
         <v/>
       </c>
     </row>
@@ -8714,11 +8716,11 @@
         <v/>
       </c>
       <c r="E19" s="12">
-        <f>IFERROR('Claim 03'!I44,"")</f>
+        <f>IFERROR('Claim 03'!D44,"")</f>
         <v/>
       </c>
       <c r="F19" s="9">
-        <f>IFERROR('Claim 03'!I45,"")</f>
+        <f>IFERROR('Claim 03'!D45,"")</f>
         <v/>
       </c>
     </row>
@@ -8739,11 +8741,11 @@
         <v/>
       </c>
       <c r="E20" s="12">
-        <f>IFERROR('Claim 04'!I44,"")</f>
+        <f>IFERROR('Claim 04'!D44,"")</f>
         <v/>
       </c>
       <c r="F20" s="9">
-        <f>IFERROR('Claim 04'!I45,"")</f>
+        <f>IFERROR('Claim 04'!D45,"")</f>
         <v/>
       </c>
     </row>
@@ -8764,11 +8766,11 @@
         <v/>
       </c>
       <c r="E21" s="12">
-        <f>IFERROR('Claim 05'!I44,"")</f>
+        <f>IFERROR('Claim 05'!D44,"")</f>
         <v/>
       </c>
       <c r="F21" s="9">
-        <f>IFERROR('Claim 05'!I45,"")</f>
+        <f>IFERROR('Claim 05'!D45,"")</f>
         <v/>
       </c>
     </row>
@@ -8789,11 +8791,11 @@
         <v/>
       </c>
       <c r="E22" s="12">
-        <f>IFERROR('Claim 06'!I44,"")</f>
+        <f>IFERROR('Claim 06'!D44,"")</f>
         <v/>
       </c>
       <c r="F22" s="9">
-        <f>IFERROR('Claim 06'!I45,"")</f>
+        <f>IFERROR('Claim 06'!D45,"")</f>
         <v/>
       </c>
     </row>
@@ -8814,11 +8816,11 @@
         <v/>
       </c>
       <c r="E23" s="12">
-        <f>IFERROR('Claim 07'!I44,"")</f>
+        <f>IFERROR('Claim 07'!D44,"")</f>
         <v/>
       </c>
       <c r="F23" s="9">
-        <f>IFERROR('Claim 07'!I45,"")</f>
+        <f>IFERROR('Claim 07'!D45,"")</f>
         <v/>
       </c>
     </row>
@@ -8839,11 +8841,11 @@
         <v/>
       </c>
       <c r="E24" s="12">
-        <f>IFERROR('Claim 08'!I44,"")</f>
+        <f>IFERROR('Claim 08'!D44,"")</f>
         <v/>
       </c>
       <c r="F24" s="9">
-        <f>IFERROR('Claim 08'!I45,"")</f>
+        <f>IFERROR('Claim 08'!D45,"")</f>
         <v/>
       </c>
     </row>
@@ -8864,11 +8866,11 @@
         <v/>
       </c>
       <c r="E25" s="12">
-        <f>IFERROR('Claim 09'!I44,"")</f>
+        <f>IFERROR('Claim 09'!D44,"")</f>
         <v/>
       </c>
       <c r="F25" s="9">
-        <f>IFERROR('Claim 09'!I45,"")</f>
+        <f>IFERROR('Claim 09'!D45,"")</f>
         <v/>
       </c>
     </row>
@@ -8889,11 +8891,11 @@
         <v/>
       </c>
       <c r="E26" s="12">
-        <f>IFERROR('Claim 10'!I44,"")</f>
+        <f>IFERROR('Claim 10'!D44,"")</f>
         <v/>
       </c>
       <c r="F26" s="9">
-        <f>IFERROR('Claim 10'!I45,"")</f>
+        <f>IFERROR('Claim 10'!D45,"")</f>
         <v/>
       </c>
     </row>

--- a/docs/Clinical_Documentation_Audit_Simple.xlsx
+++ b/docs/Clinical_Documentation_Audit_Simple.xlsx
@@ -420,7 +420,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -710,6 +710,9 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1494,7 +1497,14 @@
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="52" t="n"/>
     </row>
-    <row r="7" ht="12" customHeight="1"/>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>Date of audit:</t>
+        </is>
+      </c>
+      <c r="B7" s="109" t="n"/>
+    </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="29" t="inlineStr">
         <is>
@@ -1850,7 +1860,6 @@
       <c r="E33" s="10" t="n"/>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="35"/>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="34" t="inlineStr">
         <is>
@@ -1986,7 +1995,6 @@
       </c>
       <c r="E42" s="14" t="inlineStr"/>
     </row>
-    <row r="43"/>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="38" t="inlineStr">
         <is>
@@ -2317,7 +2325,14 @@
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="52" t="n"/>
     </row>
-    <row r="7" ht="12" customHeight="1"/>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>Date of audit:</t>
+        </is>
+      </c>
+      <c r="B7" s="109" t="n"/>
+    </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="29" t="inlineStr">
         <is>
@@ -3022,7 +3037,14 @@
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="52" t="n"/>
     </row>
-    <row r="7" ht="12" customHeight="1"/>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>Date of audit:</t>
+        </is>
+      </c>
+      <c r="B7" s="109" t="n"/>
+    </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="29" t="inlineStr">
         <is>
@@ -3727,7 +3749,14 @@
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="52" t="n"/>
     </row>
-    <row r="7" ht="12" customHeight="1"/>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>Date of audit:</t>
+        </is>
+      </c>
+      <c r="B7" s="109" t="n"/>
+    </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="29" t="inlineStr">
         <is>
@@ -9179,7 +9208,14 @@
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="52" t="n"/>
     </row>
-    <row r="7" ht="12" customHeight="1"/>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>Date of audit:</t>
+        </is>
+      </c>
+      <c r="B7" s="109" t="n"/>
+    </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="29" t="inlineStr">
         <is>
@@ -9884,7 +9920,14 @@
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="52" t="n"/>
     </row>
-    <row r="7" ht="12" customHeight="1"/>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>Date of audit:</t>
+        </is>
+      </c>
+      <c r="B7" s="109" t="n"/>
+    </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="29" t="inlineStr">
         <is>
@@ -10589,7 +10632,14 @@
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="52" t="n"/>
     </row>
-    <row r="7" ht="12" customHeight="1"/>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>Date of audit:</t>
+        </is>
+      </c>
+      <c r="B7" s="109" t="n"/>
+    </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="29" t="inlineStr">
         <is>
@@ -11294,7 +11344,14 @@
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="52" t="n"/>
     </row>
-    <row r="7" ht="12" customHeight="1"/>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>Date of audit:</t>
+        </is>
+      </c>
+      <c r="B7" s="109" t="n"/>
+    </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="29" t="inlineStr">
         <is>
@@ -11999,7 +12056,14 @@
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="52" t="n"/>
     </row>
-    <row r="7" ht="12" customHeight="1"/>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>Date of audit:</t>
+        </is>
+      </c>
+      <c r="B7" s="109" t="n"/>
+    </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="29" t="inlineStr">
         <is>
@@ -12704,7 +12768,14 @@
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="52" t="n"/>
     </row>
-    <row r="7" ht="12" customHeight="1"/>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>Date of audit:</t>
+        </is>
+      </c>
+      <c r="B7" s="109" t="n"/>
+    </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="29" t="inlineStr">
         <is>
@@ -13409,7 +13480,14 @@
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="52" t="n"/>
     </row>
-    <row r="7" ht="12" customHeight="1"/>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>Date of audit:</t>
+        </is>
+      </c>
+      <c r="B7" s="109" t="n"/>
+    </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="29" t="inlineStr">
         <is>

--- a/docs/Clinical_Documentation_Audit_Simple.xlsx
+++ b/docs/Clinical_Documentation_Audit_Simple.xlsx
@@ -420,7 +420,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -711,6 +711,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -1467,13 +1470,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="26" customHeight="1">
       <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Claim Number:</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
+      <c r="B5" s="110" t="n"/>
       <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Auditor:</t>
@@ -2295,13 +2298,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="26" customHeight="1">
       <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Claim Number:</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
+      <c r="B5" s="110" t="n"/>
       <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Auditor:</t>
@@ -3007,13 +3010,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="26" customHeight="1">
       <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Claim Number:</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
+      <c r="B5" s="110" t="n"/>
       <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Auditor:</t>
@@ -3719,13 +3722,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="26" customHeight="1">
       <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Claim Number:</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
+      <c r="B5" s="110" t="n"/>
       <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Auditor:</t>
@@ -9178,13 +9181,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="26" customHeight="1">
       <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Claim Number:</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
+      <c r="B5" s="110" t="n"/>
       <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Auditor:</t>
@@ -9890,13 +9893,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="26" customHeight="1">
       <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Claim Number:</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
+      <c r="B5" s="110" t="n"/>
       <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Auditor:</t>
@@ -10602,13 +10605,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="26" customHeight="1">
       <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Claim Number:</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
+      <c r="B5" s="110" t="n"/>
       <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Auditor:</t>
@@ -11314,13 +11317,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="26" customHeight="1">
       <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Claim Number:</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
+      <c r="B5" s="110" t="n"/>
       <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Auditor:</t>
@@ -12026,13 +12029,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="26" customHeight="1">
       <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Claim Number:</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
+      <c r="B5" s="110" t="n"/>
       <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Auditor:</t>
@@ -12738,13 +12741,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="26" customHeight="1">
       <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Claim Number:</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
+      <c r="B5" s="110" t="n"/>
       <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Auditor:</t>
@@ -13450,13 +13453,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="28" customHeight="1">
+    <row r="5" ht="26" customHeight="1">
       <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Claim Number:</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n"/>
+      <c r="B5" s="110" t="n"/>
       <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Auditor:</t>

--- a/docs/Clinical_Documentation_Audit_Simple.xlsx
+++ b/docs/Clinical_Documentation_Audit_Simple.xlsx
@@ -848,39 +848,6 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Quarterly Report'!B12</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="7"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Quarterly Report'!$C$12:$N$12</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Quarterly Report'!$C$12:$N$12</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
               <f>'Quarterly Report'!B13</f>
             </strRef>
           </tx>
@@ -910,8 +877,8 @@
           </val>
         </ser>
         <ser>
-          <idx val="2"/>
-          <order val="2"/>
+          <idx val="1"/>
+          <order val="1"/>
           <tx>
             <strRef>
               <f>'Quarterly Report'!B14</f>
@@ -943,8 +910,8 @@
           </val>
         </ser>
         <ser>
-          <idx val="3"/>
-          <order val="3"/>
+          <idx val="2"/>
+          <order val="2"/>
           <tx>
             <strRef>
               <f>'Quarterly Report'!B15</f>
@@ -976,8 +943,8 @@
           </val>
         </ser>
         <ser>
-          <idx val="4"/>
-          <order val="4"/>
+          <idx val="3"/>
+          <order val="3"/>
           <tx>
             <strRef>
               <f>'Quarterly Report'!B16</f>
@@ -1009,8 +976,8 @@
           </val>
         </ser>
         <ser>
-          <idx val="5"/>
-          <order val="5"/>
+          <idx val="4"/>
+          <order val="4"/>
           <tx>
             <strRef>
               <f>'Quarterly Report'!B17</f>
